--- a/Xlsx filer/Kvickly_produkter.xlsx
+++ b/Xlsx filer/Kvickly_produkter.xlsx
@@ -2241,7 +2241,11 @@
           <t>Ølands,</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>35,00. kr/stk</t>
@@ -2285,7 +2289,11 @@
           <t>Tebolle*</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>4,00. kr/stk</t>
@@ -2329,7 +2337,11 @@
           <t>Onsdagssnegl*</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>10,00. kr/stk</t>
@@ -2533,7 +2545,11 @@
           <t>Coop</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>4 stk</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>198,57. kr/kg</t>
@@ -2585,7 +2601,11 @@
           <t>Grillmarked</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>7 stk</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
         <v>100</v>
@@ -2737,7 +2757,11 @@
           <t>Courget</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>6,00. kr/stk</t>
@@ -2941,7 +2965,11 @@
           <t>PremiuM</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2 stk</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>214,29. kr/kg</t>
@@ -3097,7 +3125,11 @@
           <t>BORNHOLMERGRISEN</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>217,78. kr/kg</t>
@@ -3313,7 +3345,11 @@
           <t>Delikatessens</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>165,00. kr/stk</t>
@@ -3413,7 +3449,11 @@
           <t>Delikatessens</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>85,00. kr/stk</t>
@@ -3465,7 +3505,11 @@
           <t>Stjernekaster</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>45,00. kr/stk</t>
@@ -3685,7 +3729,11 @@
           <t>Galia</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>20,00. kr/stk</t>
@@ -4003,7 +4051,11 @@
           <t>Puslespil*</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
@@ -4049,7 +4101,11 @@
           <t>AquaPlay</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
@@ -4095,7 +4151,11 @@
           <t>X-SHOT</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
@@ -5583,7 +5643,11 @@
           <t>Änglamark</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="n">
         <v>20</v>
@@ -7143,7 +7207,11 @@
           <t>Merrild</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>3 stk</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="n">
         <v>49</v>
@@ -7191,7 +7259,11 @@
           <t>Fleece</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="n">
         <v>50</v>
@@ -7277,7 +7349,11 @@
           <t>Cottonfield</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
@@ -7507,7 +7583,11 @@
           <t>Big-T</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
@@ -7595,7 +7675,11 @@
           <t>Kosmetiktaske</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>

--- a/Xlsx filer/Kvickly_produkter.xlsx
+++ b/Xlsx filer/Kvickly_produkter.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L137"/>
+  <dimension ref="A1:L175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -507,41 +507,41 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Merrild eller Lavazza formalet kaffe eller Merrild instant kaffe</t>
+          <t>Lurpak smør eller smørbar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Merrild</t>
+          <t>Lurpak</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>120-500 g</t>
+          <t>200 g</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>408,33. kr/kg</t>
+          <t>60,00. kr/kg</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1029583</t>
+          <t>1032087</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdbcab21afefadd5ab9fe3e3e45518b02%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F38455839fd5b675dae832f327d5949d3%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9c32ca11754f00b1759a64cfd34c0258%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fad908444ef3c203efd8a81c3109846e0%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F94ca2bf34837bac93b3935fa90353609&amp;w=552&amp;s=8cec18191d3d48971fc627d4685b5600</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F00848faaef9298bc5599957fdac20828&amp;w=552&amp;s=67112d89fa479c02a4eeafbcabeab9d0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>f67c6d531c3823a1</t>
+          <t>d5aaeaf5d00f1071</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -549,11 +549,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>1 pose/glas</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -563,41 +559,41 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Änglamark økologisk hakket oksekød 8-12%</t>
+          <t>BKI,Karat eller Peter Larsen formalet kaffe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>BKI,Karat</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>350-400 g</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>122,50. kr/kg</t>
+          <t>100,00. kr/kg</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1029587</t>
+          <t>1032387</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa253d8f52b53114ff0677db343dfc37a&amp;w=252&amp;s=1c435b201e2c7be8ba9d865b1f735600</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5c7484d9ad6d8e373a8d16cfdcb54de3&amp;w=249&amp;s=b68b75743508af3113c0ce9531c9ebe7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ee3d39c34cc05372</t>
+          <t>c0ad1f0e2a5af1f1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -607,7 +603,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -619,41 +615,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Naturli' drik</t>
+          <t>Langelænder pølser</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Naturli'</t>
+          <t>Langelænder</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1 l</t>
+          <t>325-360 g</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10,00. kr/l</t>
+          <t>58,46. kr/kg</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1029588</t>
+          <t>1032084</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F980f4ec50f81d09dec94d9ec80402d77%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd4c2e0d85a3443bda6ad6c0c1f003692%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd26f5699d5bfb9735210634c42a2a459&amp;w=252&amp;s=5b0b1b5f4214a0ed843206d7714302bb</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb4c4e33e0c7e682696281fe491faceb9%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F063e68ae8d1b5b4ca16fe29584c62c9c%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0dbc3875575dca29c324254185507391&amp;w=252&amp;s=c5c478b13c1db1796b9221f3e20f6795</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>d95972540e6337a6</t>
+          <t>907ed42aa43de87a</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -663,7 +659,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -675,41 +671,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Riberhus skæreost</t>
+          <t>Xtra! hel kylling</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Riberhus</t>
+          <t>Xtra!</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>. 430 g</t>
+          <t>1450 g</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>90,70. kr/kg</t>
+          <t>33,79. kr/kg</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1029592</t>
+          <t>1032086</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5932c78cfeea5c479b539338e154b8d9%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc4b8b92b2f71cb39a7a3b7a88fb78804&amp;w=375&amp;s=e1fdbf80415108e376aa55e9d8d285b8</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F95e444724e8cd27b4d3504a329627bc6&amp;w=252&amp;s=da42f402f5b4f61765113f0589525655</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>d0e26b602e9ae61f</t>
+          <t>c33e6dc1341c369b</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -731,41 +727,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ristorante pizza</t>
+          <t>Hardys Crest</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ristorante</t>
+          <t>Hardys</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>320-340 g</t>
+          <t>. 75 cl</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>62,50. kr/kg</t>
+          <t>46,67. kr/l</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>79.95.</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1029893</t>
+          <t>1032088</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7c2ee0226514b3cf1aa0028648d1b946%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F239634d066dca3b53d5f4cbc9755ec87&amp;w=352&amp;s=9552d3e2cc62baccc966c1a8475cb924</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1f074fb7caf6b3180dba8606c6265be0&amp;w=261&amp;s=26122da5e7460170d339212230656b3a</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>cce74d4868393717</t>
+          <t>8d3c72628ae9758d</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -787,45 +787,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Torres Coronas eller Esmeralda</t>
+          <t>Galle &amp; Jessen pålægschokolade</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Torres</t>
+          <t>Galle</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>216 g</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>46,67. kr/l</t>
+          <t>162,04. kr/kg</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>35</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>79.95.</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1029898</t>
+          <t>1032085</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0cb0ee171ad636d1c94ec865e2231b92%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe74a7c2484a55c6defbb9b89668a2537%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2fc150ba37f59650bf53c134b8d2f776&amp;w=352&amp;s=70dde4784420caff7f91cc5c7c64422d</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F116e67cc629b323cd29f76c4fbfca3d8%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F97c2908d0bf51f22c5ca8c714d40bb3b&amp;w=552&amp;s=7eae88cca9948b0da4d2d01d5df75e21</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>c63838c76b946e9c</t>
+          <t>8dc06e2f1323373b</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -835,7 +831,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -847,41 +843,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Faxe Kondi eller Pepsi Max, Heineken eller Royal</t>
+          <t>Sun Lolly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Faxe</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18-24 x 33 cl</t>
+          <t>8 x 60 ml</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>12,63 kr/l</t>
+          <t>25,00. kr/l</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1029593</t>
+          <t>1032384</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F32180118573cc5f124abc6b60a85dd72&amp;w=552&amp;s=1adfecda5a3536e1054ad4c5deade690</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F26ac34945e6f531473bcc493c5e39668&amp;w=552&amp;s=d334c7ddd88e8fdc6b78fd71dcafae3f</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>cf333964346665c6</t>
+          <t>ce619e6493cd3c64</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -903,41 +899,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Marabou chokoladeplade</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Marabou</t>
+          <t>Philadelphia</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>160 g</t>
+          <t>200 g</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>125,00. kr/kg</t>
+          <t>50,00. kr/kg</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1029899</t>
+          <t>1032291</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff629fa0ff6869b9644338eece1537878%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fee4746530f77d0b4fd97930dc2c6ce94%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3a3d46a9aa4428fa2daa979cbba94a30%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9fde3520832369d8d04844afb9175aab%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc303721b7f070452d2326e1f3e145b81&amp;w=552&amp;s=41ee7a82603b6fe4e5c3ce43fbea0e06</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4648892302e28d7d9c3bd36e94e76cf4%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F282b8aff0378a8596ce4a27d000549a9%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa37c3df7e11810e59a8a297e7a49a3bf%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa29ed878b1b925f4855724c910c71991%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F510d7b3418e67325c1aab8f84efaf37c&amp;w=552&amp;s=8b865da0772c5428404b44d593db33a2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>94be6941feae9111</t>
+          <t>d4e92b126e8790f9</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -947,7 +943,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1 plade</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -959,22 +955,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Den Grønne Slagter pålæg eller kalkunbacon</t>
+          <t>Coop burgerboller</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Den</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>70-100 g</t>
+          <t>300-330 g</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>171,43. kr/kg</t>
+          <t>40,00. kr/kg</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -983,17 +979,17 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1029606</t>
+          <t>1032093</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbb7ecd861698e66b5aaafe7526ffe3f1&amp;w=552&amp;s=f4010131ab2c057ca8d04059fd5aab38</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5408c7dbfb4dde8afb8d9f6e816ad4e0&amp;w=552&amp;s=96c392b51c18abfd0f4283b717b95f03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>c0b476433d6d6da8</t>
+          <t>957a6a813a37b5c8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1015,41 +1011,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rossini laks eller Diskobay kutterrejer</t>
+          <t>Graasten dressinger</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rossini</t>
+          <t>Graasten</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>90-230 g</t>
+          <t>375-425 g</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>433,33. kr/kg</t>
+          <t>32,00. kr/kg</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1029602</t>
+          <t>1032090</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3ea20a6e990b67218a0d43578f25fc3b&amp;w=265&amp;s=1244bd9b2d5c803722d9ebc95cec8cbd</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb1169cf32f65c7c49fc4fa5628fd6c6c%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F163bc4e29a2644b6019efa77990b5323%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8de6913c710dcdf25847060318763b01%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F596c3631d568b36b0209278e606a7931&amp;w=552&amp;s=572d88737211a9412fee1a643995b908</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>dcaa6645632d4a5d</t>
+          <t>f0554264396eb5ba</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1071,41 +1067,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Glyngøre fersk laksefilet</t>
+          <t>Irma Vitendo tomater</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Glyngøre</t>
+          <t>Irma</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>600 g</t>
+          <t>. 400 g</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>141,67. kr/kg</t>
+          <t>50,00. kr/kg</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1029605</t>
+          <t>1032091</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa8e7464033f4796eae9f82f8dba619cf&amp;w=552&amp;s=ed079415cd2b66a6ade178d156d718d0</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2bc0716167daac2816f3ce2aa89c64a5&amp;w=252&amp;s=fff6ba06abce3a6f09da6e8b33e486a7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>c7386cc1c39393c7</t>
+          <t>923c936dc66393c3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1115,7 +1111,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 bakke</t>
         </is>
       </c>
     </row>
@@ -1127,41 +1123,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>K-Salat pålægssalat</t>
+          <t>Dragonfly, Refsvindinge, Thy eller Ørbæk øl</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>K-Salat</t>
+          <t>Dragonfly,</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>100-150 g</t>
+          <t>44-50 cl</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>100,00. kr/kg</t>
+          <t>34,09 kr/l</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1029598</t>
+          <t>1032089</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2e9115f63d2ead49c69a6d0e6f851d71%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2ac00a74036ca78a571efa77ef6ca211%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3f861489ecce6f716046e15da2882b63%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fabb69b07d0c729f523279246f59e1b38%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff40df4eaeed63dbb309d7fbbd9efca2e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbc56740eb8d4466069b508165fc877d7%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa5189fbf9a7033faa428270ee9f325a2%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdb36da7b2d2601822c7e4bf771d84ee0%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F54861f54f187ee0d7497b4fa5bc1a200&amp;w=1152&amp;s=8f0368a5ae3ce7ad6e58cf0096a6e218</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8c3e62c6e9455af0c9d333cd611d866c&amp;w=252&amp;s=216f0f2f242a1443b99781a9f4102502</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>94aa2b40ffff808a</t>
+          <t>9a6d6cb39a98654c</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1171,7 +1167,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 flaske/dåse</t>
         </is>
       </c>
     </row>
@@ -1183,41 +1179,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Coop skrabeæg</t>
+          <t>Entrecote eller ribeye</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Coop</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>8 stk</t>
-        </is>
-      </c>
+          <t>Entrecote</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1,88. kr/stk</t>
+          <t>247,50. kr/kg</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1029611</t>
+          <t>1032097</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa0a653de890e07341e03b7f12d5a584d&amp;w=552&amp;s=3ed15638e96adb9205d08f8582ff0071</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4bc6149d4d46d157b1239fd3e411f572&amp;w=552&amp;s=3dd5211c799439674217d384ee7d8ec2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>c1e1161eea9d95e2</t>
+          <t>c0b769c936356dc8</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1225,11 +1217,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>1 bakke</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1239,41 +1227,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Arla proteindrik eller Starbucks triple</t>
+          <t>Irma økologiske pølser</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Arla</t>
+          <t>Irma</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>500 g</t>
+          <t>240-280 g</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>24,00 kr/kg</t>
+          <t>145,83. kr/kg</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1029615</t>
+          <t>1032095</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F55045360cd8dffb72cf77b19267c389e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8bacece6b3faa9f1944d6fcde120a3df%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb0fb1bfdeec351fb0e3db86944bf961c%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F87885f3473d8708091f4bb308ff2b716%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F21690743d38db353db8a071b61cbbf99&amp;w=552&amp;s=f8627156885e378faad28cbd2d8486fd</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0a1ec9c4a8d34d05979333d846b11209&amp;w=229&amp;s=fa48c4c87d6e1829b845313d7870558e</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>85e8cc93c5cc3c3b</t>
+          <t>80c31b405fffe70c</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1283,7 +1271,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -1295,41 +1283,41 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Thise dansk økologisk græsk inspireret yoghurt</t>
+          <t>Kyllingebryst med lage eller kyllingebryst med bbq</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thise</t>
+          <t>Kyllingebryst</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1 kg</t>
+          <t>700-800 g</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>26,00. kr/kg</t>
+          <t>78,57. kr/kg</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1029613</t>
+          <t>1032101</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F970e78c5d9f49769ae68e15daec3d4c2&amp;w=211&amp;s=ac92bfff3bc8eaf0df8709ae7c364ed5</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fac1597701a09a1a652c56580eaa40566%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8b37daf8252679a94b7f7c1b55419573&amp;w=252&amp;s=dbee14fcd68ba5927ff16ba930a4acfe</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>d0b56a7a3f070371</t>
+          <t>957e46a0e4c713e3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1339,7 +1327,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -1351,39 +1339,41 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Udvalgt alkoholfri spiritus, vin og øl</t>
+          <t>Coop hel ovnklar flæske-steg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Udvalgt</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>33 - 75 cl</t>
+          <t>4000-5000 g</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>171,38 kr/l</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>47,25. kr/kg</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>189</v>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1029621</t>
+          <t>1032099</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F41e93964a6ad113e7fa9ebb334aafd6b&amp;w=1152&amp;s=f4346488cc1273a9b4741442685f28f8</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fce4ebfbc392bec7c7e98b0842ee207fa&amp;w=252&amp;s=beff629dbfaaaf210ce38305027a4752</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>cf6538b23c923996</t>
+          <t>999b6d6d3092326d</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1391,7 +1381,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1 stk.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1401,7 +1395,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Coop grønne asparges</t>
+          <t>Coop grøntsager</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1411,31 +1405,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>500 g</t>
+          <t>. 200-900 g</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>50,00. kr/kg</t>
+          <t>60,00. kr/kg</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1029627</t>
+          <t>1032103</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb62502b133cbdbe648ed886ba441cd4d&amp;w=100&amp;s=4d3c463933b688d319bf96e42c0110e4</t>
+          <t>https://d3qnoxvhi29qvt.cloudfront.net/feed-images/c8f6be75e53a76a3d39f8e1c91ca081f</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>956a3ab0097f562d</t>
+          <t>aac4d15ac72db42b</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1445,7 +1439,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1 bundt</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -1457,41 +1451,41 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Coop formodne avocado</t>
+          <t>Royal Classic eller Pilsner, Odense Classic, Faxe Kondi Booster, Pepsi Max eller Faxe Kondi</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Royal</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6 stk</t>
+          <t>8 x 50 cl</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5,83. kr/stk</t>
+          <t>19,75 kr/l</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1029629</t>
+          <t>1054526</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1bf77ef94fcd08f8f1e407188e0390be&amp;w=200&amp;s=291a181d8c41e546339675c45f3e3395</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Facb4c8dde2b79a1808cecd42a2ea848f&amp;w=552&amp;s=f51c86cc24fcfcc702c52b3df5cc9904</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>d1cf5d6330364699</t>
+          <t>9a6c39c7633331cc</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1501,7 +1495,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1 bakke</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -1513,41 +1507,41 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Taffel chips</t>
+          <t>1664, Breezer, Somersby eller Red Bull</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Taffel</t>
+          <t>1664,</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>160-175 g</t>
+          <t>25-33 cl</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>75,00. kr/kg</t>
+          <t>44,00 kr/l</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1029631</t>
+          <t>1054528</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F77c0651bc2beb0ee9e23dcfa1f2f532a%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff1598661a1805d026cd4aa922abadc22%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4e8566ee084f6dd927f46d8e6f36f5d2%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7f868dd85e664f092ddbec3b14d8058c%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F679dbe358f4ac63700ae38e9418dc450&amp;w=552&amp;s=4224fa2e8923b82b4c50fa6558a12734</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9ffa4616cbde482352c31be10bf06a16&amp;w=552&amp;s=ff1741e2fec4892faf898888156aa68d</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>91ec6e13e92c92ec</t>
+          <t>942f6ad03a953dc5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1557,7 +1551,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1 pose</t>
+          <t>1 dåse/flaske</t>
         </is>
       </c>
     </row>
@@ -1569,41 +1563,41 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bonduelle majs eller kikærter</t>
+          <t>Ben &amp; Jerry´s is</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bonduelle</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>390-420 g</t>
+          <t>465 ml</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>38,46. kr/kg</t>
+          <t>83,87. kr/l</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1029635</t>
+          <t>1054527</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faf60b50696cae2a00ac66f9dcfaa5cd1%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffc4b402c79ade33d4a1a252737d3fb73&amp;w=552&amp;s=106c06a763ae520b89de06669dea0e80</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F243aad5da6534e9b2317a532184cea34%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb89a47c60c36f53a78edd0ba5ee5c769%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fee9b9b0fc33110e6c08f019845295cf8&amp;w=552&amp;s=4db025c768ff848b4ae85c8de1670be3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>d8e56d11a6ba98c5</t>
+          <t>f80e07f15aa0b79c</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1613,7 +1607,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -1625,41 +1619,41 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kellogg's morgenmad</t>
+          <t>Gøl pølser</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kellogg's</t>
+          <t>Gøl</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>330-375 g</t>
+          <t>630-750 g</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>75,76. kr/kg</t>
+          <t>71,43. kr/kg</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1029638</t>
+          <t>1054530</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F43ce7dfd5c1ab8ec7dc0554219cfea9e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb6c7d705e51ac80fcefe116354d6b080%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb4ea73572417b14481a146c9c0085a22&amp;w=252&amp;s=4f81363f131db24cbbab6fb06b837eb9</t>
+          <t>https://d3qnoxvhi29qvt.cloudfront.net/feed-images/ff01024581c5c2993cc736e3d4da21a3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>d3e42e0b3918bc6d</t>
+          <t>beb689596a26d249</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1681,41 +1675,41 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Toffifee, Werthers eller Riesen</t>
+          <t>Citterio bresaola, mortadella, prosciutto cotto, salame di milano eller prosciutto crudo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Toffifee,</t>
+          <t>Citterio</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>125-135 g</t>
+          <t>70-125 g</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>152,00. kr/kg</t>
+          <t>257,14. kr/kg</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1029640</t>
+          <t>1054529</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9c49cbbe5c7072510c95ff30c685a6b2&amp;w=252&amp;s=7bd23a3162331238d4c62737302d5242</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1750b3ebeee32d1bc4ec174f419b610b&amp;w=552&amp;s=eaae50c1fce2120b7b8034a265c87c03</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>e6a419eb19573cd0</t>
+          <t>9b6c6c2c2193ce9b</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1723,11 +1717,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>1 pakke/pose</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1737,41 +1727,41 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Coop dansk kyllingover-, underlår eller lårfilet uden skind</t>
+          <t>Hele kyllingelår eller hakket gris/kalv 8-12%</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Hele</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>400-800 g</t>
+          <t>900-2000 g</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>62,50. kr/kg</t>
+          <t>76,67. kr/kg</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1029647</t>
+          <t>1054531</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F03e265243dfb0c41b08939f12bb51067%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fece59c63f585a8c8ed4a1c45a7e85e59%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F673f5a06081d68c9cf56544f30ab9043&amp;w=552&amp;s=e88faf704beffb41418fae7cdfa3f97a</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fee676c65ae0717e6ae0435ec8cfff083&amp;w=258&amp;s=80dbe8e70abe46d4fb4cb780a055fa1c</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>91f85e1d86708dc7</t>
+          <t>858e27d3e08f6dd0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1779,11 +1769,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>1 pakke</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1793,41 +1779,41 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kærgården smørbar</t>
+          <t>Malaco, snøre eller stjerner</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kærgården</t>
+          <t>Malaco,</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>200 g</t>
+          <t>. 92-120 g</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>70,00. kr/kg</t>
+          <t>108,70. kr/kg</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1029645</t>
+          <t>1032105</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F331c5dbfa3587a30455f9ece1e4d0055%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc7fbedff0b74491f28e049ff1536ae24&amp;w=552&amp;s=41971c304a92e91a9270b8aeca25eabf</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0ff84dc7b20664488e6c69acefa03762&amp;w=552&amp;s=ff386998daab1dd328cf7bf1a57d542b</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>9966556e6c6a9998</t>
+          <t>d2ad435a2d5f7c20</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1837,7 +1823,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -1849,41 +1835,41 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Yoggi yoghurt</t>
+          <t>Knorr sauce eller fond du chef</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yoggi</t>
+          <t>Knorr</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1 kg</t>
+          <t>57-112 g</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12,00. kr/l</t>
+          <t>175,44. kr/kg</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1029650</t>
+          <t>1032108</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd33f05fd7d0853ea60d0a7bb4c856363%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F74223075c39446fee36dbcbee0f4516e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa12f4e1a92d5b1a215ee0d3b3aaf95ff&amp;w=552&amp;s=4ae4dbb9f999b1a759eaf675c3fe503d</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F615057e95c90d626c42c121ef753c801&amp;w=552&amp;s=0160edda5cab3136112a74627abe4b80</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>923c6c65336d6c65</t>
+          <t>96646d336f66360c</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1893,7 +1879,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -1905,41 +1891,41 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Royal Classic eller Pilsner, Odense Classic, Faxe Kondi Booster, Pepsi Max eller Faxe Kondi</t>
+          <t>Rahbek indbagt fisk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Royal</t>
+          <t>Rahbek</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8 x 50 cl</t>
+          <t>250 g</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>19,75 kr/l</t>
+          <t>44,25. kr/kg</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1053684</t>
+          <t>1032110</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=602&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5563bc7d6d6a7308a8ecb94995fe01d7&amp;w=552&amp;s=daa7702881590cfaa35cec3d9ef2bd97</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faef4c42a7897699f9634745451dc59a6%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4d5bfb2dd3c414311378a0dbbfb0b06a%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F00eb240608d79189922355ef0e7279cd&amp;w=552&amp;s=105a05290bb92aba6d17bbf2f03240c1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>854a3db172b54ec5</t>
+          <t>9f75109a6d4ce5e0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1961,41 +1947,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1664, Breezer, Somersby eller Red Bull</t>
+          <t>Coop danske skoleagurker</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1664,</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>25-33 cl</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>44,00 kr/l</t>
-        </is>
-      </c>
+          <t>3 stk</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1053685</t>
+          <t>1032112</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F469b9ee2fc585bc3aa66e4d3133cee77&amp;w=552&amp;s=7583ac258f567cb14dd3ebd57d741350</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9b301dadd46b99338d2852ef294848cc&amp;w=233&amp;s=d20647e8f104411b7f16b4aca42a5759</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>942f6ad03a953dc5</t>
+          <t>8b86f4a05f9a413f</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2005,7 +1987,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1 dåse/flaske</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -2017,41 +1999,41 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ben &amp; Jerry´s is</t>
+          <t>Defco pålæg</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>Defco</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>465 ml</t>
+          <t>80 g</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>83,87. kr/l</t>
+          <t>125,00. kr/kg</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1053683</t>
+          <t>1032114</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F243aad5da6534e9b2317a532184cea34%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb89a47c60c36f53a78edd0ba5ee5c769%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fee9b9b0fc33110e6c08f019845295cf8&amp;w=252&amp;s=c9d43e95f2d7074a2164c22f4996d150</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2378f56cdfb3b3eafc90f12e6bae2869&amp;w=190&amp;s=21979c6861fb3986c69eb6b570da0b19</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>c4772a88a53fe6e0</t>
+          <t>d2f652de09c0e9d8</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2061,7 +2043,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -2073,41 +2055,41 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gøl pølser</t>
+          <t>Castello dessertost eller krans</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Gøl</t>
+          <t>Castello</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>630-750 g</t>
+          <t>. 125-200 g</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>71,43. kr/kg</t>
+          <t>160,00. kr/kg</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1053680</t>
+          <t>1032121</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faaa9236c5b20d31130ff320b6c6d7311&amp;w=252&amp;s=a25af654d8849380b15e39926bbe2f92</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe3d58c1bf2e4dc61803b65e3ca5a2789&amp;w=552&amp;s=0eddeb212af9dab846c062f91c04effb</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>a862579f2ad0ec2e</t>
+          <t>cf72613c8c6639c6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2117,7 +2099,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -2129,41 +2111,41 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Citterio bresaola, mortadella, prosciutto cotto, salame di milano eller prosciutto crudo</t>
+          <t>Steff Houlberg bacon</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Citterio</t>
+          <t>Steff</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>70-125 g</t>
+          <t>2 x 100 g</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>257,14. kr/kg</t>
+          <t>100,00. kr/kg</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1053682</t>
+          <t>1032119</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6ffa2917619de5d87ffabb34333ee025&amp;w=552&amp;s=d105a0941a0be240b96e848b823c9993</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fba09fb385fdbdc8a69851abb8d735fcc&amp;w=552&amp;s=787462b9669daae1223ee376c52f616c</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>9b6c6c2c2193ce9b</t>
+          <t>9b93666764989966</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2171,7 +2153,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1 pakke</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2181,41 +2167,41 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hele kyllingelår eller hakket gris/kalv 8-12%</t>
+          <t>Coop Italiana eller Deep pan pizza</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hele</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>900-2000 g</t>
+          <t>. 300-435 g</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>76,67. kr/kg</t>
+          <t>66,67. kr/kg</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1053681</t>
+          <t>1032117</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc899b15adc91aeeeecb0ca986efb42b2&amp;w=258&amp;s=0033b2705ebd6c520822ad34ead3f4f4</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7e14e0f0e947c5fac887d7c6e2448363&amp;w=1152&amp;s=d41c33c345c626f0d2829e657ba41b9a</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>858e27d3e08f6dd0</t>
+          <t>8731662e33c7333a</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2223,7 +2209,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1 stk.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2233,35 +2223,43 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ølands, græskar-solsikke eller spelt-chia surdejsbrød*</t>
+          <t>Änglamark økologiske bananer</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ølands,</t>
+          <t>Änglamark</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1 stk</t>
+          <t>. 1,3 kg</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>35,00. kr/stk</t>
+          <t>15,38. kr/kg</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1029658</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>1032127</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F96eb11229954b017af38fcdf24b06e09&amp;w=552&amp;s=f56bdbac4c4b4eb359e396dd1b100802</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>d4723a926b0d6d2d</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -2269,7 +2267,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -2281,35 +2279,43 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tebolle*</t>
+          <t>Coop hakket grisekød 4-7% eller 8-12%</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tebolle*</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1 stk</t>
+          <t>400-500 g</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>4,00. kr/stk</t>
+          <t>62,50. kr/kg</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1029652</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>1032123</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4968afec4802c5f16a5128031f9ed672%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fae49081e9f4046821eceb0db64c5f31f&amp;w=552&amp;s=b1989cfe3632215dcae547639ce4251b</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>af1158f0581f652f</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -2317,7 +2323,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -2329,35 +2335,43 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Onsdagssnegl*</t>
+          <t>Cheasy hytteost</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Onsdagssnegl*</t>
+          <t>Cheasy</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1 stk</t>
+          <t>500 g</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>10,00. kr/stk</t>
+          <t>40,00. kr/kg</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1029656</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>1032125</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4b0db11fd1f4040d73e61f11b40948de&amp;w=552&amp;s=dcc9281c22c88713778bf5aebcb953c4</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>cb93cc8433666e39</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -2377,37 +2391,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dansk Kalv culotte eller tyndsteg</t>
+          <t>Alt urtekram</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dansk</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Alt</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>190,00. kr/kg</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>95</v>
-      </c>
+          <t>247,91 kr/kg</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1029686</t>
+          <t>1032128</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd141853019fbfa5bc3064555d0e193f0&amp;w=552&amp;s=64a5ffefbaf01698e1b4d667eed714a1</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe3d170f12a5cb831fb7fcc717a79db99&amp;w=1152&amp;s=30aed8eb850eba15f401e02312e18630</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>95f06a2f36d087c5</t>
+          <t>cf9c29ce234d2699</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2425,41 +2441,41 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tulip spareribs eller pulled pork</t>
+          <t>Irma is</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tulip</t>
+          <t>Irma</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>900 g</t>
+          <t>. 700 ml</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>76,67. kr/kg</t>
+          <t>64,29. kr/l</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1029689</t>
+          <t>1054532</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F01e4d102858a16e25ebedfd927108040%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb8705c2bb3312c970f664899d0b0787a&amp;w=552&amp;s=17ae9554fe8760fc78e616ffb033a119</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5bd3415daec45be286d3e4de97ecb494&amp;w=1152&amp;s=fae36a1f5bd752fb51f8c26256a459bd</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>936392966d98db98</t>
+          <t>9eb4793929696cc1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2467,11 +2483,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>1 pakke</t>
-        </is>
-      </c>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2481,41 +2493,41 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bähcke mayo*</t>
+          <t>Änglamark formalet eller hele kaffebønner</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bähcke</t>
+          <t>Änglamark</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>255 g</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>54,90. kr/kg</t>
+          <t>147,50. kr/kg</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1029684</t>
+          <t>1032132</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F05f4cc6b45195fbbee78562e713426a6%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa3d26966107456213d48db8d273b18a8%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2b84a034c4d0367710433ce10e03ce18&amp;w=552&amp;s=96a759f0f62390321895d4b323e5f22f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdfc40f7ced7e3228689b78741ff889cb&amp;w=552&amp;s=71679ba820ff9ba3ac31fbe5967b00f6</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>ad5170160bd69dad</t>
+          <t>c0e12fce2b8ff01a</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2525,7 +2537,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -2537,41 +2549,41 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Coop entrecote</t>
+          <t>Cirkel Kaffe eller Änglamark økologiske kaffekapsler</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Cirkel</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4 stk</t>
+          <t>10 stk</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>198,57. kr/kg</t>
+          <t>2,00. kr/stk</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1029691</t>
+          <t>1032135</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F405f1aa9518e28c9071e2bc370b953de&amp;w=552&amp;s=e96b89144d9ac0fcf844b0228b5cdda5</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc433d822e198cb92b1b8b1e849a33e6a&amp;w=213&amp;s=82730b6bf6358cacf6d8688f6e0b628f</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>94906b961a6dcf99</t>
+          <t>b32a52916c6cdb93</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2581,7 +2593,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>4 stk./ 700 g</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -2593,31 +2605,43 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Grillmarked</t>
+          <t>Cirkel Kaffe hele kaffebønner</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Grillmarked</t>
+          <t>Cirkel</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>7 stk</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+          <t>850-900 g</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>151,76. kr/kg</t>
+        </is>
+      </c>
       <c r="F40" t="n">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1029696</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>1032137</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F08e9b31c296ab716d9bd4c868e727632&amp;w=552&amp;s=e2041177b80427436ce83544791839b1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>999366cf3119ce98</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -2625,7 +2649,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>7 stk.</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -2637,22 +2661,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Steff Houlberg pølser</t>
+          <t>Irma løs eller brevte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Steff</t>
+          <t>Irma</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>300-400 g</t>
+          <t>200 g</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>96,67. kr/kg</t>
+          <t>125,00 kr/kg</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -2661,17 +2685,17 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1029693</t>
+          <t>1032130</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fda044d16882e56e3a617424101459b08%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd373c447bd6e57acd305eb26b03b59e5%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F17e2413ff72b525620bf472cdeca7cf8&amp;w=252&amp;s=0e8876ec727e87eb91039cc7cd915b2f</t>
+          <t>https://d3qnoxvhi29qvt.cloudfront.net/feed-images/19cbd31f54205d2f06a9668e3f74bcce</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>91d9796026366f69</t>
+          <t>aa87f15b0aa5b586</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2681,7 +2705,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 pose/æske</t>
         </is>
       </c>
     </row>
@@ -2693,41 +2717,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kohberg fastfoodbrød eller madbrød</t>
+          <t>Spar op til 25% på udebelysning*</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kohberg</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>240-360 g</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>75,00. kr/kg</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>18</v>
-      </c>
+          <t>Spar</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1029697</t>
+          <t>1032141</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd6edbbbc54c99dbf272c817cac4a8fc9%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd511ce97b98ecd596c2444a1d0614b01%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F084d0a1e5855b32a45c45692bd7acc1e&amp;w=252&amp;s=fad7f7d003e4728807321e524b8d614c</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0eb3105543009e7aa57a594b34d8f24b&amp;w=552&amp;s=44e2729b1c5b2757f402e8ee3dc0ff5b</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>c0df75c12b052f6a</t>
+          <t>9264e5d21e6369e3</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2735,11 +2749,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>1 pakke</t>
-        </is>
-      </c>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2749,43 +2759,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Courget</t>
+          <t>Nordicgrill Engangsgrill*</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Courget</t>
+          <t>Nordicgrill</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1 stk</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>6,00. kr/stk</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>6</v>
-      </c>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1029687</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9a20dd71fa9720adf8fa2389d9a028c7&amp;w=1152&amp;s=45e51cd1031133574cd97d5352790d90</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>95b536351f250f25</t>
-        </is>
-      </c>
+          <t>1032145</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -2805,37 +2801,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Coop roastbeef</t>
+          <t>Nature 9 kg Grillbriketter*</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Coop</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>160,00. kr/kg</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>80</v>
-      </c>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>9 kg</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1029703</t>
+          <t>1032144</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=694&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3126d187daca1bf8f769a425437d6f68&amp;w=463&amp;s=c00186f3074194a6c175e6021f89843f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffb2c08ac9827fe258ddf71ada9563b92&amp;w=252&amp;s=ffbca122b5362c63a5cccf2044f55d22</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>9ab2459d7549749c</t>
+          <t>9e9b79c661666134</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2843,7 +2837,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1 pose</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2853,41 +2851,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Coop hakket gris 8-12% eller medister</t>
+          <t>Køletasker i pastelfarver*</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Køletasker</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1000 g</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>55,00. kr/kg</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>55</v>
-      </c>
+          <t>2 x 200 ml</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1029716</t>
+          <t>1032147</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5a8a5c0225dd437e4c3247f11eaf83df&amp;w=552&amp;s=b8388b4ad5cc0c20ba48749f60b89b5c</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F04e0d9789524afd0574b522fbe3e172f&amp;w=252&amp;s=ec47208b3408effa6e8f601f9015744d</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>d1c96e1ab564d2c9</t>
+          <t>c5e47ab2620f3cc9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2895,11 +2887,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>1 pakke</t>
-        </is>
-      </c>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2909,37 +2897,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Coop marineret lammekølle</t>
+          <t>Sistema Klip It opbevaringsbokse 10-pak*</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Coop</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>140,00. kr/kg</t>
-        </is>
-      </c>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1 x 2 l</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1043652</t>
+          <t>1032153</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc73c383dc4469ea810a7b20e9a174e32&amp;w=198&amp;s=190c37f0d30b0c41a12dc66614b56b4d</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F42ef74b689e2a4c79c26695f6a117550&amp;w=552&amp;s=df5b1854abb25c87a9e23e4afa6b67c3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>92a56c9a4d661e6b</t>
+          <t>c1bc3a536e48bd61</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2947,7 +2935,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1 sæt</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2957,41 +2949,37 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PremiuM oksemedaljon, tykstegsbøffer eller peberbøffer</t>
+          <t>Hybrid pande*</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PremiuM</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2 stk</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>214,29. kr/kg</t>
-        </is>
-      </c>
+          <t>. 1 stk</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1043653</t>
+          <t>1032156</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe1b61fac8578e1940c38a10e7ff68c20&amp;w=252&amp;s=8fff20eac6976b33e7f7a7fdaa907723</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe6cc84625d18d512e4ff3cf55792b49b&amp;w=252&amp;s=1fd12a8d4072b521b5896caf93686b8b</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>c69d685a1b6e12b5</t>
+          <t>cc9339386ecf3138</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3001,7 +2989,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2 stk./350 g</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -3013,41 +3001,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Glyngøre fiske- eller laksefars</t>
+          <t>Fleecetæppe*</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Glyngøre</t>
+          <t>Fleecetæppe*</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>400 g</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>80,00. kr/kg</t>
-        </is>
-      </c>
+          <t>. 1 stk</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1029713</t>
+          <t>1032154</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6c8366b4a328b24179f6ee2264fca46d%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9a31bb49815e5b84bc10a4fae9cabf60&amp;w=252&amp;s=ddc38315a0be8b429101ba0f792ae02f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9eb8984327ccec53515e53be15a706b3&amp;w=252&amp;s=fad67d9446d51c2b3f16bc4db8fecab7</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>c0784f376ce067b2</t>
+          <t>c50f7a6424b333d5</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3057,7 +3041,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3053,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BORNHOLMERGRISEN dansk krogmodnet flæskesteg</t>
+          <t>BORNHOLMERGRISEN krogmodnet nakkefilet</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3080,26 +3064,26 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>150,00. kr/kg</t>
+          <t>140,00. kr/kg</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1029699</t>
+          <t>1032163</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F69b78b72f35694e262060a58440ffc2d&amp;w=552&amp;s=0fe9f3a99782f49cf33fb490d235b418</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff20560f15884d35728d7e1bd1d358381&amp;w=552&amp;s=8c44b8891d08222a59887a45a748dab6</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>c36165c39b3c9a2d</t>
+          <t>9b66676766990c4c</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3117,7 +3101,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BORNHOLMERGRISEN krogmodnet skaftkotelet</t>
+          <t>BORNHOLMERGRISEN filet a la mørbrad med paprika og hvidløg</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3125,14 +3109,10 @@
           <t>BORNHOLMERGRISEN</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>1 stk</t>
-        </is>
-      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>217,78. kr/kg</t>
+          <t>98,00. kr/kg</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -3141,17 +3121,17 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1029701</t>
+          <t>1032161</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2be3e5030b5400b3eeaf3ad3134bf9de&amp;w=552&amp;s=72aa7fa345b88f2e349aebe5e0628e3f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb95e3014a5fd89fd3eb4621a127c921c&amp;w=552&amp;s=e6d922461c1d3c8e6cc164eacb7d2f86</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>c973636c369c1927</t>
+          <t>96c3696178c36f34</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3159,11 +3139,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>1 stk./ 225 g</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3173,41 +3149,37 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Frijsenborg hel kylling, hel kylling cook in bag med salt/peber eller kyllingefilet</t>
+          <t>Dansk Kalv mørbrad</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Frijsenborg</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>550-1350 g</t>
-        </is>
-      </c>
+          <t>Dansk</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>136,36. kr/kg</t>
+          <t>358,00. kr/kg</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>75</v>
+        <v>179</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1029707</t>
+          <t>1032157</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6ab32719344e9295565781931d31e181&amp;w=552&amp;s=b11d859586f05832d8503c7f17db2495</t>
+          <t>https://d3qnoxvhi29qvt.cloudfront.net/feed-images/e2c89ea932a9eac03262a5a72afc3d5d</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>9638e3c7389c4cd3</t>
+          <t>98bffc500fe0d00f</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3215,11 +3187,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>1 stk.</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3229,41 +3197,37 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Frijsenborg kyllingemarked</t>
+          <t>Krogmodnet ribbensteg</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Frijsenborg</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>260-700 g</t>
-        </is>
-      </c>
+          <t>Krogmodnet</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>134,62. kr/kg</t>
+          <t>150,00. kr/kg</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1029710</t>
+          <t>1032159</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4fa9fea1919aca6331ad3949f3767d07&amp;w=552&amp;s=07bc987e5fd24065af12c5d7e7963005</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9850a31a5d0d7ca3ccc56177109a7418&amp;w=395&amp;s=a3ccb53f16f84e7fa9391a9a7ee00bdc</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>c69661d31c6d39cc</t>
+          <t>d2c32dbd4c6d98c2</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3271,11 +3235,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>1 pakke</t>
-        </is>
-      </c>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3285,41 +3245,37 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fredagsbøf</t>
+          <t>PremiuM oksecuvette</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fredagsbøf</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>. Kg</t>
-        </is>
-      </c>
+          <t>PremiuM</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>300,00. kr/kg</t>
+          <t>158,00. kr/kg</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1029705</t>
+          <t>1048620</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4d2dca12a3e51b21091a08f4bb851afd&amp;w=352&amp;s=f70b30137caab43778eecbb6c03403f3</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa1c4dff93357541e0f67e53aba679aa3&amp;w=210&amp;s=1714ee1f6f3c67fb73292c2b2aede37b</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>96996465cb96cc99</t>
+          <t>9efa48a3258667cc</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3337,41 +3293,37 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Delikatessens fredagstapas</t>
+          <t>PremiuM roastbeef, steak, tern eller strimler</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Delikatessens</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>1 stk</t>
-        </is>
-      </c>
+          <t>PremiuM</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>165,00. kr/stk</t>
+          <t>160,00. kr/kg</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1029723</t>
+          <t>1048621</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbdc1e74d1b1528dd02e310d6407f5658&amp;w=352&amp;s=fb1dfda7f00a54e0193b94d36c71a2ac</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdd27881b98a739d1bbff9d58d81036f6&amp;w=232&amp;s=005ee6a2c21511acdbed7485c3593cb5</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>cecc6439319b6366</t>
+          <t>c0d23b6d29653de4</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3379,11 +3331,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>1 stk.</t>
-        </is>
-      </c>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3393,39 +3341,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Lun lørdag</t>
+          <t>Grillmarked</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lun</t>
+          <t>Grillmarked</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>25,00. kr/stk</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>25</v>
-      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1043655</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5dbc43a8e9081461eef2d5616d063af4%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F76ee9a77a1cd739755738f55a5ba8b73%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4652c5cb9a2be83438923e6f594a9625%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbe870c8b34387a44fdea778b10933afd&amp;w=352&amp;s=49a6c0c7f1b594deba469886a48543ae</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>979939873871073d</t>
-        </is>
-      </c>
+          <t>1032169</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -3441,41 +3375,41 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Delikatessens frokostplatte</t>
+          <t>Irma iberico presa, secreto eller kotelet med ben</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Delikatessens</t>
+          <t>Irma</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1 stk</t>
+          <t>180-200 g</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>85,00. kr/stk</t>
+          <t>327,78. kr/kg</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1029718</t>
+          <t>1032165</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F22a954819f2a8c60555ead8d0ab30828&amp;w=352&amp;s=566de43ccf659b15148674238643585f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7675d32f80c3e21d968c42ec5dc4ca94&amp;w=488&amp;s=2b424b37c2fac28b2e8dd53be733db4e</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>d0a14f5f739f2308</t>
+          <t>c1f41e6b6b3e4388</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3485,7 +3419,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -3497,41 +3431,37 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Stjernekaster</t>
+          <t>Irma nyretapper af kødkvæg</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Stjernekaster</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>1 stk</t>
-        </is>
-      </c>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>45,00. kr/stk</t>
+          <t>218,00. kr/kg</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1029722</t>
+          <t>1032171</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5dfa6d3ea69e4bd48e58b38521b1c21f&amp;w=352&amp;s=31d16122c838d3be0e9fb13edea5222b</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F883306a46be3bd8725b5fc628d39bb7a&amp;w=466&amp;s=9ac0d688dc55d730631a6faa158c32f5</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>91c94e8c6d333cd6</t>
+          <t>c5b11e6c718719e3</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3539,11 +3469,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>1 stk.</t>
-        </is>
-      </c>
+      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3553,41 +3479,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Charcuteri fra middelhavet</t>
+          <t>Spar 15% på Irma lam</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charcuteri</t>
+          <t>Spar</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>140 g</t>
+          <t>. Kg</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>357,14. kr/kg</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>50</v>
-      </c>
+          <t>509,92. kr/kg</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1043654</t>
+          <t>1048619</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2a1aa439c8b1d240e42a081668886549%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffa624c9b132cbbc117a79cffcf74f6fb%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2cdabc0c110103cc1119aadb329054fb&amp;w=352&amp;s=3fdfcb32154143c237ee90cdb60a75cc</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9270877f3e9145817dee2d1cc099db6a&amp;w=1152&amp;s=6c9701d8c81e0756a6f711c4919cc6f1</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>d2e621196c039bfe</t>
+          <t>936767141b669693</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3595,11 +3519,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>1 pakker</t>
-        </is>
-      </c>
+      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3609,41 +3529,41 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Coop royal gala æbler</t>
+          <t>Frijsenborg hakket kylling</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Frijsenborg</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>8 stk</t>
+          <t>800 g</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1,50. kr/stk</t>
+          <t>68,75. kr/kg</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1029731</t>
+          <t>1032185</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6f0ce27daae4a74fbf8ec8aba4a3e6aa&amp;w=752&amp;s=fae09b0af41847dad59c34e513e63f00</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F11a796057a5696071c71ca393916e5ca&amp;w=1152&amp;s=9937b4d702c86765c35b1fc0e0120902</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>c59a3396786ccc36</t>
+          <t>c7c365c731c6193c</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3653,7 +3573,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>1 bakke</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -3665,41 +3585,41 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Økologiske danske brune champignoner</t>
+          <t>Coop koteletter, skinkeschnitzler eller stegeflæsk</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Økologiske</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>400-500 g</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>55,00. kr/kg</t>
+          <t>97,50. kr/kg</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1029726</t>
+          <t>1032178</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=602&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2b9430b445683c53c68554fbe39b9462&amp;w=352&amp;s=0c4eb9ac3ded3f8e5b6b775fc1ba165d</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fad21a1ca970ff32ac6d8735ffd3d4786&amp;w=552&amp;s=04c7428c6b74164408c7ba4e888d10d0</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>c1e37a8595381e37</t>
+          <t>d6ce50340a9bad5b</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3709,7 +3629,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1 bakke</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -3721,41 +3641,41 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Galia melon</t>
+          <t>Glyngøre laks eller rødspætte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Galia</t>
+          <t>Glyngøre</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1 stk</t>
+          <t>225-250 g</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20,00. kr/stk</t>
+          <t>200,00. kr/kg</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1029727</t>
+          <t>1032183</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa79a004a466f75dba4bb01b3d665ea96&amp;w=352&amp;s=0b9501a4b8409cf628f34325c5982618</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa0c58b46fbce52b47359e1e0d7f8be5e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0536bfa39c8584e658c5510b330b62bc&amp;w=552&amp;s=b5cee90c905ee8c58fe49f860f130600</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>91343ed370cb638b</t>
+          <t>d1661be407581f6e</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3765,7 +3685,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -3777,41 +3697,41 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Coop røde kernefri druer</t>
+          <t>Hakket oksekød 4-7%</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Hakket</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>500 g</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>44,00. kr/kg</t>
+          <t>137,50. kr/kg</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1029729</t>
+          <t>1032180</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F61b29140042a2e58665f713d6dd79804&amp;w=352&amp;s=c835831578491fefb1256797c1232657</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F232e0e257eb7685222265ee6c34eef52&amp;w=252&amp;s=89ced3ba1f45d9747f08a1e15476e167</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>c63199d366ce698c</t>
+          <t>ee3d33c744371270</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3821,7 +3741,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>1 bakke</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -3833,41 +3753,41 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Änglamark babymad på glas</t>
+          <t>Xtra! hel kylling</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>Xtra!</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>190-210 g</t>
+          <t>1450 g</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>52,63. kr/kg</t>
+          <t>33,79. kr/kg</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1029758</t>
+          <t>1032182</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3a52a631dc43420c9b898e1f3fe914a3%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6d13e0036f0a8fc3cf3fe1caa65bb066&amp;w=552&amp;s=2084fbe5d60e4d4aec157a0583024be2</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F84f0f95e59efa7f9971c54675b17588b&amp;w=252&amp;s=45ee796007562398eff3597948739c46</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>c33c6dc326933e68</t>
+          <t>c3366dc1341c3e9b</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3889,41 +3809,41 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Lifebrands, Castus eller Änglamark majssnacks</t>
+          <t>Maasdamer</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Lifebrands,</t>
+          <t>Maasdamer</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>30-90 g</t>
+          <t>450 g</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>400,00. kr/kg</t>
+          <t>108,89. kr/kg</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1029760</t>
+          <t>1032188</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F421a1b32d66f765b88e275a024813bda%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1509e9cb0b7e9aa5b84e1d9ffa46e8f5%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F60f3ab2824d13ff5f678c363030f0da7&amp;w=252&amp;s=ac621b5a09ab448584308d674fe2c649</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4c9c4596bc49346b2dee47ac8d1f2b7a&amp;w=163&amp;s=639990b7cc5ea1fcf063ec730347ccc2</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>9ab07f1f604c2dcc</t>
+          <t>99e4b99e27919607</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3945,41 +3865,41 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Semper Smoothie</t>
+          <t>Ferske salsiccia</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Semper</t>
+          <t>Ferske</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>90 g</t>
+          <t>300 g</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>66,67. kr/kg</t>
+          <t>133,33. kr/kg</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1029766</t>
+          <t>1032190</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9eddae5c92a5387e0394b622ff34cba5%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F14ed24609d7f745023eede1d81a835d5%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Febd98bea95a10d9900358adf7de615ec&amp;w=252&amp;s=b15d1e7ae6885c56f0fe2ae1f187e3e0</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F88d6ddd2caf5039598dd5fb6e7faabe8%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa5c1b24d79e827cb8b94c4df19bd75a1%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F28a4a762ed54457a5e71e370752f4685&amp;w=352&amp;s=77de94d4fd985401e08175485e4f1976</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>d2a52f58300fefc2</t>
+          <t>d5b163f30fe422e0</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3989,7 +3909,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -4001,31 +3921,41 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Plys*</t>
+          <t>Flæskestegs sandwich med chilimayo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Plys*</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+          <t>Flæskestegs</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>45,00. kr/stk</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>45</v>
+      </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1029778</t>
+          <t>1032193</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fac45c8781ec16673669e3ee8cc2e06fb&amp;w=552&amp;s=37d9df439a375beb9cf13f25c4bca1d9</t>
+          <t>https://d3qnoxvhi29qvt.cloudfront.net/feed-images/0d14df138fea7e873d0eb4a8b2575ed2</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>c7f36c4f32981887</t>
+          <t>ebd00e43bc96e14e</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4033,7 +3963,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>1 stk.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4043,12 +3977,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Puslespil*</t>
+          <t>Torsdagssmørrebrød</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Puslespil*</t>
+          <t>Torsdagssmørrebrød</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4056,22 +3990,28 @@
           <t>1 stk</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>29,00. kr/stk</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>29</v>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1029784</t>
+          <t>1048623</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc4fb9f789bddcca3cda71118f3dd4dbe%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Facc0a26a7931beba0ef874a0beff9e5f%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2303b3768357c6d1977466d911050b20%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fcbe24956fec251c2b12491137d96f2d8&amp;w=552&amp;s=5081707db227e666ad243e73303e3072</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd55b1bc276e5724e1e2bc2903baea6e0&amp;w=558&amp;s=94e80f1158ebedadb95cd14b0aeb7bdf</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>e6411dbec219fc61</t>
+          <t>d3917e6e1a5445d1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4093,12 +4033,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AquaPlay sejlbåde*</t>
+          <t>Fredagsbøf</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AquaPlay</t>
+          <t>Fredagsbøf</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4106,22 +4046,28 @@
           <t>1 stk</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>300,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>75</v>
+      </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1029781</t>
+          <t>1032175</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0bcf79d203ff387bf5271f061ef87849&amp;w=252&amp;s=46385ba423160f0dc8ab8602d7cf8ae0</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd63f5e11ff65681ce516f2f65ce45bb2&amp;w=1152&amp;s=cc3b3feb288babde12d7ebc1bdd6bb48</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>8e6736936b946899</t>
+          <t>d0990f663ea6615b</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4143,12 +4089,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>X-SHOT Typhoon Thunder vandpistol*</t>
+          <t>Fredagstapas fra Delikatessen</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>X-SHOT</t>
+          <t>Fredagstapas</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4157,21 +4103,23 @@
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="n">
+        <v>165</v>
+      </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1029777</t>
+          <t>1032195</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7d7d102cbeb6ea12cbd49428cca60e85&amp;w=538&amp;s=7ea41039dfc8a96104318a2ca036a70a</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fab8d4dacd0ee58e026bf22c900bcb735&amp;w=558&amp;s=32ffefaf3f8336d907235d9a2141a599</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>95863ed51d7c60f0</t>
+          <t>d8981f67051d2fe1</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4193,25 +4141,35 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AquaPlay vandbane*</t>
+          <t>Lun lørdag</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AquaPlay</t>
+          <t>Lun</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="n">
+        <v>25</v>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1029783</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>1048622</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F71a15d0b00a901f096c51199e1305b6a&amp;w=539&amp;s=42fa7e797462795b0a4b1425ea4e0132</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>d18d2d465a5e17d2</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -4227,43 +4185,31 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Pagus Bisano Apasio, 100% Grenache eller 100% Chardonnay</t>
+          <t>Nakke- og skuldermassage</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pagus</t>
+          <t>Nakke-</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>66,67. kr/l</t>
-        </is>
-      </c>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
-        <v>50</v>
+        <v>399</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1029789</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=602&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1cf0f0d6e95491aea8b60da36930731e&amp;w=552&amp;s=168c8a3462a4452b3b0aa3c29651885b</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>95176c64379858f6</t>
-        </is>
-      </c>
+          <t>1032364</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -4271,7 +4217,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -4283,41 +4229,41 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Yellow Tail</t>
+          <t>Irma spisemoden avocado eller mango</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Irma</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>2-3 stk</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>53,33. kr/l</t>
+          <t>11,00. kr/stk</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1029791</t>
+          <t>1032202</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc3b3ce71baab4335afefd46a79a10945%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa9167d329b10a1259f75adb240248268%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faf756f5d249b5b31d7f481b5a2c2a793&amp;w=224&amp;s=9b01742cf1504f8db6989d047c2c3221</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe87b5e7e30c28f93ae06b77e05a8ecb2&amp;w=552&amp;s=02a6eda63ba34af1dbc4cb5060de1338</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>9d6172a2639f489e</t>
+          <t>855e4b845e932c5f</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4327,7 +4273,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 bakke</t>
         </is>
       </c>
     </row>
@@ -4339,41 +4285,41 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Z-Zinfandel eller Bread &amp; Butter i boks</t>
+          <t>Coop stor bakke blåbær</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Z-Zinfandel</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2,25-3 l</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>66,22. kr/l</t>
+          <t>97,50. kr/kg</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>149</v>
+        <v>39</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1029793</t>
+          <t>1032204</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F034747840c87ac445b7313245ffb7f93%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9152ea3ff8b894a13bb67ee4d39d5611%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa93fd9d9cb3bc2b8ecd8a74bc3a28846&amp;w=252&amp;s=99dec5af5d7c2e83d27cb78c53b6cab2</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F593d774b06a17b1f37a4196b9d197af5&amp;w=552&amp;s=3ad50f59f0ac58cf21b0d0bbdc413837</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>a0a05e5f795f5831</t>
+          <t>c667c34ccc716c65</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4383,7 +4329,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>1 boks</t>
+          <t>1 bakke</t>
         </is>
       </c>
     </row>
@@ -4395,41 +4341,41 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Viña Maipo i boks</t>
+          <t>Dansk agurk</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Viña</t>
+          <t>Dansk</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>3 l</t>
+          <t>1 stk</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>39,67. kr/l</t>
+          <t>9,00. kr/stk</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>119</v>
+        <v>9</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1029795</t>
+          <t>1032199</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1fea17240ec9a07a86cf39c34860b35e&amp;w=252&amp;s=e962784878e93d355f197103ae1bfec7</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7b148dea4aeb9084be9bc7c94d410fc7&amp;w=190&amp;s=e3f561b81f3c40702067714ea598c527</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>9336696d3cc39e90</t>
+          <t>a52b54d113edc437</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4439,7 +4385,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>1 boks</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -4451,45 +4397,41 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Route 2 i boks</t>
+          <t>Store conference pærer</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>3 l</t>
+          <t>Stk</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>33,00. kr/l</t>
+          <t>22,00. kr/stk</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>99</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>134.95.</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1029797</t>
+          <t>1032207</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1a40868d9245ae65bc37aeeb75b4e449%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2b4471eed7f09f48687c205ea78b02f2%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb9e6f4c42b235a4373bb758fdfab794a&amp;w=1152&amp;s=5fbfe0bdd244221bc2efa540f48b0203</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9c216922794c7efc5d36bc9708e91dd9&amp;w=552&amp;s=87a96e32c9f7d34c1d044fcd1e82ccd8</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>92636fc79c969099</t>
+          <t>ce6c30936b33cc9a</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4499,7 +4441,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>1 boks</t>
+          <t>1 bakke</t>
         </is>
       </c>
     </row>
@@ -4511,45 +4453,41 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Why Not?</t>
+          <t>Honningmelon</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Why</t>
+          <t>Honningmelon</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>1 stk</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>66,44. kr/l</t>
+          <t>22,00. kr/stk</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>299</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>109.95</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1029808</t>
+          <t>1032210</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F64e0371f973f65241c5ddb59bd97beb6&amp;w=552&amp;s=32e4e3375fa718c23ff596c0934d4721</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fab32a975ba7cddd2cc0063167b85aeb7&amp;w=552&amp;s=e0b6b04d19f9d659f5bb55ab561843c5</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>954e6ab13a934f4c</t>
+          <t>cbc365cd3838666c</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4559,7 +4497,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>6 flasker</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -4571,41 +4509,41 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fuentespina Crianza, Kungfu Girl Riesling eller Amaluna Brut Sparkling</t>
+          <t>Dronning Ingrid Pelargonia</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fuentespina</t>
+          <t>Dronning</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>Stk</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>118,67. kr/l</t>
+          <t>25,00. kr/stk</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>1029800</t>
+          <t>1032211</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6f47ed63de5d59c8d578d9f3049704ea%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3e30b1fc0851b70dd994d713dcf1ccb5%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff9e69f8f1caa1801099c5031fe45f550&amp;w=219&amp;s=a86ca4154e1fddcb27770b2e65fb476c</t>
+          <t>https://d3qnoxvhi29qvt.cloudfront.net/feed-images/35c581b69836e512c2c6a28854742d12</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>d80d26da03b766f4</t>
+          <t>ea99957aa684d02f</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4615,7 +4553,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -4627,41 +4565,41 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Weinbiet eller Yealands Single Block</t>
+          <t>Änglamark økologiske æg</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Weinbiet</t>
+          <t>Änglamark</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>10 stk</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>92,00. kr/l</t>
+          <t>2,90. kr/stk</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1029804</t>
+          <t>1032222</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fff85c7a6dd430d6522cb0a23ea04cd53%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fcb1a2fc3a4ed2cc16f556aeadf5b4c55%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F96e67e63076bdb3e638bc6cb7f3bdf3d&amp;w=252&amp;s=d3ede1266175155906dd06a0841cacf6</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdfd533404e0fcd6ea8f876f52f6099ae&amp;w=1152&amp;s=2b761fcd83ec5e214c2f494fed42dce9</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>c03f8cc93bd46996</t>
+          <t>c56e6ec53991b113</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4671,7 +4609,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 bakke</t>
         </is>
       </c>
     </row>
@@ -4683,41 +4621,41 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Domaine de La Baume eller Cune Reserva</t>
+          <t>Coop remoulade eller mayon-naise</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Domaine</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>78,67. kr/l</t>
+          <t>30,00. kr/kg</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1029807</t>
+          <t>1032213</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9f1287d0b92d74e9cdf4cd7f0508513c%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F549f11715e1708d6cc3e52f4fbbcb6d6%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F69272e1bb280ecf7e63733776b9fe25f&amp;w=252&amp;s=8ad1091a2b62da65f6af19c579ef8682</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F728461f3294429b3c7973790e1d52b43&amp;w=552&amp;s=13fe8ad8f919cb243c0ba356255304e0</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>946a37c049b74b37</t>
+          <t>95c6426a2feb69c8</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4727,7 +4665,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -4739,41 +4677,37 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ripasso Superiore Villa Annaberta eller Moillard Bourgogne</t>
+          <t>Poke bowls</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ripasso</t>
+          <t>Poke</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>105,33. kr/l</t>
-        </is>
-      </c>
+          <t>1 stk</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1029802</t>
+          <t>1032224</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F79ac2c63542e6cc5bbc809439b56a3a1&amp;w=1152&amp;s=6a8ebfefd80954b5f8502fd16ed6a877</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe41aa3658140cf67e1f335b8e2b9a4c8&amp;w=552&amp;s=923c32e5cd060ad4f1253373dbceeab4</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>9b6c36c33c92653c</t>
+          <t>ce666c663032399f</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4783,7 +4717,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -4795,41 +4729,41 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Barolo Villa Dierico eller 1000 Stories</t>
+          <t>Kohberg brød</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Kohberg</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>320-1000 g</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>132,00. kr/l</t>
+          <t>56,25. kr/kg</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1029817</t>
+          <t>1032220</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F81915cc9e936c1ddfeec45021d35d9ff&amp;w=552&amp;s=f0d660980b24fe7a986ee04867352741</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1765f3a5515e79c3c98e2ac7208a1dae&amp;w=252&amp;s=5305d0c50d2c3848d21b9aa4644f20cb</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>f870038f7f2700fa</t>
+          <t>92673ec76192c696</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4839,7 +4773,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -4851,41 +4785,41 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Les Jablieres Côtes de Provence, Vallée des Reines Cabernet d'Anjou eller Cava Recoda</t>
+          <t>Coop røget-, gravad laks eller Kaptajnens fangst rejer</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Les</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>150-200 g</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>78,67. kr/l</t>
+          <t>326,67. kr/kg</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1029811</t>
+          <t>1032215</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd683a6478c8688afee44541bbbd74132&amp;w=237&amp;s=23f8a6defb0010ee960099009642d18a</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff60dfcc771d8d158886069fca9b5b4bc&amp;w=252&amp;s=693650eefccd27fa1cb8e49b6b8788e9</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>f5746de3729c2888</t>
+          <t>c33e4c93619b2d6c</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4895,7 +4829,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -4907,41 +4841,41 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Spier Moscato, Southbank Sauvignon Blanc eller Mediteo Méditeranée Rosé</t>
+          <t>Beauvais survarer</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spier</t>
+          <t>Beauvais</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>310-580 g</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>66,67. kr/l</t>
+          <t>64,52. kr/kg</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1029813</t>
+          <t>1032217</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=197&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa88c64252bae956e0d01b1ad8462e135&amp;w=252&amp;s=9e3e3dac0c07d8de90711d6d43071eb2</t>
+          <t>https://d3qnoxvhi29qvt.cloudfront.net/feed-images/4c02f3f36a726ae49254ad5b103c1026</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>92694d9830c766f7</t>
+          <t>f693e572324d8847</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -4951,7 +4885,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 glas</t>
         </is>
       </c>
     </row>
@@ -4963,41 +4897,41 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Santa Rita eller Zimmermann's Grüner Veltliner</t>
+          <t>Änglamark økologiske nye kartofler</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Santa</t>
+          <t>Änglamark</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>75 cl</t>
+          <t>1 kg</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>53,33. kr/l</t>
+          <t>16,00. kr/kg</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1029815</t>
+          <t>1032232</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F14a58512191d75b417323d0e5cb0d134&amp;w=252&amp;s=84910fdce47a53ccf7f50de0c18476d3</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdd4871de6124a9bfe1bc3d4363ccf892&amp;w=552&amp;s=78052433816dbf079338e7f4f3d5442f</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>943b369639b66b0a</t>
+          <t>80df7f1166a63aa8</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5007,7 +4941,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -5019,41 +4953,41 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Kahlua, Havana Club Especiel Rom, OP Anderson Aquavit eller Råstoff Shots</t>
+          <t>Änglamark økologiske ærter</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kahlua,</t>
+          <t>Änglamark</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>70 cl</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>155,71. kr/l</t>
+          <t>37,50. kr/kg</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1029825</t>
+          <t>1032226</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F527d13413369f0e9e99865e88963702a&amp;w=552&amp;s=988a2e48c5a937f88a035491ea64fffc</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff85278e738d7cac2c5e5084d5540a6df&amp;w=552&amp;s=5ac04477e4c711a2b0cb21249709afc4</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>cd6732b8b20db472</t>
+          <t>c73c346d34cb32c3</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5063,7 +4997,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -5075,41 +5009,41 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Gammel Dansk Bitter, Ballantine's Whisky, Absolut Vodka, Beefeater Gin, Havana Club 3 års Rom, Malibu eller Underberg Box</t>
+          <t>Coop kyllingebryst, -inderfilet eller -overlårsfilet med skind</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Gammel</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>70 cl</t>
+          <t>300-400 g</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>412,50. kr/l</t>
+          <t>96,67. kr/kg</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1029827</t>
+          <t>1032229</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5c5b261737bc2cb47db4946fd04af45c&amp;w=552&amp;s=c388f6c9987bbe834868e4855789333a</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F842d6e8fc22e3f446f081a800b744321&amp;w=252&amp;s=4f78da7d03ca52d61cd7c8967dacd0fa</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>9b3965c532c966cc</t>
+          <t>95581f27e1e41ee1</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5119,7 +5053,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>1 flaske/dåse</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -5131,41 +5065,41 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The Glenlivet 12 års Single Malt Whisky, Don Papa Masskara eller Bumbu Original</t>
+          <t>Änglamark økologisk dansk persille</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>The</t>
+          <t>Änglamark</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>70 cl</t>
+          <t>320 g</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>355,71. kr/l</t>
+          <t>62,50. kr/kg</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>249</v>
+        <v>20</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1029819</t>
+          <t>1032231</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbc00212870fae8f79de321b7f127ee45&amp;w=252&amp;s=cfa77d5749dca7ce2a8818fbc69e6a01</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F08c310326c045c88d0cf58bf331dc134&amp;w=252&amp;s=e7e1cefda627a6c7b8966b4304afb52e</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>c3633a6ed83c92a6</t>
+          <t>9ab62c4d6565656c</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5175,7 +5109,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -5187,41 +5121,45 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Hendrick's Gin, The Singleton 12 års Whisky eller Italicus Rosolio di Bergamotto</t>
+          <t>Torres Coronas eller Esmeralda i boks</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hendrick's</t>
+          <t>Torres</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>70 cl</t>
+          <t>. 3 l</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>284,29. kr/l</t>
+          <t>43,00. kr/l</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>199</v>
-      </c>
-      <c r="G88" t="inlineStr"/>
+        <v>129</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>229.00.</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1029822</t>
+          <t>1032240</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbe6d82c45a8011fb81f932fa64d4567e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9e7177ed80851c22084bc9698c81b9d6%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Feef091f16d3c921e2060457fd372b166%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb61acbf8d72b974084270b8c1a950ad1&amp;w=252&amp;s=7df266488aa1ba01731f663ee1c160b2</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F25c9be19b1c599db3b40be047b24a3bd%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F960bd451998a7bf60d468572ec2ae075%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5c73b5fd4085728657f38de1bc1a521f&amp;w=552&amp;s=e743733196effba1ea180d9eff5c6830</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>fa64018b53fb2593</t>
+          <t>a3a25e5d6958a6a3</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5231,7 +5169,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 boks</t>
         </is>
       </c>
     </row>
@@ -5243,41 +5181,45 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Stryhns leverpostej</t>
+          <t>Cuvée Dissenay eller Grant Burge Reserve</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Stryhns</t>
+          <t>Cuvée</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>275 g</t>
+          <t>. 75 cl</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>50,91. kr/kg</t>
+          <t>66,67. kr/l</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>14</v>
-      </c>
-      <c r="G89" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>99.95.</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1029830</t>
+          <t>1032234</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2e1406edef60cdee2087948fd88b0b52%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb690ef8de01c5b8a243d2ad49434cc22%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8dff2d31b23f9e58e5341a7b01866207&amp;w=552&amp;s=651b68fc75cd10fff0eed7694dbcd64a</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2e97af6cd698da8f035c454509520450&amp;w=552&amp;s=712c077e62da8e38722119cd8b84f2db</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>e01d1d77708ce237</t>
+          <t>9e32cd9a32cd31b2</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5287,7 +5229,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>1 bakke</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -5299,41 +5241,41 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Kohberg Velsmag</t>
+          <t>Casillero del Diablo</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Kohberg</t>
+          <t>Casillero</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>380-600 g</t>
+          <t>. 75 cl</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>47,37. kr/kg</t>
+          <t>53,33. kr/l</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1029609</t>
+          <t>1032236</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F61f165afb25f96bca795b4eb565a21b5%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4a2bcd46fc1756451da9736ce786aab0%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F033b7844893bd2fe51b134eb43dd94d5&amp;w=552&amp;s=8fc71d365ae30fbe33c3fd81bd79583e</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F44f3e895aac9fd4dd021c86e3baa2681&amp;w=257&amp;s=c55be4d27ecf2f190d4e48eebfd4b875</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>c42c73cc7392387b</t>
+          <t>b44d30bacb374137</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5343,7 +5285,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -5355,41 +5297,45 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Steff Houlberg cocktail pølser eller skinke strimler</t>
+          <t>Outlaw Zin i boks</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Steff</t>
+          <t>Outlaw</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>175-200 g</t>
+          <t>. 3 l</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>91,43. kr/kg</t>
+          <t>38,33. kr/l</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>16</v>
-      </c>
-      <c r="G91" t="inlineStr"/>
+        <v>115</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>159.00.</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1029832</t>
+          <t>1032238</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F54a73479af8901f1c32574efc00896ad%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa7ade91c63ad2a682e500b14a15f0681&amp;w=252&amp;s=b1b280ec112c29c1ea0be2bcdfa710c1</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb12a98f013efc4c2d8357dc54365ef7f&amp;w=316&amp;s=9e33ab96a35aab1e3b61a1f390e3cdbe</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>ae6d11661dc6678a</t>
+          <t>e7c708cc5d99c619</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5399,7 +5345,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 boks</t>
         </is>
       </c>
     </row>
@@ -5411,41 +5357,41 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Pålækker salamisnacks</t>
+          <t>Ripasso Superiore Pagus Bisano</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pålækker</t>
+          <t>Ripasso</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>10 x 10 g</t>
+          <t>. 6 x 75 cl</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>220,00. kr/kg</t>
+          <t>66,44. kr/l</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>22</v>
+        <v>299</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1029834</t>
+          <t>1032250</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fefaa7590dd59309c57dfc4522fdb1fcb&amp;w=252&amp;s=3c827d70d2627118f817a0b9bc75c69e</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F47fbfccd1594d606ff1d4db2930039a2&amp;w=352&amp;s=060eec8d64c6397371a6f4a09948c037</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>c1e765c93c633c8c</t>
+          <t>92194b87b4636f65</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5455,7 +5401,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>1 pose</t>
+          <t>6 flasker</t>
         </is>
       </c>
     </row>
@@ -5467,41 +5413,41 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Jensens Køkken sauce</t>
+          <t>Vamos! eller Sandara Sparkling Rosé</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Jensens</t>
+          <t>Vamos!</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>250-350 ml</t>
+          <t>. 75 cl</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>64,00. kr/l</t>
+          <t>53,33. kr/l</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1029835</t>
+          <t>1032248</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa42f5f4cddb7a5b0b7f4a36cc0310424%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc9888fae13143e2e1659c04849666f4e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fabe5805063ea864a9be2b607288c7fcb%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffce21d15c7c1218cab8c5208a999d1ea&amp;w=252&amp;s=14f94416416339e429fe9868a0e3f12d</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=602&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F086eb849f38b15ade73e15cfcc8e4e95&amp;w=352&amp;s=ff6f9e3b8dd27a07ff07fa702aefbe44</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>da5e4e3925253d29</t>
+          <t>944663316d9d4be9</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5511,7 +5457,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -5523,41 +5469,41 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Peka flødekartofler</t>
+          <t>Piccini Zinfandel, Poeme Vineyards eller Fat Bastard Chardonnay</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Peka</t>
+          <t>Piccini</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>700 g</t>
+          <t>. 75 cl</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>28,57. kr/kg</t>
+          <t>66,67. kr/l</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1029838</t>
+          <t>1032245</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb70ff860b344672aeb1f56047b53f9b9&amp;w=252&amp;s=b7c9d2ed5e692dc52e2da0c5cb51156b</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F23375553e5af78330787c767dcad56b9&amp;w=352&amp;s=a1d5b9f2485a8e6b91a9257bb8d5943e</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>d07a97c5ad956862</t>
+          <t>926c39c3689c67b3</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5567,7 +5513,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -5579,41 +5525,45 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>De Cecco Extra Jomfru olivenolie</t>
+          <t>Spier Private Collection</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>Spier</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>500 ml</t>
+          <t>. L</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>130,00. kr/l</t>
+          <t>92,00. kr/l</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>65</v>
-      </c>
-      <c r="G95" t="inlineStr"/>
+        <v>69</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>129.95.</t>
+        </is>
+      </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1029839</t>
+          <t>1032242</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4cede36f4f3e7e2dc5193629d81628be&amp;w=552&amp;s=4d728ba858349060e0fd4d8c974d0cc3</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F49fbecdde94fe59d4f008b81d92245c6&amp;w=352&amp;s=3ca99473d13f96dee4c35edd8f7f113f</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>cb4c649ccc99c967</t>
+          <t>926c3d92cdb26cc9</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5635,37 +5585,41 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Änglamark økologisk dansk basilikum</t>
+          <t>Amarone Nino Ardevi eller Cattin Grand Cru</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>Amarone</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1 stk</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
+          <t>. 75 cl</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>132,00. kr/l</t>
+        </is>
+      </c>
       <c r="F96" t="n">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1029842</t>
+          <t>1032257</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2ac717dfa77a6f7012af50cd8e86833e&amp;w=213&amp;s=2a374b9480f2d0e8d512a80815961e67</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbd37ce263915a96532b8cb69b7eb549b&amp;w=552&amp;s=792f5e450c53c05eb9ab9c92924412c0</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>94a16a9f3d3a1a1e</t>
+          <t>824c31cf0ff14cfc</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5675,7 +5629,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -5687,41 +5641,41 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Coop danske store løg</t>
+          <t>Spier Heritage, Yealands Reserve Sauvignon Blanc eller Les Jablieres Côtes de Provence</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Spier</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>1,5 kg</t>
+          <t>. 75 cl</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>10,00. kr/kg</t>
+          <t>78,67. kr/l</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>1029844</t>
+          <t>1032255</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4b477a71a60826bcee5aa77f742b2ff3&amp;w=252&amp;s=93008edc777fa67239922cb14ec86dad</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F33ca5ea8dfd9af14ee498581eed316ed&amp;w=223&amp;s=4d94234dd20e7ced7d5276a385efca4c</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>c71e6c947ac04ee5</t>
+          <t>ac3432a633c771cd</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5731,7 +5685,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>1 net</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -5743,41 +5697,41 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Änglamark økologisk hakket oksekød 8-12%</t>
+          <t>Chateau Cap L'Ousteau, Laugel Pinot Gris eller GM par Gabriel Meffre Rosé</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>Chateau</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>. 75 cl</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>122,50. kr/kg</t>
+          <t>92,00. kr/l</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1029587</t>
+          <t>1032253</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa253d8f52b53114ff0677db343dfc37a&amp;w=252&amp;s=1c435b201e2c7be8ba9d865b1f735600</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=197&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9faaf7646d62283493497fc55d06eb5f&amp;w=252&amp;s=6c3746b57b647308b2d0905c49f68f31</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>ee3d39c34cc05372</t>
+          <t>926c6dc3388d36cd</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5787,7 +5741,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -5799,41 +5753,41 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Buko smøreost</t>
+          <t>Torres Gran Coronas, Guigal Côtes-du-Rhône eller Moillard Cremant de Bourgogne</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Buko</t>
+          <t>Torres</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>200 g</t>
+          <t>. 75 cl</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>70,00. kr/kg</t>
+          <t>118,67. kr/l</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>14</v>
+        <v>89</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1029846</t>
+          <t>1032251</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8b3b11348fb24cc157ade6db4d41e900%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc1c4630d1452eea9852159cb9d3be5f9%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1855b10920af4e503be9dadbfaaaabaa%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9ba8e399e87982361f0f45a58c2657d7&amp;w=552&amp;s=6e12630ab1a561709985936062bc516a</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=197&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1797f507c043a9e9f005f5600e45ecbd&amp;w=252&amp;s=7336cc1ad560fd8a85336291b41d8a64</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>9a65659a9167ea64</t>
+          <t>96639686639c69b6</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5843,7 +5797,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -5855,41 +5809,41 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Økologisk Godmorgen juice eller nektar</t>
+          <t>Aalborg Taffel Akvavit, Poliakov Vodka eller Aalborg Rød Grød Shot</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Økologisk</t>
+          <t>Aalborg</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>850 ml</t>
+          <t>70 cl</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>29,41 kr/l</t>
+          <t>112,86. kr/l</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1029850</t>
+          <t>1032264</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7b6025803ba7a432de43812d3dde9413%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F67201eaa90e3c2035313250a8b085bb5%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2451619ff3ccba0198a3be665a847be7&amp;w=552&amp;s=961828ef94a8554426f2cb310bc253da</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe9501deaa11f9da26b2bd666d95cfd18%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdba54e5ef0711bb8e7e3c9832f06b5a7%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb7c734e0ce16658f4cf4b6bf2557c8f9&amp;w=552&amp;s=3bce0fe3ffeff29a55cc29630c2c1290</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>9238666d6d86396d</t>
+          <t>b16868c862f23f75</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -5911,41 +5865,41 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Thise økologisk koldskål</t>
+          <t>Jameson Whiskey, Hansen Rom, Dr. Nielsen Bitter, Tanqueray London Dry eller Flavoured Gin</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Thise</t>
+          <t>Jameson</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1 l</t>
+          <t>70 cl</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>20,00. kr/l</t>
+          <t>170,00. kr/l</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1029852</t>
+          <t>1032262</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd5b221a677a22371d1eaf290fdcd6322&amp;w=252&amp;s=890831aaf7ab6de6c3db91eef7b53967</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F143e5f0238ad315463083a065e63393b&amp;w=552&amp;s=730f1eebad1a548ef434033cbe503b37</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>c43c3b63c7339790</t>
+          <t>cf69309e69326599</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -5955,7 +5909,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -5967,41 +5921,41 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Galbani mozzarella</t>
+          <t>Barolo Fontanafredda, Amarone Pagus Bisano, Morel Gigondas eller Laroche Chablis</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Galbani</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>125-250 g</t>
+          <t>, G</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>144,00. kr/kg</t>
+          <t>198,67. kr/l</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>1029855</t>
+          <t>1032266</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd0d9dcaac81ab2ae2d81b1f898314fda%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8aaf23fd05fefc97143277414aa10fa8&amp;w=252&amp;s=3cc9ed5291650a15513d0cfcbdec8147</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5bf8fa8968e5d75af2a1e7cde974757d&amp;w=552&amp;s=7ec4c655f3f78cb5f275aa2238d932b2</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>913c2dc276873ce9</t>
+          <t>9b64cf9a30cf3186</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6011,7 +5965,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -6023,41 +5977,41 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Klovborg eller Cheasy skiveost</t>
+          <t>Normandin XO Cognac, Renault VSOP Cognac, Talisker 10 års eller Dalwhinnie 15 års Single Malt Whisky</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Klovborg</t>
+          <t>Normandin</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>200-240 g</t>
+          <t>70 cl</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>140,00. kr/kg</t>
+          <t>370,00. kr/l</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>28</v>
+        <v>259</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>1029856</t>
+          <t>1032260</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faa4e03edf4be7c509942c6da61f29316%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F68c40260d6bc4000f79d350455e54a4c&amp;w=252&amp;s=ac34232e3cf6ade7ce1fa3112c894ca0</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff495f5534fd293304c72fc2907a66d3f&amp;w=343&amp;s=c20a62e7bd705d1d00899b6f792c02ac</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>886753266699b6bc</t>
+          <t>b0506aba4fa5358f</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6067,7 +6021,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -6079,41 +6033,41 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Stay Strong skyr</t>
+          <t>Coop proteinshake</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Stay</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>950 g</t>
+          <t>500 g</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>26,32. kr/kg</t>
+          <t>30,00. kr/kg</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1029859</t>
+          <t>1032269</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1c4d719b9ab26571ffc26a202d804e8d%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6c06bb9edba4cf540a5796fe927d1e63&amp;w=252&amp;s=c4b9176bb6b4a0e35eafb78553f64b67</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbeaf71f6c8da5d4f435ccafc09097e50&amp;w=552&amp;s=0e20f04df9ba555db4b1a786180d7e1c</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>d1ec2f5322338b35</t>
+          <t>9ace384c9b333333</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6135,41 +6089,41 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Mammen laktosefri hytteost</t>
+          <t>LinusPro elektrolytter tabs</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Mammen</t>
+          <t>LinusPro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>450 g</t>
+          <t>20 stk</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>40,00. kr/kg</t>
+          <t>1,00. kr/stk</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>1029854</t>
+          <t>1032271</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F50af70c8c7c78467277f8f82b13b4bcf&amp;w=235&amp;s=e66a805b5fd7da3e5b946b79bac73da6</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb4eb190b0ac0f3ceb7acbb03cf4bb5ee&amp;w=252&amp;s=21766ae8d6265d543dc9244c9d678bb0</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>c0abbeb46b4a1734</t>
+          <t>bcda03e38383e38d</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6191,41 +6145,41 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Arla laktosefri friskost</t>
+          <t>Bodylab proteinpulver eller creatin kapsler</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Arla</t>
+          <t>Bodylab</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>200 g</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>75,00. kr/kg</t>
+          <t>237,50. kr/kg</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>1029857</t>
+          <t>1032273</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe2fd03ada1e0772a3c160c23bac3041b&amp;w=552&amp;s=f1cc2cbb1dc23a1c8627f6b0c2799775</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faa0e5e6896c2ec0a7e5433edcdad54fe&amp;w=252&amp;s=80e1e4838899ee5cbe802758b7318214</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>956e3a729c314b99</t>
+          <t>964933cd68696679</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6247,41 +6201,41 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Coop håndværkere, møllehjul eller Hatting kanelsnegle</t>
+          <t>Thise økologisk aktiv yoghurt</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Thise</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>340-600 g</t>
+          <t>750 g</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>41,18. kr/kg</t>
+          <t>20,00. kr/kg</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>1029866</t>
+          <t>1032275</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8571c55f259c51fe049da35bc3d17fc9%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9da7ffe5b06337f0ddb4316979bfd801%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fca20e86e5fb55e7ecb1172b976fa9e2d&amp;w=752&amp;s=bfa16cdf6e0e0139da2d42a320f7e690</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7e93d2ca013495801149437c4f337db8&amp;w=252&amp;s=d7ee564021d2eab178c920b4c6ad8d18</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>859c9594f3279c2d</t>
+          <t>c2c3e1e369593936</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6303,41 +6257,41 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Daloon forårsruller, spring rolls eller miniruller</t>
+          <t>Stay Strong pro skyr</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Daloon</t>
+          <t>Stay</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>400-800 g</t>
+          <t>500 g</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>62,50. kr/kg</t>
+          <t>30,00. kr/kg</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1029861</t>
+          <t>1032277</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=602&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F92e9eb14880c73dc8a8206306720bd10&amp;w=352&amp;s=c3c8767a0f0252104bd21fd9d899dec5</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F80a0572d8976ff02703e64057e8d3aa1&amp;w=274&amp;s=d85bf00dcef16293e579c2df7f850832</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>dc406a9f17b1616e</t>
+          <t>d4f05fa3a54b1e0a</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6359,22 +6313,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Knorr færdigret</t>
+          <t>Arla eller Cheasy koldskål</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Knorr</t>
+          <t>Arla</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>262-324 g</t>
+          <t>1 l</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>68,70. kr/kg</t>
+          <t>18,00. kr/l</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -6383,17 +6337,17 @@
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1029864</t>
+          <t>1032279</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb38184e49dff563c71ffce88af38804e&amp;w=352&amp;s=8dca307f496a50fe4f0e98fb5f6bf66a</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F21d4dfcafd3ae43fad3470cc7d2ba34d&amp;w=552&amp;s=f4bad87656fd986cac8ef360ed05cd37</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>929e643c63c33cc7</t>
+          <t>c4a10af40bf61bf6</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6403,7 +6357,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -6415,41 +6369,41 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Amo mel</t>
+          <t>Président Brie eller Saint Morgon rødkit</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Amo</t>
+          <t>Président</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>1,8 kg</t>
+          <t>200 g</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>10,00. kr/kg</t>
+          <t>140,00. kr/kg</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>1029868</t>
+          <t>1032281</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5224bf115b1d24940f97c26b2d26587f&amp;w=352&amp;s=216066565439e6430fcf14476b9d6325</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fde57cf6c9c3f11f6fcecc9a7afee6b3d&amp;w=260&amp;s=60e6444287b44a80e2a1a225299715ea</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>c3cc1999ce3336c6</t>
+          <t>c4c44beb1f242f1b</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -6459,7 +6413,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -6471,41 +6425,41 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Marabou ispinde eller Carte D'or vanilla is</t>
+          <t>Them Fætter Kras skæreost</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Marabou</t>
+          <t>Them</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>270-1000 ml</t>
+          <t>. 450 g</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>129,63. kr/l</t>
+          <t>122,22. kr/kg</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1029875</t>
+          <t>1032284</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe7aa2b4d7720d02c212be5d9fba58e92&amp;w=552&amp;s=07b64b4153e9b9415cc9fa43f090b155</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd6b18bfb1c1fa6eccee9cb1390dad49d&amp;w=252&amp;s=688d6637048917189e692b27f3680009</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>c39669399a39393a</t>
+          <t>c0c3c73cd6989b33</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6527,41 +6481,41 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Haribo slikpose</t>
+          <t>Riberhus skiveost</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Haribo</t>
+          <t>Riberhus</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>325-375 g</t>
+          <t>200-240 g</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>129,23. kr/kg</t>
+          <t>145,00. kr/kg</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
-          <t>1029870</t>
+          <t>1032286</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F988d9863b97477d085fe9476f0de9cb2%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc99a5c58f607e354407d92e9ac778272%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe63b4f72c96f690f7c9df833dd980f7b&amp;w=552&amp;s=d076b52696ee0d0ba99f51352a3d3fc3</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F31a840cb8a5bce2c381aa01154011e9d&amp;w=252&amp;s=77aa83c8826b4c671c2f187ad65e5459</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>f9d9536250753326</t>
+          <t>c11b6af437353568</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6571,7 +6525,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>1 pose</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -6583,41 +6537,41 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Toms G´oe stænger</t>
+          <t>Coop dansk piskefløde</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Toms</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>100-104 g</t>
+          <t>500 ml</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>150,00. kr/kg</t>
+          <t>40,00. kr/l</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>1029872</t>
+          <t>1032391</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd8590655e7f9e1295a98b1ff1325a226%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7165d3c32be60b6c8b241e5410ad0bc7%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff6542cd8048beb9ce8543e6f873907d9&amp;w=252&amp;s=5df4b2153843e2b2f1c8c710b932ddf4</t>
+          <t>https://d3qnoxvhi29qvt.cloudfront.net/feed-images/a625bbb17159f916dafa1b52a7584a9e</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>8ce99e869d070f2b</t>
+          <t>abf1947b1a64c19c</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6627,7 +6581,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>1 pose</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -6639,41 +6593,41 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Coop is</t>
+          <t>Hanegal økologisk postej</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Hanegal</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>300-900 ml</t>
+          <t>200 g</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>96,67. kr/l</t>
+          <t>80,00. kr/kg</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1029873</t>
+          <t>1032293</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0e1ac39284b7c263f2a11d9d54510d8f&amp;w=252&amp;s=20958377a8552fc9f0127199d1a9465e</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa75e687ee442a326dbf38132cf8b1606%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fad8e47f99bb6be477e88b675707447b1&amp;w=552&amp;s=b4ba9827e900802cc878acf0d99ee6b7</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>913c1ed34b614e6d</t>
+          <t>81683b7767116799</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6695,41 +6649,41 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nestlé eller Mars barer</t>
+          <t>Coop fyldt pasta, gnocci eller pastasauce</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Nestlé</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>38-51 g</t>
+          <t>250-500 g</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>263,16. kr/kg</t>
+          <t>72,00. kr/kg</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
-          <t>1029880</t>
+          <t>1032295</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fcf53998efb95f9dd6510404fe465d48c&amp;w=252&amp;s=150b9f61084b7987f78b2c716931c2e3</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffd2885822175ab2e1cb4bf6b077d6634&amp;w=552&amp;s=dca688f0dcbe3d7b5f424b7687fdaf3e</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>9497969432cf7163</t>
+          <t>ca933999b3659992</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6751,41 +6705,41 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Carletti æske eller Lindor hjerteæske</t>
+          <t>Eriks sauce</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Carletti</t>
+          <t>Eriks</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>350 g</t>
+          <t>230 ml</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>214,29. kr/kg</t>
+          <t>86,96. kr/l</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
-          <t>1029878</t>
+          <t>1032298</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9d3d88965c7e37e2d7ba93d0412c9db7%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc0d902d9d1f5aadc9179fe5649056014&amp;w=252&amp;s=007f96363500f6f1f605f01e95ca10a9</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F988e68b0918858bbd1cb60af06ed50b6%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8c48223405c63dbd7b7dcffa03c67663%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F385eddfb6a96a3717db24d9527b9da14&amp;w=252&amp;s=c3937679391848c776a0cfdbb9bd4bd7</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>f4c80f17f23035ce</t>
+          <t>96b2694da4babab0</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -6795,7 +6749,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>1 æske</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -6807,41 +6761,41 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Coca-Cola, Fanta, Tuborg Squash eller San Pellegrino</t>
+          <t>Peka flødekartofler</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Coca-Cola,</t>
+          <t>Peka</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>100-150 cl</t>
+          <t>1500 g</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>13,00 kr/l</t>
+          <t>30,00. kr/kg</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1029596</t>
+          <t>1032297</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff46891c657bc10881f63e11db8bd8e96&amp;w=552&amp;s=b29a7d7117db3cfd6984e4704a17c68c</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4f21d3a0410b2b4c20fd41a75cc36127&amp;w=252&amp;s=fdec354c32f610f74c4b2b30470f179f</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>835c7ca34cc3a376</t>
+          <t>9664c76566669b19</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -6851,7 +6805,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -6863,43 +6817,31 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Powerade, State, Fun eller Scoop</t>
+          <t>Ølands-, græskar-solsikke eller spelt-chia surdejsbaguette*</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Powerade,</t>
+          <t>Ølands-,</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>50 cl</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>20,00. kr/l</t>
-        </is>
-      </c>
+          <t>. 1 stk</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>1029881</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F93e8d2bb60d97e4b639cc00125fa5917%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9e7766d598ceb56384e1d6d4049bf569%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbe3780762f5d39ef9f140fd1e6cd2a6a%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F41685b004eee5bf788394f14f3dac0bc&amp;w=252&amp;s=cb5b91c1537f6d662e1114260045cea8</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>de52393954443dad</t>
-        </is>
-      </c>
+          <t>1032301</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -6907,7 +6849,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -6919,43 +6861,31 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Coop hele kaffebønner</t>
+          <t>Onsdagssnegl*</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Onsdagssnegl*</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1000 g</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>125,00. kr/kg</t>
-        </is>
-      </c>
+          <t>. Stk</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>1029884</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F30e950054899a8ff86292219a0c7b529%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F15adc835c4d15b0c3eef9dec9404c20f&amp;w=252&amp;s=f95e8edd5989533d4f5b99b4b547d65c</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>c4c468336de8b3bc</t>
-        </is>
-      </c>
+          <t>1032300</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -6963,7 +6893,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>1 pose</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -6975,43 +6905,31 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Grimbergen, Jacobsen eller Leffe</t>
+          <t>Softkernerugbrød*</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Grimbergen,</t>
+          <t>Softkernerugbrød*</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>75 cl</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>32,00 kr/l</t>
-        </is>
-      </c>
+          <t>30,00. 1 stk</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>1029886</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F56c8a13155f426d5c0458c1742f93776%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb8c167cf8eb629cc847410e6c6073b7d%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F01244e613193fbfca35b2048857e7123%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F36faed86ac33f8f60bd1ad4344f260aa&amp;w=252&amp;s=f9ea4904f8e63656c867f379bd5d4208</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>aa5154ae11f4759b</t>
-        </is>
-      </c>
+          <t>1032303</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -7019,7 +6937,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -7031,43 +6949,31 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Carlsberg eller Tuborg 30 stk kasse</t>
+          <t>Dagmar- eller vandkringlestang*</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Carlsberg</t>
+          <t>Dagmar-</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>30 x 33 cl</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>14,14 kr/l</t>
-        </is>
-      </c>
+          <t>. 1 stk</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="n">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>1029888</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F797ee62bcb421309ec3b50f4f0291b2c%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Feb7709c9c944d1c5c5cbb8ca7fce0144%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F07824b34ad67dafce8cfdcec3e38ee89&amp;w=252&amp;s=ecfe55656531ea1975bf82cb5889ff8d</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>c76068333f1d64d9</t>
-        </is>
-      </c>
+          <t>1032305</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -7075,7 +6981,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>30 flasker</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -7087,41 +6993,41 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Monster Energy</t>
+          <t>Coop Asia cubes eller dumplings</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Monster</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>50 cl</t>
+          <t>320-350 g</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>28,00 kr/l</t>
+          <t>62,50. kr/kg</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>1029890</t>
+          <t>1032314</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1a69bfd8b961b89a22bac0e19ec829e0&amp;w=352&amp;s=5b9151a7f5577c3b7f8c7ffcab0ce18c</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff581625e8a342f4ac897e14e2d6822a9&amp;w=552&amp;s=0a6c370c43ba917e7f8dbdc536f6152a</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>ce66659b38383c39</t>
+          <t>ccbd736319602e99</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7131,7 +7037,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>1 dåse</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -7143,41 +7049,41 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Mokai, Shaker eller Royal Club</t>
+          <t>Coop bagels, croissanter eller Irma pitabrød</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Mokai,</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>27,5-33 cl</t>
+          <t>330-440 g</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>36,36 kr/l</t>
+          <t>60,61. kr/kg</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>1029891</t>
+          <t>1032308</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3513dd007038bebc205bb2d2b16fec00%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9bd6ead511a8ab3d1158779ff08dfdbf%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1093ef9f6107e1aa492d8d4db03d49e8%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F42c21c1b242c069eedfe224a668fae46&amp;w=352&amp;s=a21bc53a24fa3b37cb0a62b56de4d0bb</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F85f3106d4c6c546aac725ec8960f86ec&amp;w=552&amp;s=6d1905fa930f03b64d1fd4c2a23305a9</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>d16a261fe0e43b36</t>
+          <t>9a6d65cc318693ce</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7187,7 +7093,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -7199,37 +7105,41 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Merrild eller Lavazza formalet kaffe eller Merrild instant kaffe</t>
+          <t>Coop færdigret</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Merrild</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>3 stk</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
+          <t>300-400 g</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>66,67. kr/kg</t>
+        </is>
+      </c>
       <c r="F124" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>1050524</t>
+          <t>1032311</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc1a7ca15f5e327d16377d6dbbf34be63&amp;w=352&amp;s=c6e9a56ba7914454c5d541bef53f9bd5</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9e1da16dd557c87d08156b291dfa382d&amp;w=252&amp;s=8d9197c25dbd7a8bf86f3e758552cace</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>d06369692d9e1e96</t>
+          <t>93131ad08cc7cb6f</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7239,7 +7149,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>3 stk. pr.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -7251,31 +7161,43 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Fleece</t>
+          <t>Coop Kylling</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Fleece</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>1 stk</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
+          <t>350-1500 g</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>111,43. kr/kg</t>
+        </is>
+      </c>
       <c r="F125" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
-          <t>1029845</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
+          <t>1032307</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3ce72983cb84d346721b9561d732e5f8&amp;w=252&amp;s=29c8334e8f887c23dfee17616de96a7b</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>c16dcbc466b29369</t>
+        </is>
+      </c>
       <c r="K125" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -7295,35 +7217,41 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Mickis bagegrej</t>
+          <t>De Cecco pasta</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Mickis</t>
+          <t>De</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
+          <t>500 g</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>44,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>22</v>
+      </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>1029848</t>
+          <t>1032319</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5bccd0d022021e9251496cbe5782c13a&amp;w=552&amp;s=16f9617a827a0be7941d43b6d386bffa</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbccdd1a4a97bb1a6c93b9385fe1d5d00&amp;w=236&amp;s=f3ce185abbae5d9ad99e93222482db0f</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>ccdc3323ccdd146a</t>
+          <t>c4496e9b37b23067</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7331,7 +7259,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>1 pakke</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7341,35 +7273,41 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Cottonfield skjorte</t>
+          <t>Beauvais ketchup eller Heinz mayonnaise</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Cottonfield</t>
+          <t>Beauvais</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>1 stk</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>395-500 g</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>40,51. kr/kg</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>16</v>
+      </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
-          <t>1029862</t>
+          <t>1032327</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa9def59f1b75feb80dd91ce675bc7033&amp;w=160&amp;s=0c9bfb7e5729a854f9514805d5037a89</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbbd4f6c9994d41069470e32148174cd3&amp;w=352&amp;s=1530754d30c85651c64e531cc426c7ee</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>0000000000000000</t>
+          <t>916a66dc6a993917</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7391,31 +7329,41 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cottonfield bukser</t>
+          <t>Havrefras, Pauluns eller Nesquik morgenmad</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Cottonfield</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+          <t>Havrefras,</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>300-375 g</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>96,67. kr/kg</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>29</v>
+      </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1029858</t>
+          <t>1032325</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa9def59f1b75feb80dd91ce675bc7033&amp;w=160&amp;s=0c9bfb7e5729a854f9514805d5037a89</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fcc75c5fbc9928c4d2033a12a0801ce69%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0282210ae3d81e1e4c3a5763a504602e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F90f71e29fd933dfcbbc2baacc7ce2c3d&amp;w=752&amp;s=b023ef318e2fcb0804683eb84fb568ab</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>0000000000000000</t>
+          <t>8495e966855a3f72</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7425,7 +7373,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>1 par</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -7437,35 +7385,41 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Cottonfield shorts</t>
+          <t>Snackpot eller Reeva nudler</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Cottonfield</t>
+          <t>Snackpot</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>31-38. G</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
+          <t>58-75 g</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>172,41. kr/kg</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>10</v>
+      </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>1029853</t>
+          <t>1032321</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa9def59f1b75feb80dd91ce675bc7033&amp;w=160&amp;s=0c9bfb7e5729a854f9514805d5037a89</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1f34a0c079c535b1835ee54eb42ce927%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F30950d44c9893bb166b2d22515f6ceb5&amp;w=352&amp;s=0a4291687e62533c40a303123c0584fa</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>0000000000000000</t>
+          <t>95e82a424b17677b</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -7473,7 +7427,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>1 stk.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7483,31 +7441,41 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Boxer shorts 3-pak</t>
+          <t>Valsemøllen mel</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Boxer</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
+          <t>Valsemøllen</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>1700-2000 g</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>10,59. kr/kg</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>18</v>
+      </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
-          <t>1029860</t>
+          <t>1032323</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0ca4ab08a421537b996b82b95c844ee1&amp;w=373&amp;s=1d4d0c507ec0ba15d9fa234bee95d138</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F45245aa7cafc6008d35cd56b1f571c2e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F26c3bce03269f1b790b95f2e2dded4e6%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F94f8684603f324e946da60c1ac847f45&amp;w=352&amp;s=654e498e71ec907441d6023924ca2b77</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>d4710787f4f80e87</t>
+          <t>90a147f277639e4a</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7529,35 +7497,41 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Spar 30% på alle trolleys</t>
+          <t>Haribo, Minecraft, Twister, Champagnebrus eller Filur is</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spar</t>
+          <t>Haribo,</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
+          <t>300-400 ml</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>106,67. kr/l</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>32</v>
+      </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>1029863</t>
+          <t>1032317</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7b41452820b66c3a2c4214faea0acb8e&amp;w=1152&amp;s=1a373e859679be2499a9e7af96863739</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3bb0b1ce9b819ead9006103b4ac48978&amp;w=1152&amp;s=fdf095121d825afd1db7e2631cb2d027</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>d1376ed8429372d8</t>
+          <t>cf9e69903c613669</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7565,7 +7539,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr"/>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>1 pakke</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7575,35 +7553,41 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Big-T</t>
+          <t>Ritter Sport</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Big-T</t>
+          <t>Ritter</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>1 stk</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+          <t>100 g</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>150,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>15</v>
+      </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>1029865</t>
+          <t>1032335</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2e31948cb8be21784e1a6f78d70f17e3%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F21b7bda1141fb9cef8468b047a494501&amp;w=352&amp;s=b66b5367ff0a74a8de917cd4fcd45acc</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5c3b985750b52b08ac05e348cc91caea&amp;w=552&amp;s=56cc71570c3259676e2ff734018f7bf9</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>c7c478662a073d3b</t>
+          <t>924dc7276c6c3365</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7625,31 +7609,41 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Sloggi Zero Fell AIR</t>
+          <t>Kims chips</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Sloggi</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+          <t>Kims</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>75-95 g</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>136,84. kr/kg</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>13</v>
+      </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>1029874</t>
+          <t>1032328</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8b85b6093e273ddf30072a86128e3029&amp;w=104&amp;s=f335d6fd3f681043c31900f255c4af2a</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8dd6b48ae02256a81d443070b70eb83b%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F345f7631fc0ec8166fd84b331ae94a27%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0bed7d070350a742826c40e788c8c085%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa8423809ed43114a7b59626e9a14c79b&amp;w=552&amp;s=26826038cc1b9b889fd129754594c593</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>c6e92c26393e39d2</t>
+          <t>f96644be039d069d</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -7657,7 +7651,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>1 pose</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7667,35 +7665,41 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Kosmetiktaske</t>
+          <t>Panda lakrids</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Kosmetiktaske</t>
+          <t>Panda</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>1 stk</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
+          <t>175-200 g</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>102,86. kr/kg</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>18</v>
+      </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>1029871</t>
+          <t>1032330</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3ee261e16ca470f002c86c8a968788e5&amp;w=352&amp;s=d0eb0b23feec2a89e8d38bb72881a45a</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3c7e49722268778ba70212d46acd4460%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff2b91423719bc682e8ec1bd2b78aa726&amp;w=252&amp;s=001af68e63c467d49d231e7a288b952a</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>81157feb600bd716</t>
+          <t>91c47f7e449336b0</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -7705,7 +7709,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -7717,41 +7721,41 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Coop kartofler</t>
+          <t>Toms karameller</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Toms</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>4x400-1000 g</t>
+          <t>100-160 g</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>25,00. kr/kg</t>
+          <t>220,00. kr/kg</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
-          <t>1029887</t>
+          <t>1032332</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3069f6faa18d1c59b42ad054e437e3d8&amp;w=552&amp;s=65a3c38590a7244d577fff42d8f65b83</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2330f293d45af72debd3395d66e69182%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4cd6647a4fc03779eb695b809d41b1e3%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Febf0755cbc7cf738b709f7295ef50344&amp;w=252&amp;s=78a99d14bd749e85971bdca2cab602d5</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>93c93dcd3932343c</t>
+          <t>96b34bda344d60ec</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -7761,7 +7765,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>4 poser</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -7773,41 +7777,41 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Pakkemarked</t>
+          <t>Lindt Excellence chokolade</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Pakkemarked</t>
+          <t>Lindt</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>200-900 g</t>
+          <t>100 g</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>275,00. kr/kg</t>
+          <t>350,00. kr/kg</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
-          <t>1029889</t>
+          <t>1032334</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff9b7c0308fa5d4be2133b1b7895da9a7&amp;w=552&amp;s=2e3f3f7eb1aaa4d0d46c4e0a33e98ec5</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffa17f1fab0cb98d42f55636724d59223%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe60a0a06130a95b493e510fe95c31bbe%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F08e017a61d039ece6dd4f14583ad64ed&amp;w=252&amp;s=7663ac3ec0486b108096255491bd72a7</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>c2e53fc1c265869e</t>
+          <t>ace9711616e1ad8d</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -7817,7 +7821,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2 pakker</t>
+          <t>1 plade</t>
         </is>
       </c>
     </row>
@@ -7829,41 +7833,41 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Irma hummus, spreads eller oliven</t>
+          <t>M&amp;M's eller Maltesers</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>M&amp;M's</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>130-210 g</t>
+          <t>93-125 g</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>176,92. kr/kg</t>
+          <t>301,08. kr/kg</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>1053688</t>
+          <t>1032338</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9aa705cfdfc3dd40ba0b3e4501e58f2f&amp;w=1152&amp;s=80077a06a894c22ec5e38099a3a901c1</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd8fe0605bca67b79f79df39f4c798fc1%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F22691f7565912a8e280633d7cd61ef81%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb47cfcdca344d4f7d730e1779f8bf55d&amp;w=252&amp;s=d6d04e17983a0c02541f2471b47db75d</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>c1b479d834cd36d2</t>
+          <t>b5b25a9d4d48694b</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -7873,7 +7877,1963 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
+          <t>1 pose</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Coca-Cola, Tuborg Squash eller Monster</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Coca-Cola,</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>. 24 x 33 cl</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>19,75 kr/l</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>79</v>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>1032348</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9367eeb451f887222420fd3d05dbb8b1&amp;w=552&amp;s=8ef83f672ea1720f7bdf850713492225</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>c7336fc43e38086b</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>1 pakke</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Smirnoff</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Smirnoff</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>27,5 cl</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>47,27 kr/l</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>13</v>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>1032342</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc204450127c987e0a2dc615139740e6c%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2f8f90c27c5f0fe41ccc197a03a3a00b%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff0d878e996b891f0252e0b633cefd2f0&amp;w=236&amp;s=7f55e5e728c765805f59271787ee02ad</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>ad4152fa03b75b07</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>1 flaske</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Blandet saft, Cocio eller 16 Serien</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Blandet</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>. 60-100 cl</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>26,67. kr/l</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>16</v>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>1032353</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1a75ea076163d6cddb0fc6868664ec47&amp;w=252&amp;s=4ceb6463c4579cee6afac5c1cb209bce</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>c4b272b6e392e2c9</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>1 stk./flaske</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Faxe Kondi eller Pepsi Max</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Faxe</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>150 cl</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>12,00 kr/l</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>18</v>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>1032350</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd0bd1df678221fa74c9449b0c09216f0&amp;w=252&amp;s=43376f4b5feb82e39b2ac08c22a92204</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>f48701701d7f0e6e</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>1 flaske</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Kaiserdom, Oranjeboom eller Praga øl</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Kaiserdom,</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>50 cl</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>16,00 kr/l</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>8</v>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>1032340</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F14c38e90ab2e6791dad79baea5988e88&amp;w=252&amp;s=b60bcb51c8a34fcc5907b1f9ffbf6ac0</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>da87257964e4984f</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>1 dåse</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Corona, Leffe, Peroni eller Stella Artois øl</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Corona,</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>. 33 cl</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>36,36 kr/l</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>12</v>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>1032355</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4d51277a0dfa650baaf4212c70bb82bf&amp;w=252&amp;s=ad9064b46952dd01c9dc2c9dbec2a342</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>b1392dd6c6197a13</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>1 flaske/dåse</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1664, Carlsberg eller Tuborg øl</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>1664,</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>. 12-18 x 33 cl</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>22,47 kr/l</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>89</v>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>1032345</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5fb2cb78ae6e81779b3ba8e2ca16d9f5&amp;w=1152&amp;s=78420e93c7e6c3160e56ebfae0d2b811</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>d04861643d373fd3</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>1 pakke</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Whiskas menuboks eller tørkost</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Whiskas</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>800-1020 g</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>50,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>40</v>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>1032363</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7507f919eec60e502b127d1071208b32&amp;w=252&amp;s=4068aa337b6e6f24c42198a79c109204</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>90cc3c3acd6939a7</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>1 stk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Änglamark eller Coop Color vaskekapsler</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Änglamark</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="n">
+        <v>39</v>
+      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>1032357</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc49559a533a30044634e6adaca380d68%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffc3deeb63bdd2b141c92cb39d649610c&amp;w=252&amp;s=bafb594a39f187d9ae7df6401d6346cb</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>d4d6142f6f3e4823</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>1 stk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>A+ flydende vaske-middel eller kapsler</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>675 ml</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="n">
+        <v>27</v>
+      </c>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>1032359</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F568fabf752b06f7c1ccd8856fd0ee654&amp;w=343&amp;s=f996b38a30b2cf3f8646608aabf5b681</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>80e115e9f9167c9e</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>1 stk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Urban Spa håndæbe</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>300-500 ml</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>96,67. kr/l</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>29</v>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>1032369</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb4080f12a54dc31fdea134cf1ab20fca%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6096fa6d0a3ae1c7dbf0716031833320&amp;w=552&amp;s=8318b8e99c46ad642a236fe694def561</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>c45633633be8dcc8</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>1 stk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Änglamark håndopvask</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Änglamark</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>500 ml</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>18,00. kr/l</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>9</v>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>1032372</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3a3d575b4fbb667babf4046399bd2ddc&amp;w=129&amp;s=3e86d775810e3981b4c94a02e33fb3e2</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>c44f2e2f24bc74b4</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>1 stk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Domestos, Harpic toiletrengøring eller Bref blokke</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Domestos,</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>750 ml</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>400,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>15</v>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>1032374</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F311f7de2060d8d8e924aff6d27e7d7ae&amp;w=252&amp;s=96ff70458b992e6b1c537d4183ae3be4</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>e44f37a01d793133</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>1 stk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Always eller Tampax</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>16-60 stk</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>2,27. kr/stk</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>109</v>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>1032375</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7505403b8a4bcb3f2029de2717d4afc4&amp;w=252&amp;s=c0434f2f6e60412e5e7ecf2eef829ab0</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>805842b23be73fb3</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>3 pakker</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Livol eller Gerimax vitaminer</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Livol</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>80-150 stk</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>1,11. kr/stk</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>89</v>
+      </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>1032382</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8a8d2864ae1a9ccc4251e7986c92a9cd&amp;w=552&amp;s=316bf63c38fae7a44df0866d450a5445</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>ef65319a1a518e2d</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>1 stk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Kleenex</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Kleenex</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>56-72 stk</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>0,19. kr/stk</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>14</v>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>1032378</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa9abe7e675e43d817d027c2d24a91552%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F764e729fb48391b3ed7c6ee09818fcee%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6aa55d5b7210d408e56cb3aba16d1a27&amp;w=552&amp;s=b26b1a1280952b2601390fd4ae9f4b3b</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>d6e5291aac46c2f5</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>1 pakke</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Essence kurv str M</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Essence</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2 stk</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="n">
+        <v>30</v>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>1032362</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4599ca8db1f52a1e8b955e9cb4f16ebc%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe0c11f636ecb4899113d8fdaa0c789fa&amp;w=552&amp;s=771c6a04d212c62c0c63e020845b32e0</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>817a7d853a47698e</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2 stk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Indpakning</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Indpakning</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>, g</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="n">
+        <v>5</v>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>1032360</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbb6b21cf9c54434874e0ef4e7c05e630&amp;w=552&amp;s=84c494ed55b2e77185b78df42dfc367c</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>cecd3198663833ce</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>1 stk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Nakke- og skuldermassage</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Nakke-</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="n">
+        <v>399</v>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>1032364</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>1 stk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>OBH Nordica støvsuger</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>OBH</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>. L</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="n">
+        <v>699</v>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>1032370</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4c36185453b387c77e988dab9a0500fa&amp;w=214&amp;s=2c3275ee3b962afd11544bbc3a0854e8</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>cb1e30c92d714bcd</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>1 stk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Sjö strygerobot</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Sjö</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>-1 l</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="n">
+        <v>499</v>
+      </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>1032368</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8519bef5a4c780b2f8a5977ef21cd5ca&amp;w=552&amp;s=a275946ef5b89e41e8234c9a903400dd</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>9966319966799966</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Sjö husholdningsprodukter</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Sjö</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="n">
+        <v>99</v>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>1032373</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F30b40da706c72239dee649a83dd6a91c&amp;w=1152&amp;s=8016c39982f18ff213417d282201a037</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>91696a366966d6b4</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>1 stk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Leki Orange mobiltilbehør</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Leki</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>3 stk</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="n">
+        <v>100</v>
+      </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>1032377</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdfbdf3d6ca169f60df8d03228bbed721%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7f150f7f7e31e1004519c360620c4135%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F98f97e4844fcc74429b160cfa50929b3&amp;w=552&amp;s=6cd24750c0a36550ef0e65b816eb9ed3</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>94199936694ee1f9</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
           <t>3 stk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>25% rabat på alle print</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>1032376</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Ovnfaste fade</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Ovnfaste</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>1032386</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Udvalgte opbevaringsglas</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Udvalgte</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>200-1500 ml</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>1032385</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7b9d245863e5d29f1987e6edcc5a658e&amp;w=1152&amp;s=1e2d3677b53fd58d874ebb78ca00c8d8</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>c9993c9467c139bc</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Udvalgte Gastromax køkkenredskaber</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Udvalgte</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>1032388</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbe4176b465cbb9eaa7319ee66f781012&amp;w=1152&amp;s=ee17c69604190a18362583e4f1b806d5</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>d99999622667791c</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Opbevaringssæt 6-pak</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Opbevaringssæt</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2 x 500 ml</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="n">
+        <v>79</v>
+      </c>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>1032383</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F880557680fc5f735654372578a01a6d4&amp;w=343&amp;s=4db085654b5d0e55a15d6c522771a5cc</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>c81f7072798d34f1</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>1 sæt</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Klar til sommer</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Klar</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>128.  G</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="n">
+        <v>80</v>
+      </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>1032392</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=602&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff2411675331b4577005f65368bd434e2&amp;w=552&amp;s=0724f2a457bbc41a915a37a7328744c4</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>d12e2ed1eee3900e</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Bluey kjole</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Bluey</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>1 stk</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>1032389</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2cf274507a758766463f2bd7e00a54d5&amp;w=131&amp;s=ce9a826cc83b39784246999a7c98cd86</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>955a2e582ee125e7</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>1 stk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Bluey 3-pak hipster eller 2-pak boxershorts</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Bluey</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>1032393</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa93b1e5f88fa258b3a20a6c52833dc94&amp;w=1152&amp;s=51db888b3785d099c61bd48d48ddcb6e</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>84e80b17797d1774</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>1 pakke</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Sloggi Pure Comfort</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Sloggi</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>1032397</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd1aa829f25f4f7331f43856b2df9c1bd&amp;w=1152&amp;s=2767e8553062196bd4abf51342a83f45</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>9bcc74cc65316633</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Dameundertøj</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Dameundertøj</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>3 stk</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="n">
+        <v>149</v>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>1032396</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>3 stk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>EVA dameslippers</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>EVA</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>1032394</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8882fac3a7634bbfb1203ca9a3dfc590&amp;w=552&amp;s=45b35642568078c332252384efbf18a3</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>9d9b624572d69c0b</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>1 par</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Dreams, Gosh eller Kaos deospray</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Dreams,</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>150 ml</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>566,67. kr/l</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>85</v>
+      </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>1032398</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa420994c6b75e356fe6da0294d108a9f%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F18eff764342e595150406c8c226bf353%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F571efe16a7c29009bb4dda55b1f74fe7&amp;w=552&amp;s=59b981a1d26f0711f8bf8da28238671f</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>cf38383892c7c3c7</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>1 stk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Ribena</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Ribena</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>3 x 85 cl</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>27,06. kr/l</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>69</v>
+      </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>1032401</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F75347ae354784e9008f1f3778a01c554%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5b09cde4195e593e11ee54e2bfc62b7d%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4d51d3cfba7d26613c50927fb72c7a68&amp;w=251&amp;s=34100420548d0e8143b723477d1a3bfc</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>acc95236a97233ae</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>3 flasker</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>San Pellegrino</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>San</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>6x100 cl</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>10,00 kr/l</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>60</v>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>1032402</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5b957ae768be1db716b35d6aa306e4e2&amp;w=552&amp;s=0aa6dac213b0e80a8304cbfe025b3036</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>c26a3fd03fc278c2</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>6 flasker</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Avis</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Irma rejer</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>4x150 g</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>165,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>99</v>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>1032403</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=694&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3cff44ec878276625e94d33eddb83d25&amp;w=507&amp;s=6a349ad3605db5ca16ce34692d74e0ec</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>d0650ee83f9ee189</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>4 poser</t>
         </is>
       </c>
     </row>

--- a/Xlsx filer/Kvickly_produkter.xlsx
+++ b/Xlsx filer/Kvickly_produkter.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L175"/>
+  <dimension ref="A1:L142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1779,22 +1779,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Malaco, snøre eller stjerner</t>
+          <t>Knorr sauce eller fond du chef</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Malaco,</t>
+          <t>Knorr</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>. 92-120 g</t>
+          <t>57-112 g</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>108,70. kr/kg</t>
+          <t>175,44. kr/kg</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1803,17 +1803,17 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1032105</t>
+          <t>1032108</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0ff84dc7b20664488e6c69acefa03762&amp;w=552&amp;s=ff386998daab1dd328cf7bf1a57d542b</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F615057e95c90d626c42c121ef753c801&amp;w=552&amp;s=0160edda5cab3136112a74627abe4b80</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>d2ad435a2d5f7c20</t>
+          <t>96646d336f66360c</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1 pose</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -1835,22 +1835,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Knorr sauce eller fond du chef</t>
+          <t>Rahbek indbagt fisk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Knorr</t>
+          <t>Rahbek</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>57-112 g</t>
+          <t>250 g</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>175,44. kr/kg</t>
+          <t>44,25. kr/kg</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1859,17 +1859,17 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1032108</t>
+          <t>1032110</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F615057e95c90d626c42c121ef753c801&amp;w=552&amp;s=0160edda5cab3136112a74627abe4b80</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faef4c42a7897699f9634745451dc59a6%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4d5bfb2dd3c414311378a0dbbfb0b06a%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F00eb240608d79189922355ef0e7279cd&amp;w=552&amp;s=105a05290bb92aba6d17bbf2f03240c1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96646d336f66360c</t>
+          <t>9f75109a6d4ce5e0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1891,41 +1891,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rahbek indbagt fisk</t>
+          <t>Coop danske skoleagurker</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rahbek</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>250 g</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>44,25. kr/kg</t>
-        </is>
-      </c>
+          <t>3 stk</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
         <v>10</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1032110</t>
+          <t>1032112</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faef4c42a7897699f9634745451dc59a6%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4d5bfb2dd3c414311378a0dbbfb0b06a%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F00eb240608d79189922355ef0e7279cd&amp;w=552&amp;s=105a05290bb92aba6d17bbf2f03240c1</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9b301dadd46b99338d2852ef294848cc&amp;w=233&amp;s=d20647e8f104411b7f16b4aca42a5759</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>9f75109a6d4ce5e0</t>
+          <t>8b86f4a05f9a413f</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1935,7 +1931,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -1947,37 +1943,41 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Coop danske skoleagurker</t>
+          <t>Defco pålæg</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Defco</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3 stk</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>80 g</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>125,00. kr/kg</t>
+        </is>
+      </c>
       <c r="F28" t="n">
         <v>10</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1032112</t>
+          <t>1032114</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9b301dadd46b99338d2852ef294848cc&amp;w=233&amp;s=d20647e8f104411b7f16b4aca42a5759</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2378f56cdfb3b3eafc90f12e6bae2869&amp;w=190&amp;s=21979c6861fb3986c69eb6b570da0b19</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>8b86f4a05f9a413f</t>
+          <t>d2f652de09c0e9d8</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1 pose</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -1999,41 +1999,41 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Defco pålæg</t>
+          <t>Castello dessertost eller krans</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Defco</t>
+          <t>Castello</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>80 g</t>
+          <t>. 125-200 g</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>125,00. kr/kg</t>
+          <t>160,00. kr/kg</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1032114</t>
+          <t>1032121</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2378f56cdfb3b3eafc90f12e6bae2869&amp;w=190&amp;s=21979c6861fb3986c69eb6b570da0b19</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe3d58c1bf2e4dc61803b65e3ca5a2789&amp;w=552&amp;s=0eddeb212af9dab846c062f91c04effb</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>d2f652de09c0e9d8</t>
+          <t>cf72613c8c6639c6</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -2055,22 +2055,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Castello dessertost eller krans</t>
+          <t>Steff Houlberg bacon</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Castello</t>
+          <t>Steff</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>. 125-200 g</t>
+          <t>2 x 100 g</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>160,00. kr/kg</t>
+          <t>100,00. kr/kg</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -2079,17 +2079,17 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1032121</t>
+          <t>1032119</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe3d58c1bf2e4dc61803b65e3ca5a2789&amp;w=552&amp;s=0eddeb212af9dab846c062f91c04effb</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fba09fb385fdbdc8a69851abb8d735fcc&amp;w=552&amp;s=787462b9669daae1223ee376c52f616c</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>cf72613c8c6639c6</t>
+          <t>9b93666764989966</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -2111,22 +2111,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Steff Houlberg bacon</t>
+          <t>Coop Italiana eller Deep pan pizza</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Steff</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2 x 100 g</t>
+          <t>. 300-435 g</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>100,00. kr/kg</t>
+          <t>66,67. kr/kg</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -2135,17 +2135,17 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1032119</t>
+          <t>1032117</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fba09fb385fdbdc8a69851abb8d735fcc&amp;w=552&amp;s=787462b9669daae1223ee376c52f616c</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7e14e0f0e947c5fac887d7c6e2448363&amp;w=1152&amp;s=d41c33c345c626f0d2829e657ba41b9a</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>9b93666764989966</t>
+          <t>8731662e33c7333a</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -2167,22 +2167,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Coop Italiana eller Deep pan pizza</t>
+          <t>Änglamark økologiske bananer</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Änglamark</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>. 300-435 g</t>
+          <t>. 1,3 kg</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>66,67. kr/kg</t>
+          <t>15,38. kr/kg</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2191,17 +2191,17 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1032117</t>
+          <t>1032127</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7e14e0f0e947c5fac887d7c6e2448363&amp;w=1152&amp;s=d41c33c345c626f0d2829e657ba41b9a</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F96eb11229954b017af38fcdf24b06e09&amp;w=552&amp;s=f56bdbac4c4b4eb359e396dd1b100802</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>8731662e33c7333a</t>
+          <t>d4723a926b0d6d2d</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -2223,41 +2223,41 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Änglamark økologiske bananer</t>
+          <t>Coop hakket grisekød 4-7% eller 8-12%</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>. 1,3 kg</t>
+          <t>400-500 g</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>15,38. kr/kg</t>
+          <t>62,50. kr/kg</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1032127</t>
+          <t>1032123</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F96eb11229954b017af38fcdf24b06e09&amp;w=552&amp;s=f56bdbac4c4b4eb359e396dd1b100802</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4968afec4802c5f16a5128031f9ed672%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fae49081e9f4046821eceb0db64c5f31f&amp;w=552&amp;s=b1989cfe3632215dcae547639ce4251b</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>d4723a926b0d6d2d</t>
+          <t>af1158f0581f652f</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1 pose</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -2279,41 +2279,41 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Coop hakket grisekød 4-7% eller 8-12%</t>
+          <t>Cheasy hytteost</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Cheasy</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>400-500 g</t>
+          <t>500 g</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>62,50. kr/kg</t>
+          <t>40,00. kr/kg</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1032123</t>
+          <t>1032125</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4968afec4802c5f16a5128031f9ed672%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fae49081e9f4046821eceb0db64c5f31f&amp;w=552&amp;s=b1989cfe3632215dcae547639ce4251b</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4b0db11fd1f4040d73e61f11b40948de&amp;w=552&amp;s=dcc9281c22c88713778bf5aebcb953c4</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>af1158f0581f652f</t>
+          <t>cb93cc8433666e39</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -2335,41 +2335,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cheasy hytteost</t>
+          <t>Alt urtekram</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cheasy</t>
+          <t>Alt</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>500 g</t>
+          <t>l</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>40,00. kr/kg</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>20</v>
-      </c>
+          <t>247,91 kr/kg</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1032125</t>
+          <t>1032128</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4b0db11fd1f4040d73e61f11b40948de&amp;w=552&amp;s=dcc9281c22c88713778bf5aebcb953c4</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe3d170f12a5cb831fb7fcc717a79db99&amp;w=1152&amp;s=30aed8eb850eba15f401e02312e18630</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>cb93cc8433666e39</t>
+          <t>cf9c29ce234d2699</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2377,11 +2375,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>1 stk.</t>
-        </is>
-      </c>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2391,39 +2385,41 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Alt urtekram</t>
+          <t>Irma is</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alt</t>
+          <t>Irma</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>. 700 ml</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>247,91 kr/kg</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>64,29. kr/l</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>45</v>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1032128</t>
+          <t>1054532</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe3d170f12a5cb831fb7fcc717a79db99&amp;w=1152&amp;s=30aed8eb850eba15f401e02312e18630</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5bd3415daec45be286d3e4de97ecb494&amp;w=1152&amp;s=fae36a1f5bd752fb51f8c26256a459bd</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>cf9c29ce234d2699</t>
+          <t>9eb4793929696cc1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2441,41 +2437,41 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Irma is</t>
+          <t>Änglamark formalet eller hele kaffebønner</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>Änglamark</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>. 700 ml</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>64,29. kr/l</t>
+          <t>147,50. kr/kg</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1054532</t>
+          <t>1032132</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5bd3415daec45be286d3e4de97ecb494&amp;w=1152&amp;s=fae36a1f5bd752fb51f8c26256a459bd</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdfc40f7ced7e3228689b78741ff889cb&amp;w=552&amp;s=71679ba820ff9ba3ac31fbe5967b00f6</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>9eb4793929696cc1</t>
+          <t>c0e12fce2b8ff01a</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2483,7 +2479,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1 pose</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2493,41 +2493,41 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Änglamark formalet eller hele kaffebønner</t>
+          <t>Cirkel Kaffe eller Änglamark økologiske kaffekapsler</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>Cirkel</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>10 stk</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>147,50. kr/kg</t>
+          <t>2,00. kr/stk</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1032132</t>
+          <t>1032135</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdfc40f7ced7e3228689b78741ff889cb&amp;w=552&amp;s=71679ba820ff9ba3ac31fbe5967b00f6</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc433d822e198cb92b1b8b1e849a33e6a&amp;w=213&amp;s=82730b6bf6358cacf6d8688f6e0b628f</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>c0e12fce2b8ff01a</t>
+          <t>b32a52916c6cdb93</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1 pose</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cirkel Kaffe eller Änglamark økologiske kaffekapsler</t>
+          <t>Cirkel Kaffe hele kaffebønner</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2559,31 +2559,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10 stk</t>
+          <t>850-900 g</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2,00. kr/stk</t>
+          <t>151,76. kr/kg</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1032135</t>
+          <t>1032137</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc433d822e198cb92b1b8b1e849a33e6a&amp;w=213&amp;s=82730b6bf6358cacf6d8688f6e0b628f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F08e9b31c296ab716d9bd4c868e727632&amp;w=552&amp;s=e2041177b80427436ce83544791839b1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>b32a52916c6cdb93</t>
+          <t>999366cf3119ce98</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -2605,41 +2605,41 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cirkel Kaffe hele kaffebønner</t>
+          <t>Irma løs eller brevte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cirkel</t>
+          <t>Irma</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>850-900 g</t>
+          <t>200 g</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>151,76. kr/kg</t>
+          <t>125,00 kr/kg</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>129</v>
+        <v>29</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1032137</t>
+          <t>1032130</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F08e9b31c296ab716d9bd4c868e727632&amp;w=552&amp;s=e2041177b80427436ce83544791839b1</t>
+          <t>https://d3qnoxvhi29qvt.cloudfront.net/feed-images/19cbd31f54205d2f06a9668e3f74bcce</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>999366cf3119ce98</t>
+          <t>aa87f15b0aa5b586</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1 pose</t>
+          <t>1 pose/æske</t>
         </is>
       </c>
     </row>
@@ -2661,43 +2661,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Irma løs eller brevte</t>
+          <t>Nordicgrill Engangsgrill*</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>Nordicgrill</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>200 g</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>125,00 kr/kg</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>29</v>
-      </c>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1032130</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>https://d3qnoxvhi29qvt.cloudfront.net/feed-images/19cbd31f54205d2f06a9668e3f74bcce</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>aa87f15b0aa5b586</t>
-        </is>
-      </c>
+          <t>1032145</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -2705,7 +2691,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1 pose/æske</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -2717,31 +2703,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Spar op til 25% på udebelysning*</t>
+          <t>Nature 9 kg Grillbriketter*</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spar</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>9 kg</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1032141</t>
+          <t>1032144</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0eb3105543009e7aa57a594b34d8f24b&amp;w=552&amp;s=44e2729b1c5b2757f402e8ee3dc0ff5b</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffb2c08ac9827fe258ddf71ada9563b92&amp;w=252&amp;s=ffbca122b5362c63a5cccf2044f55d22</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>9264e5d21e6369e3</t>
+          <t>9e9b79c661666134</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2749,7 +2739,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1 pose</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2759,17 +2753,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nordicgrill Engangsgrill*</t>
+          <t>Køletasker i pastelfarver*</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nordicgrill</t>
+          <t>Køletasker</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>2 x 200 ml</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2777,21 +2771,25 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>1032145</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>1032147</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F04e0d9789524afd0574b522fbe3e172f&amp;w=252&amp;s=ec47208b3408effa6e8f601f9015744d</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>c5e47ab2620f3cc9</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>1 stk.</t>
-        </is>
-      </c>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2801,35 +2799,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nature 9 kg Grillbriketter*</t>
+          <t>BORNHOLMERGRISEN krogmodnet nakkefilet</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nature</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>9 kg</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+          <t>BORNHOLMERGRISEN</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>140,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>70</v>
+      </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1032144</t>
+          <t>1032163</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffb2c08ac9827fe258ddf71ada9563b92&amp;w=252&amp;s=ffbca122b5362c63a5cccf2044f55d22</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff20560f15884d35728d7e1bd1d358381&amp;w=552&amp;s=8c44b8891d08222a59887a45a748dab6</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>9e9b79c661666134</t>
+          <t>9b66676766990c4c</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2837,11 +2837,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>1 pose</t>
-        </is>
-      </c>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2851,35 +2847,37 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Køletasker i pastelfarver*</t>
+          <t>BORNHOLMERGRISEN filet a la mørbrad med paprika og hvidløg</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Køletasker</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2 x 200 ml</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+          <t>BORNHOLMERGRISEN</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>98,00. kr/kg</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>49</v>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1032147</t>
+          <t>1032161</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F04e0d9789524afd0574b522fbe3e172f&amp;w=252&amp;s=ec47208b3408effa6e8f601f9015744d</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb95e3014a5fd89fd3eb4621a127c921c&amp;w=552&amp;s=e6d922461c1d3c8e6cc164eacb7d2f86</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>c5e47ab2620f3cc9</t>
+          <t>96c3696178c36f34</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2897,37 +2895,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sistema Klip It opbevaringsbokse 10-pak*</t>
+          <t>Dansk Kalv mørbrad</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sistema</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>1 x 2 l</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
+          <t>Dansk</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>358,00. kr/kg</t>
+        </is>
+      </c>
       <c r="F46" t="n">
-        <v>99</v>
+        <v>179</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1032153</t>
+          <t>1032157</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F42ef74b689e2a4c79c26695f6a117550&amp;w=552&amp;s=df5b1854abb25c87a9e23e4afa6b67c3</t>
+          <t>https://d3qnoxvhi29qvt.cloudfront.net/feed-images/e2c89ea932a9eac03262a5a72afc3d5d</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>c1bc3a536e48bd61</t>
+          <t>98bffc500fe0d00f</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2935,11 +2933,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>1 sæt</t>
-        </is>
-      </c>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2949,37 +2943,37 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Hybrid pande*</t>
+          <t>Krogmodnet ribbensteg</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>. 1 stk</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>Krogmodnet</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>150,00. kr/kg</t>
+        </is>
+      </c>
       <c r="F47" t="n">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1032156</t>
+          <t>1032159</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe6cc84625d18d512e4ff3cf55792b49b&amp;w=252&amp;s=1fd12a8d4072b521b5896caf93686b8b</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9850a31a5d0d7ca3ccc56177109a7418&amp;w=395&amp;s=a3ccb53f16f84e7fa9391a9a7ee00bdc</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>cc9339386ecf3138</t>
+          <t>d2c32dbd4c6d98c2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2987,11 +2981,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>1 stk.</t>
-        </is>
-      </c>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3001,37 +2991,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fleecetæppe*</t>
+          <t>PremiuM oksecuvette</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fleecetæppe*</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>. 1 stk</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>PremiuM</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>158,00. kr/kg</t>
+        </is>
+      </c>
       <c r="F48" t="n">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1032154</t>
+          <t>1048620</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9eb8984327ccec53515e53be15a706b3&amp;w=252&amp;s=fad67d9446d51c2b3f16bc4db8fecab7</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa1c4dff93357541e0f67e53aba679aa3&amp;w=210&amp;s=1714ee1f6f3c67fb73292c2b2aede37b</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>c50f7a6424b333d5</t>
+          <t>9efa48a3258667cc</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3039,11 +3029,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>1 stk.</t>
-        </is>
-      </c>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3053,37 +3039,37 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BORNHOLMERGRISEN krogmodnet nakkefilet</t>
+          <t>PremiuM roastbeef, steak, tern eller strimler</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BORNHOLMERGRISEN</t>
+          <t>PremiuM</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>140,00. kr/kg</t>
+          <t>160,00. kr/kg</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1032163</t>
+          <t>1048621</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff20560f15884d35728d7e1bd1d358381&amp;w=552&amp;s=8c44b8891d08222a59887a45a748dab6</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdd27881b98a739d1bbff9d58d81036f6&amp;w=232&amp;s=005ee6a2c21511acdbed7485c3593cb5</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>9b66676766990c4c</t>
+          <t>c0d23b6d29653de4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3101,39 +3087,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BORNHOLMERGRISEN filet a la mørbrad med paprika og hvidløg</t>
+          <t>Grillmarked</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BORNHOLMERGRISEN</t>
+          <t>Grillmarked</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>98,00. kr/kg</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>49</v>
-      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1032161</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb95e3014a5fd89fd3eb4621a127c921c&amp;w=552&amp;s=e6d922461c1d3c8e6cc164eacb7d2f86</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>96c3696178c36f34</t>
-        </is>
-      </c>
+          <t>1032169</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -3149,37 +3121,41 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dansk Kalv mørbrad</t>
+          <t>Irma iberico presa, secreto eller kotelet med ben</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dansk</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>180-200 g</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>358,00. kr/kg</t>
+          <t>327,78. kr/kg</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>179</v>
+        <v>59</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1032157</t>
+          <t>1032165</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://d3qnoxvhi29qvt.cloudfront.net/feed-images/e2c89ea932a9eac03262a5a72afc3d5d</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7675d32f80c3e21d968c42ec5dc4ca94&amp;w=488&amp;s=2b424b37c2fac28b2e8dd53be733db4e</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>98bffc500fe0d00f</t>
+          <t>c1f41e6b6b3e4388</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3187,7 +3163,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>1 pakke</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3197,37 +3177,37 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Krogmodnet ribbensteg</t>
+          <t>Irma nyretapper af kødkvæg</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Krogmodnet</t>
+          <t>Irma</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>150,00. kr/kg</t>
+          <t>218,00. kr/kg</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1032159</t>
+          <t>1032171</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9850a31a5d0d7ca3ccc56177109a7418&amp;w=395&amp;s=a3ccb53f16f84e7fa9391a9a7ee00bdc</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F883306a46be3bd8725b5fc628d39bb7a&amp;w=466&amp;s=9ac0d688dc55d730631a6faa158c32f5</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>d2c32dbd4c6d98c2</t>
+          <t>c5b11e6c718719e3</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3245,37 +3225,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PremiuM oksecuvette</t>
+          <t>Spar 15% på Irma lam</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PremiuM</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>Spar</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>. Kg</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>158,00. kr/kg</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>79</v>
-      </c>
+          <t>509,92. kr/kg</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1048620</t>
+          <t>1048619</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa1c4dff93357541e0f67e53aba679aa3&amp;w=210&amp;s=1714ee1f6f3c67fb73292c2b2aede37b</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9270877f3e9145817dee2d1cc099db6a&amp;w=1152&amp;s=6c9701d8c81e0756a6f711c4919cc6f1</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>9efa48a3258667cc</t>
+          <t>936767141b669693</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3293,37 +3275,41 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PremiuM roastbeef, steak, tern eller strimler</t>
+          <t>Frijsenborg hakket kylling</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PremiuM</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Frijsenborg</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>800 g</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>160,00. kr/kg</t>
+          <t>68,75. kr/kg</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1048621</t>
+          <t>1032185</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdd27881b98a739d1bbff9d58d81036f6&amp;w=232&amp;s=005ee6a2c21511acdbed7485c3593cb5</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F11a796057a5696071c71ca393916e5ca&amp;w=1152&amp;s=9937b4d702c86765c35b1fc0e0120902</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>c0d23b6d29653de4</t>
+          <t>c7c365c731c6193c</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3331,7 +3317,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1 pakke</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3341,31 +3331,53 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Grillmarked</t>
+          <t>Coop koteletter, skinkeschnitzler eller stegeflæsk</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Grillmarked</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+          <t>Coop</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>400-500 g</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>97,50. kr/kg</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>39</v>
+      </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>1032169</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>1032178</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fad21a1ca970ff32ac6d8735ffd3d4786&amp;w=552&amp;s=04c7428c6b74164408c7ba4e888d10d0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>d6ce50340a9bad5b</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1 pakke</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3375,41 +3387,41 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Irma iberico presa, secreto eller kotelet med ben</t>
+          <t>Glyngøre laks eller rødspætte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>Glyngøre</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>180-200 g</t>
+          <t>225-250 g</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>327,78. kr/kg</t>
+          <t>200,00. kr/kg</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1032165</t>
+          <t>1032183</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7675d32f80c3e21d968c42ec5dc4ca94&amp;w=488&amp;s=2b424b37c2fac28b2e8dd53be733db4e</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa0c58b46fbce52b47359e1e0d7f8be5e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0536bfa39c8584e658c5510b330b62bc&amp;w=552&amp;s=b5cee90c905ee8c58fe49f860f130600</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>c1f41e6b6b3e4388</t>
+          <t>d1661be407581f6e</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3431,37 +3443,41 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Irma nyretapper af kødkvæg</t>
+          <t>Hakket oksekød 4-7%</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irma</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>Hakket</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>400 g</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>218,00. kr/kg</t>
+          <t>137,50. kr/kg</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>109</v>
+        <v>55</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1032171</t>
+          <t>1032180</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F883306a46be3bd8725b5fc628d39bb7a&amp;w=466&amp;s=9ac0d688dc55d730631a6faa158c32f5</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F232e0e257eb7685222265ee6c34eef52&amp;w=252&amp;s=89ced3ba1f45d9747f08a1e15476e167</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>c5b11e6c718719e3</t>
+          <t>ee3d33c744371270</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3469,7 +3485,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>1 pakke</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3479,39 +3499,41 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Spar 15% på Irma lam</t>
+          <t>Xtra! hel kylling</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spar</t>
+          <t>Xtra!</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>. Kg</t>
+          <t>1450 g</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>509,92. kr/kg</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
+          <t>33,79. kr/kg</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>49</v>
+      </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1048619</t>
+          <t>1032182</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9270877f3e9145817dee2d1cc099db6a&amp;w=1152&amp;s=6c9701d8c81e0756a6f711c4919cc6f1</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F84f0f95e59efa7f9971c54675b17588b&amp;w=252&amp;s=45ee796007562398eff3597948739c46</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>936767141b669693</t>
+          <t>c3366dc1341c3e9b</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3519,7 +3541,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>1 stk.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3529,41 +3555,41 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Frijsenborg hakket kylling</t>
+          <t>Ferske salsiccia</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Frijsenborg</t>
+          <t>Ferske</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>800 g</t>
+          <t>300 g</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>68,75. kr/kg</t>
+          <t>133,33. kr/kg</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1032185</t>
+          <t>1032190</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F11a796057a5696071c71ca393916e5ca&amp;w=1152&amp;s=9937b4d702c86765c35b1fc0e0120902</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F88d6ddd2caf5039598dd5fb6e7faabe8%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa5c1b24d79e827cb8b94c4df19bd75a1%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F28a4a762ed54457a5e71e370752f4685&amp;w=352&amp;s=77de94d4fd985401e08175485e4f1976</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>c7c365c731c6193c</t>
+          <t>d5b163f30fe422e0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3585,41 +3611,41 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Coop koteletter, skinkeschnitzler eller stegeflæsk</t>
+          <t>Flæskestegs sandwich med chilimayo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Flæskestegs</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>400-500 g</t>
+          <t>1 stk</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>97,50. kr/kg</t>
+          <t>45,00. kr/stk</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1032178</t>
+          <t>1032193</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fad21a1ca970ff32ac6d8735ffd3d4786&amp;w=552&amp;s=04c7428c6b74164408c7ba4e888d10d0</t>
+          <t>https://d3qnoxvhi29qvt.cloudfront.net/feed-images/0d14df138fea7e873d0eb4a8b2575ed2</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>d6ce50340a9bad5b</t>
+          <t>ebd00e43bc96e14e</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3629,7 +3655,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -3641,41 +3667,41 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Glyngøre laks eller rødspætte</t>
+          <t>Torsdagssmørrebrød</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Glyngøre</t>
+          <t>Torsdagssmørrebrød</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>225-250 g</t>
+          <t>1 stk</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>200,00. kr/kg</t>
+          <t>29,00. kr/stk</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1032183</t>
+          <t>1048623</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa0c58b46fbce52b47359e1e0d7f8be5e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0536bfa39c8584e658c5510b330b62bc&amp;w=552&amp;s=b5cee90c905ee8c58fe49f860f130600</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd55b1bc276e5724e1e2bc2903baea6e0&amp;w=558&amp;s=94e80f1158ebedadb95cd14b0aeb7bdf</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>d1661be407581f6e</t>
+          <t>d3917e6e1a5445d1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3685,7 +3711,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -3697,41 +3723,41 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Hakket oksekød 4-7%</t>
+          <t>Fredagsbøf</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hakket</t>
+          <t>Fredagsbøf</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>1 stk</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>137,50. kr/kg</t>
+          <t>300,00. kr/kg</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1032180</t>
+          <t>1032175</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F232e0e257eb7685222265ee6c34eef52&amp;w=252&amp;s=89ced3ba1f45d9747f08a1e15476e167</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd63f5e11ff65681ce516f2f65ce45bb2&amp;w=1152&amp;s=cc3b3feb288babde12d7ebc1bdd6bb48</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>ee3d33c744371270</t>
+          <t>d0990f663ea6615b</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3741,7 +3767,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -3753,41 +3779,37 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Xtra! hel kylling</t>
+          <t>Fredagstapas fra Delikatessen</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Xtra!</t>
+          <t>Fredagstapas</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1450 g</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>33,79. kr/kg</t>
-        </is>
-      </c>
+          <t>1 stk</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="n">
-        <v>49</v>
+        <v>165</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1032182</t>
+          <t>1032195</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F84f0f95e59efa7f9971c54675b17588b&amp;w=252&amp;s=45ee796007562398eff3597948739c46</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fab8d4dacd0ee58e026bf22c900bcb735&amp;w=558&amp;s=32ffefaf3f8336d907235d9a2141a599</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>c3366dc1341c3e9b</t>
+          <t>d8981f67051d2fe1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3809,41 +3831,41 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Maasdamer</t>
+          <t>Irma spisemoden avocado eller mango</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Maasdamer</t>
+          <t>Irma</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>450 g</t>
+          <t>2-3 stk</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>108,89. kr/kg</t>
+          <t>11,00. kr/stk</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1032188</t>
+          <t>1032202</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4c9c4596bc49346b2dee47ac8d1f2b7a&amp;w=163&amp;s=639990b7cc5ea1fcf063ec730347ccc2</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe87b5e7e30c28f93ae06b77e05a8ecb2&amp;w=552&amp;s=02a6eda63ba34af1dbc4cb5060de1338</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>99e4b99e27919607</t>
+          <t>855e4b845e932c5f</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3853,7 +3875,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 bakke</t>
         </is>
       </c>
     </row>
@@ -3865,41 +3887,41 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ferske salsiccia</t>
+          <t>Coop stor bakke blåbær</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ferske</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>300 g</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>133,33. kr/kg</t>
+          <t>97,50. kr/kg</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1032190</t>
+          <t>1032204</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F88d6ddd2caf5039598dd5fb6e7faabe8%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa5c1b24d79e827cb8b94c4df19bd75a1%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F28a4a762ed54457a5e71e370752f4685&amp;w=352&amp;s=77de94d4fd985401e08175485e4f1976</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F593d774b06a17b1f37a4196b9d197af5&amp;w=552&amp;s=3ad50f59f0ac58cf21b0d0bbdc413837</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>d5b163f30fe422e0</t>
+          <t>c667c34ccc716c65</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3909,7 +3931,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 bakke</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3943,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Flæskestegs sandwich med chilimayo</t>
+          <t>Dansk agurk</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Flæskestegs</t>
+          <t>Dansk</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3936,26 +3958,26 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>45,00. kr/stk</t>
+          <t>9,00. kr/stk</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1032193</t>
+          <t>1032199</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://d3qnoxvhi29qvt.cloudfront.net/feed-images/0d14df138fea7e873d0eb4a8b2575ed2</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7b148dea4aeb9084be9bc7c94d410fc7&amp;w=190&amp;s=e3f561b81f3c40702067714ea598c527</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>ebd00e43bc96e14e</t>
+          <t>a52b54d113edc437</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3977,41 +3999,41 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Torsdagssmørrebrød</t>
+          <t>Store conference pærer</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Torsdagssmørrebrød</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1 stk</t>
+          <t>Stk</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>29,00. kr/stk</t>
+          <t>22,00. kr/stk</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1048623</t>
+          <t>1032207</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd55b1bc276e5724e1e2bc2903baea6e0&amp;w=558&amp;s=94e80f1158ebedadb95cd14b0aeb7bdf</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9c216922794c7efc5d36bc9708e91dd9&amp;w=552&amp;s=87a96e32c9f7d34c1d044fcd1e82ccd8</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>d3917e6e1a5445d1</t>
+          <t>ce6c30936b33cc9a</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4021,7 +4043,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 bakke</t>
         </is>
       </c>
     </row>
@@ -4033,12 +4055,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Fredagsbøf</t>
+          <t>Honningmelon</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fredagsbøf</t>
+          <t>Honningmelon</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4048,26 +4070,26 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>300,00. kr/kg</t>
+          <t>22,00. kr/stk</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1032175</t>
+          <t>1032210</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd63f5e11ff65681ce516f2f65ce45bb2&amp;w=1152&amp;s=cc3b3feb288babde12d7ebc1bdd6bb48</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fab32a975ba7cddd2cc0063167b85aeb7&amp;w=552&amp;s=e0b6b04d19f9d659f5bb55ab561843c5</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>d0990f663ea6615b</t>
+          <t>cbc365cd3838666c</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4089,37 +4111,41 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fredagstapas fra Delikatessen</t>
+          <t>Änglamark økologiske æg</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fredagstapas</t>
+          <t>Änglamark</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1 stk</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
+          <t>10 stk</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2,90. kr/stk</t>
+        </is>
+      </c>
       <c r="F69" t="n">
-        <v>165</v>
+        <v>29</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1032195</t>
+          <t>1032222</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fab8d4dacd0ee58e026bf22c900bcb735&amp;w=558&amp;s=32ffefaf3f8336d907235d9a2141a599</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdfd533404e0fcd6ea8f876f52f6099ae&amp;w=1152&amp;s=2b761fcd83ec5e214c2f494fed42dce9</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>d8981f67051d2fe1</t>
+          <t>c56e6ec53991b113</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4129,7 +4155,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 bakke</t>
         </is>
       </c>
     </row>
@@ -4141,33 +4167,41 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Lun lørdag</t>
+          <t>Coop remoulade eller mayon-naise</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lun</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+          <t>Coop</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>400 g</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>30,00. kr/kg</t>
+        </is>
+      </c>
       <c r="F70" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1048622</t>
+          <t>1032213</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F71a15d0b00a901f096c51199e1305b6a&amp;w=539&amp;s=42fa7e797462795b0a4b1425ea4e0132</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F728461f3294429b3c7973790e1d52b43&amp;w=552&amp;s=13fe8ad8f919cb243c0ba356255304e0</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>d18d2d465a5e17d2</t>
+          <t>95c6426a2feb69c8</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4175,7 +4209,11 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>1 stk.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4185,31 +4223,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nakke- og skuldermassage</t>
+          <t>Poke bowls</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Nakke-</t>
+          <t>Poke</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>1 stk</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
-        <v>399</v>
+        <v>49</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1032364</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+          <t>1032224</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe41aa3658140cf67e1f335b8e2b9a4c8&amp;w=552&amp;s=923c32e5cd060ad4f1253373dbceeab4</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>ce666c663032399f</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -4229,41 +4275,41 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Irma spisemoden avocado eller mango</t>
+          <t>Kohberg brød</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Irma</t>
+          <t>Kohberg</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2-3 stk</t>
+          <t>320-1000 g</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>11,00. kr/stk</t>
+          <t>56,25. kr/kg</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1032202</t>
+          <t>1032220</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe87b5e7e30c28f93ae06b77e05a8ecb2&amp;w=552&amp;s=02a6eda63ba34af1dbc4cb5060de1338</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1765f3a5515e79c3c98e2ac7208a1dae&amp;w=252&amp;s=5305d0c50d2c3848d21b9aa4644f20cb</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>855e4b845e932c5f</t>
+          <t>92673ec76192c696</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4273,7 +4319,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>1 bakke</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4331,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Coop stor bakke blåbær</t>
+          <t>Coop røget-, gravad laks eller Kaptajnens fangst rejer</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4295,31 +4341,31 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>150-200 g</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>97,50. kr/kg</t>
+          <t>326,67. kr/kg</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1032204</t>
+          <t>1032215</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F593d774b06a17b1f37a4196b9d197af5&amp;w=552&amp;s=3ad50f59f0ac58cf21b0d0bbdc413837</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff60dfcc771d8d158886069fca9b5b4bc&amp;w=252&amp;s=693650eefccd27fa1cb8e49b6b8788e9</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>c667c34ccc716c65</t>
+          <t>c33e4c93619b2d6c</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4329,7 +4375,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>1 bakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -4341,41 +4387,41 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Dansk agurk</t>
+          <t>Beauvais survarer</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dansk</t>
+          <t>Beauvais</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1 stk</t>
+          <t>310-580 g</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>9,00. kr/stk</t>
+          <t>64,52. kr/kg</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1032199</t>
+          <t>1032217</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7b148dea4aeb9084be9bc7c94d410fc7&amp;w=190&amp;s=e3f561b81f3c40702067714ea598c527</t>
+          <t>https://d3qnoxvhi29qvt.cloudfront.net/feed-images/4c02f3f36a726ae49254ad5b103c1026</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>a52b54d113edc437</t>
+          <t>f693e572324d8847</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4385,7 +4431,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 glas</t>
         </is>
       </c>
     </row>
@@ -4397,41 +4443,41 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Store conference pærer</t>
+          <t>Änglamark økologiske nye kartofler</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Änglamark</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Stk</t>
+          <t>1 kg</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>22,00. kr/stk</t>
+          <t>16,00. kr/kg</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1032207</t>
+          <t>1032232</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9c216922794c7efc5d36bc9708e91dd9&amp;w=552&amp;s=87a96e32c9f7d34c1d044fcd1e82ccd8</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdd4871de6124a9bfe1bc3d4363ccf892&amp;w=552&amp;s=78052433816dbf079338e7f4f3d5442f</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>ce6c30936b33cc9a</t>
+          <t>80df7f1166a63aa8</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4441,7 +4487,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>1 bakke</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -4453,41 +4499,41 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Honningmelon</t>
+          <t>Änglamark økologiske ærter</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Honningmelon</t>
+          <t>Änglamark</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1 stk</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>22,00. kr/stk</t>
+          <t>37,50. kr/kg</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1032210</t>
+          <t>1032226</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fab32a975ba7cddd2cc0063167b85aeb7&amp;w=552&amp;s=e0b6b04d19f9d659f5bb55ab561843c5</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff85278e738d7cac2c5e5084d5540a6df&amp;w=552&amp;s=5ac04477e4c711a2b0cb21249709afc4</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>cbc365cd3838666c</t>
+          <t>c73c346d34cb32c3</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4497,7 +4543,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -4509,41 +4555,41 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dronning Ingrid Pelargonia</t>
+          <t>Coop kyllingebryst, -inderfilet eller -overlårsfilet med skind</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dronning</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Stk</t>
+          <t>300-400 g</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>25,00. kr/stk</t>
+          <t>96,67. kr/kg</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>1032211</t>
+          <t>1032229</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://d3qnoxvhi29qvt.cloudfront.net/feed-images/35c581b69836e512c2c6a28854742d12</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F842d6e8fc22e3f446f081a800b744321&amp;w=252&amp;s=4f78da7d03ca52d61cd7c8967dacd0fa</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>ea99957aa684d02f</t>
+          <t>95581f27e1e41ee1</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4553,7 +4599,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -4565,7 +4611,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Änglamark økologiske æg</t>
+          <t>Änglamark økologisk dansk persille</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4575,31 +4621,31 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>10 stk</t>
+          <t>320 g</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2,90. kr/stk</t>
+          <t>62,50. kr/kg</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1032222</t>
+          <t>1032231</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdfd533404e0fcd6ea8f876f52f6099ae&amp;w=1152&amp;s=2b761fcd83ec5e214c2f494fed42dce9</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F08c310326c045c88d0cf58bf331dc134&amp;w=252&amp;s=e7e1cefda627a6c7b8966b4304afb52e</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>c56e6ec53991b113</t>
+          <t>9ab62c4d6565656c</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4609,7 +4655,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>1 bakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -4621,41 +4667,45 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Coop remoulade eller mayon-naise</t>
+          <t>Torres Coronas eller Esmeralda i boks</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Torres</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>. 3 l</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>30,00. kr/kg</t>
+          <t>43,00. kr/l</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>12</v>
-      </c>
-      <c r="G79" t="inlineStr"/>
+        <v>129</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>229.00.</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1032213</t>
+          <t>1032240</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F728461f3294429b3c7973790e1d52b43&amp;w=552&amp;s=13fe8ad8f919cb243c0ba356255304e0</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F25c9be19b1c599db3b40be047b24a3bd%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F960bd451998a7bf60d468572ec2ae075%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5c73b5fd4085728657f38de1bc1a521f&amp;w=552&amp;s=e743733196effba1ea180d9eff5c6830</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>95c6426a2feb69c8</t>
+          <t>a3a25e5d6958a6a3</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4665,7 +4715,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 boks</t>
         </is>
       </c>
     </row>
@@ -4677,37 +4727,45 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Poke bowls</t>
+          <t>Cuvée Dissenay eller Grant Burge Reserve</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poke</t>
+          <t>Cuvée</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1 stk</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t>. 75 cl</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>66,67. kr/l</t>
+        </is>
+      </c>
       <c r="F80" t="n">
-        <v>49</v>
-      </c>
-      <c r="G80" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>99.95.</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1032224</t>
+          <t>1032234</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe41aa3658140cf67e1f335b8e2b9a4c8&amp;w=552&amp;s=923c32e5cd060ad4f1253373dbceeab4</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2e97af6cd698da8f035c454509520450&amp;w=552&amp;s=712c077e62da8e38722119cd8b84f2db</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>ce666c663032399f</t>
+          <t>9e32cd9a32cd31b2</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4717,7 +4775,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -4729,41 +4787,41 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Kohberg brød</t>
+          <t>Casillero del Diablo</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Kohberg</t>
+          <t>Casillero</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>320-1000 g</t>
+          <t>. 75 cl</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>56,25. kr/kg</t>
+          <t>53,33. kr/l</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1032220</t>
+          <t>1032236</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1765f3a5515e79c3c98e2ac7208a1dae&amp;w=252&amp;s=5305d0c50d2c3848d21b9aa4644f20cb</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F44f3e895aac9fd4dd021c86e3baa2681&amp;w=257&amp;s=c55be4d27ecf2f190d4e48eebfd4b875</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>92673ec76192c696</t>
+          <t>b44d30bacb374137</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4773,7 +4831,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -4785,41 +4843,45 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Coop røget-, gravad laks eller Kaptajnens fangst rejer</t>
+          <t>Outlaw Zin i boks</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Outlaw</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>150-200 g</t>
+          <t>. 3 l</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>326,67. kr/kg</t>
+          <t>38,33. kr/l</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>49</v>
-      </c>
-      <c r="G82" t="inlineStr"/>
+        <v>115</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>159.00.</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1032215</t>
+          <t>1032238</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff60dfcc771d8d158886069fca9b5b4bc&amp;w=252&amp;s=693650eefccd27fa1cb8e49b6b8788e9</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb12a98f013efc4c2d8357dc54365ef7f&amp;w=316&amp;s=9e33ab96a35aab1e3b61a1f390e3cdbe</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>c33e4c93619b2d6c</t>
+          <t>e7c708cc5d99c619</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4829,7 +4891,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 boks</t>
         </is>
       </c>
     </row>
@@ -4841,41 +4903,41 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Beauvais survarer</t>
+          <t>Ripasso Superiore Pagus Bisano</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Beauvais</t>
+          <t>Ripasso</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>310-580 g</t>
+          <t>. 6 x 75 cl</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>64,52. kr/kg</t>
+          <t>66,44. kr/l</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>20</v>
+        <v>299</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1032217</t>
+          <t>1032250</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://d3qnoxvhi29qvt.cloudfront.net/feed-images/4c02f3f36a726ae49254ad5b103c1026</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F47fbfccd1594d606ff1d4db2930039a2&amp;w=352&amp;s=060eec8d64c6397371a6f4a09948c037</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>f693e572324d8847</t>
+          <t>92194b87b4636f65</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -4885,7 +4947,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>1 glas</t>
+          <t>6 flasker</t>
         </is>
       </c>
     </row>
@@ -4897,41 +4959,41 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Änglamark økologiske nye kartofler</t>
+          <t>Vamos! eller Sandara Sparkling Rosé</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>Vamos!</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1 kg</t>
+          <t>. 75 cl</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>16,00. kr/kg</t>
+          <t>53,33. kr/l</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1032232</t>
+          <t>1032248</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdd4871de6124a9bfe1bc3d4363ccf892&amp;w=552&amp;s=78052433816dbf079338e7f4f3d5442f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=602&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F086eb849f38b15ade73e15cfcc8e4e95&amp;w=352&amp;s=ff6f9e3b8dd27a07ff07fa702aefbe44</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>80df7f1166a63aa8</t>
+          <t>944663316d9d4be9</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -4941,7 +5003,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>1 pose</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -4953,41 +5015,41 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Änglamark økologiske ærter</t>
+          <t>Piccini Zinfandel, Poeme Vineyards eller Fat Bastard Chardonnay</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>Piccini</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>. 75 cl</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>37,50. kr/kg</t>
+          <t>66,67. kr/l</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1032226</t>
+          <t>1032245</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff85278e738d7cac2c5e5084d5540a6df&amp;w=552&amp;s=5ac04477e4c711a2b0cb21249709afc4</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F23375553e5af78330787c767dcad56b9&amp;w=352&amp;s=a1d5b9f2485a8e6b91a9257bb8d5943e</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>c73c346d34cb32c3</t>
+          <t>926c39c3689c67b3</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -4997,7 +5059,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>1 pose</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -5009,41 +5071,45 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Coop kyllingebryst, -inderfilet eller -overlårsfilet med skind</t>
+          <t>Spier Private Collection</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Spier</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>300-400 g</t>
+          <t>. L</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>96,67. kr/kg</t>
+          <t>92,00. kr/l</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>29</v>
-      </c>
-      <c r="G86" t="inlineStr"/>
+        <v>69</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>129.95.</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1032229</t>
+          <t>1032242</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F842d6e8fc22e3f446f081a800b744321&amp;w=252&amp;s=4f78da7d03ca52d61cd7c8967dacd0fa</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F49fbecdde94fe59d4f008b81d92245c6&amp;w=352&amp;s=3ca99473d13f96dee4c35edd8f7f113f</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>95581f27e1e41ee1</t>
+          <t>926c3d92cdb26cc9</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5053,7 +5119,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -5065,41 +5131,41 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Änglamark økologisk dansk persille</t>
+          <t>Amarone Nino Ardevi eller Cattin Grand Cru</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Änglamark</t>
+          <t>Amarone</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>320 g</t>
+          <t>. 75 cl</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>62,50. kr/kg</t>
+          <t>132,00. kr/l</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1032231</t>
+          <t>1032257</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F08c310326c045c88d0cf58bf331dc134&amp;w=252&amp;s=e7e1cefda627a6c7b8966b4304afb52e</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbd37ce263915a96532b8cb69b7eb549b&amp;w=552&amp;s=792f5e450c53c05eb9ab9c92924412c0</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>9ab62c4d6565656c</t>
+          <t>824c31cf0ff14cfc</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5109,7 +5175,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -5121,45 +5187,41 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Torres Coronas eller Esmeralda i boks</t>
+          <t>Spier Heritage, Yealands Reserve Sauvignon Blanc eller Les Jablieres Côtes de Provence</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Torres</t>
+          <t>Spier</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>. 3 l</t>
+          <t>. 75 cl</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>43,00. kr/l</t>
+          <t>78,67. kr/l</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>129</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>229.00.</t>
-        </is>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1032240</t>
+          <t>1032255</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F25c9be19b1c599db3b40be047b24a3bd%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F960bd451998a7bf60d468572ec2ae075%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5c73b5fd4085728657f38de1bc1a521f&amp;w=552&amp;s=e743733196effba1ea180d9eff5c6830</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F33ca5ea8dfd9af14ee498581eed316ed&amp;w=223&amp;s=4d94234dd20e7ced7d5276a385efca4c</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>a3a25e5d6958a6a3</t>
+          <t>ac3432a633c771cd</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5169,7 +5231,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>1 boks</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5243,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cuvée Dissenay eller Grant Burge Reserve</t>
+          <t>Chateau Cap L'Ousteau, Laugel Pinot Gris eller GM par Gabriel Meffre Rosé</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cuvée</t>
+          <t>Chateau</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5196,30 +5258,26 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>66,67. kr/l</t>
+          <t>92,00. kr/l</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>50</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>99.95.</t>
-        </is>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1032234</t>
+          <t>1032253</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2e97af6cd698da8f035c454509520450&amp;w=552&amp;s=712c077e62da8e38722119cd8b84f2db</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=197&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9faaf7646d62283493497fc55d06eb5f&amp;w=252&amp;s=6c3746b57b647308b2d0905c49f68f31</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>9e32cd9a32cd31b2</t>
+          <t>926c6dc3388d36cd</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5241,12 +5299,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Casillero del Diablo</t>
+          <t>Torres Gran Coronas, Guigal Côtes-du-Rhône eller Moillard Cremant de Bourgogne</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Casillero</t>
+          <t>Torres</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5256,26 +5314,26 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>53,33. kr/l</t>
+          <t>118,67. kr/l</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1032236</t>
+          <t>1032251</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F44f3e895aac9fd4dd021c86e3baa2681&amp;w=257&amp;s=c55be4d27ecf2f190d4e48eebfd4b875</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=197&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1797f507c043a9e9f005f5600e45ecbd&amp;w=252&amp;s=7336cc1ad560fd8a85336291b41d8a64</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>b44d30bacb374137</t>
+          <t>96639686639c69b6</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5297,45 +5355,41 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Outlaw Zin i boks</t>
+          <t>Aalborg Taffel Akvavit, Poliakov Vodka eller Aalborg Rød Grød Shot</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Outlaw</t>
+          <t>Aalborg</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>. 3 l</t>
+          <t>70 cl</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>38,33. kr/l</t>
+          <t>112,86. kr/l</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>115</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>159.00.</t>
-        </is>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1032238</t>
+          <t>1032264</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb12a98f013efc4c2d8357dc54365ef7f&amp;w=316&amp;s=9e33ab96a35aab1e3b61a1f390e3cdbe</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe9501deaa11f9da26b2bd666d95cfd18%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdba54e5ef0711bb8e7e3c9832f06b5a7%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb7c734e0ce16658f4cf4b6bf2557c8f9&amp;w=552&amp;s=3bce0fe3ffeff29a55cc29630c2c1290</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>e7c708cc5d99c619</t>
+          <t>b16868c862f23f75</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5345,7 +5399,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>1 boks</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -5357,41 +5411,41 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ripasso Superiore Pagus Bisano</t>
+          <t>Jameson Whiskey, Hansen Rom, Dr. Nielsen Bitter, Tanqueray London Dry eller Flavoured Gin</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ripasso</t>
+          <t>Jameson</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>. 6 x 75 cl</t>
+          <t>70 cl</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>66,44. kr/l</t>
+          <t>170,00. kr/l</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>299</v>
+        <v>119</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1032250</t>
+          <t>1032262</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F47fbfccd1594d606ff1d4db2930039a2&amp;w=352&amp;s=060eec8d64c6397371a6f4a09948c037</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F143e5f0238ad315463083a065e63393b&amp;w=552&amp;s=730f1eebad1a548ef434033cbe503b37</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>92194b87b4636f65</t>
+          <t>cf69309e69326599</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5401,7 +5455,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>6 flasker</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -5413,41 +5467,41 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Vamos! eller Sandara Sparkling Rosé</t>
+          <t>Barolo Fontanafredda, Amarone Pagus Bisano, Morel Gigondas eller Laroche Chablis</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Vamos!</t>
+          <t>Barolo</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>. 75 cl</t>
+          <t>, G</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>53,33. kr/l</t>
+          <t>198,67. kr/l</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>40</v>
+        <v>149</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1032248</t>
+          <t>1032266</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=602&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F086eb849f38b15ade73e15cfcc8e4e95&amp;w=352&amp;s=ff6f9e3b8dd27a07ff07fa702aefbe44</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5bf8fa8968e5d75af2a1e7cde974757d&amp;w=552&amp;s=7ec4c655f3f78cb5f275aa2238d932b2</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>944663316d9d4be9</t>
+          <t>9b64cf9a30cf3186</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5469,41 +5523,41 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Piccini Zinfandel, Poeme Vineyards eller Fat Bastard Chardonnay</t>
+          <t>Normandin XO Cognac, Renault VSOP Cognac, Talisker 10 års eller Dalwhinnie 15 års Single Malt Whisky</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Piccini</t>
+          <t>Normandin</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>. 75 cl</t>
+          <t>70 cl</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>66,67. kr/l</t>
+          <t>370,00. kr/l</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>50</v>
+        <v>259</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1032245</t>
+          <t>1032260</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F23375553e5af78330787c767dcad56b9&amp;w=352&amp;s=a1d5b9f2485a8e6b91a9257bb8d5943e</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff495f5534fd293304c72fc2907a66d3f&amp;w=343&amp;s=c20a62e7bd705d1d00899b6f792c02ac</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>926c39c3689c67b3</t>
+          <t>b0506aba4fa5358f</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5525,45 +5579,41 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Spier Private Collection</t>
+          <t>Coop proteinshake</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spier</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>. L</t>
+          <t>500 g</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>92,00. kr/l</t>
+          <t>30,00. kr/kg</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>69</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>129.95.</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1032242</t>
+          <t>1032269</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F49fbecdde94fe59d4f008b81d92245c6&amp;w=352&amp;s=3ca99473d13f96dee4c35edd8f7f113f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbeaf71f6c8da5d4f435ccafc09097e50&amp;w=552&amp;s=0e20f04df9ba555db4b1a786180d7e1c</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>926c3d92cdb26cc9</t>
+          <t>9ace384c9b333333</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5573,7 +5623,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -5585,22 +5635,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Amarone Nino Ardevi eller Cattin Grand Cru</t>
+          <t>Bodylab proteinpulver eller creatin kapsler</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Amarone</t>
+          <t>Bodylab</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>. 75 cl</t>
+          <t>400 g</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>132,00. kr/l</t>
+          <t>237,50. kr/kg</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -5609,17 +5659,17 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1032257</t>
+          <t>1032273</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbd37ce263915a96532b8cb69b7eb549b&amp;w=552&amp;s=792f5e450c53c05eb9ab9c92924412c0</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faa0e5e6896c2ec0a7e5433edcdad54fe&amp;w=252&amp;s=80e1e4838899ee5cbe802758b7318214</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>824c31cf0ff14cfc</t>
+          <t>964933cd68696679</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5629,7 +5679,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -5641,41 +5691,41 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Spier Heritage, Yealands Reserve Sauvignon Blanc eller Les Jablieres Côtes de Provence</t>
+          <t>Thise økologisk aktiv yoghurt</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spier</t>
+          <t>Thise</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>. 75 cl</t>
+          <t>750 g</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>78,67. kr/l</t>
+          <t>20,00. kr/kg</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>1032255</t>
+          <t>1032275</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F33ca5ea8dfd9af14ee498581eed316ed&amp;w=223&amp;s=4d94234dd20e7ced7d5276a385efca4c</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7e93d2ca013495801149437c4f337db8&amp;w=252&amp;s=d7ee564021d2eab178c920b4c6ad8d18</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>ac3432a633c771cd</t>
+          <t>c2c3e1e369593936</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5685,7 +5735,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -5697,41 +5747,41 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Chateau Cap L'Ousteau, Laugel Pinot Gris eller GM par Gabriel Meffre Rosé</t>
+          <t>Stay Strong pro skyr</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chateau</t>
+          <t>Stay</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>. 75 cl</t>
+          <t>500 g</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>92,00. kr/l</t>
+          <t>30,00. kr/kg</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1032253</t>
+          <t>1032277</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=197&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9faaf7646d62283493497fc55d06eb5f&amp;w=252&amp;s=6c3746b57b647308b2d0905c49f68f31</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F80a0572d8976ff02703e64057e8d3aa1&amp;w=274&amp;s=d85bf00dcef16293e579c2df7f850832</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>926c6dc3388d36cd</t>
+          <t>d4f05fa3a54b1e0a</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5741,7 +5791,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -5753,41 +5803,41 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Torres Gran Coronas, Guigal Côtes-du-Rhône eller Moillard Cremant de Bourgogne</t>
+          <t>Arla eller Cheasy koldskål</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Torres</t>
+          <t>Arla</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>. 75 cl</t>
+          <t>1 l</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>118,67. kr/l</t>
+          <t>18,00. kr/l</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1032251</t>
+          <t>1032279</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=197&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1797f507c043a9e9f005f5600e45ecbd&amp;w=252&amp;s=7336cc1ad560fd8a85336291b41d8a64</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F21d4dfcafd3ae43fad3470cc7d2ba34d&amp;w=552&amp;s=f4bad87656fd986cac8ef360ed05cd37</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>96639686639c69b6</t>
+          <t>c4a10af40bf61bf6</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5797,7 +5847,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -5809,41 +5859,41 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Aalborg Taffel Akvavit, Poliakov Vodka eller Aalborg Rød Grød Shot</t>
+          <t>Président Brie eller Saint Morgon rødkit</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Aalborg</t>
+          <t>Président</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>70 cl</t>
+          <t>200 g</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>112,86. kr/l</t>
+          <t>140,00. kr/kg</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1032264</t>
+          <t>1032281</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe9501deaa11f9da26b2bd666d95cfd18%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdba54e5ef0711bb8e7e3c9832f06b5a7%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb7c734e0ce16658f4cf4b6bf2557c8f9&amp;w=552&amp;s=3bce0fe3ffeff29a55cc29630c2c1290</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fde57cf6c9c3f11f6fcecc9a7afee6b3d&amp;w=260&amp;s=60e6444287b44a80e2a1a225299715ea</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>b16868c862f23f75</t>
+          <t>c4c44beb1f242f1b</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -5853,7 +5903,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -5865,41 +5915,41 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Jameson Whiskey, Hansen Rom, Dr. Nielsen Bitter, Tanqueray London Dry eller Flavoured Gin</t>
+          <t>Them Fætter Kras skæreost</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jameson</t>
+          <t>Them</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>70 cl</t>
+          <t>. 450 g</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>170,00. kr/l</t>
+          <t>122,22. kr/kg</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>119</v>
+        <v>55</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1032262</t>
+          <t>1032284</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F143e5f0238ad315463083a065e63393b&amp;w=552&amp;s=730f1eebad1a548ef434033cbe503b37</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd6b18bfb1c1fa6eccee9cb1390dad49d&amp;w=252&amp;s=688d6637048917189e692b27f3680009</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>cf69309e69326599</t>
+          <t>c0c3c73cd6989b33</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -5909,7 +5959,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -5921,41 +5971,41 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Barolo Fontanafredda, Amarone Pagus Bisano, Morel Gigondas eller Laroche Chablis</t>
+          <t>Riberhus skiveost</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Barolo</t>
+          <t>Riberhus</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>, G</t>
+          <t>200-240 g</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>198,67. kr/l</t>
+          <t>145,00. kr/kg</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>149</v>
+        <v>29</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>1032266</t>
+          <t>1032286</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5bf8fa8968e5d75af2a1e7cde974757d&amp;w=552&amp;s=7ec4c655f3f78cb5f275aa2238d932b2</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F31a840cb8a5bce2c381aa01154011e9d&amp;w=252&amp;s=77aa83c8826b4c671c2f187ad65e5459</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>9b64cf9a30cf3186</t>
+          <t>c11b6af437353568</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -5965,7 +6015,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -5977,41 +6027,41 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Normandin XO Cognac, Renault VSOP Cognac, Talisker 10 års eller Dalwhinnie 15 års Single Malt Whisky</t>
+          <t>Coop dansk piskefløde</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Normandin</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>70 cl</t>
+          <t>500 ml</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>370,00. kr/l</t>
+          <t>40,00. kr/l</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>259</v>
+        <v>20</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>1032260</t>
+          <t>1032391</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff495f5534fd293304c72fc2907a66d3f&amp;w=343&amp;s=c20a62e7bd705d1d00899b6f792c02ac</t>
+          <t>https://d3qnoxvhi29qvt.cloudfront.net/feed-images/a625bbb17159f916dafa1b52a7584a9e</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>b0506aba4fa5358f</t>
+          <t>abf1947b1a64c19c</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6021,7 +6071,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -6033,41 +6083,41 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Coop proteinshake</t>
+          <t>Hanegal økologisk postej</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Hanegal</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>500 g</t>
+          <t>200 g</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>30,00. kr/kg</t>
+          <t>80,00. kr/kg</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1032269</t>
+          <t>1032293</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbeaf71f6c8da5d4f435ccafc09097e50&amp;w=552&amp;s=0e20f04df9ba555db4b1a786180d7e1c</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa75e687ee442a326dbf38132cf8b1606%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fad8e47f99bb6be477e88b675707447b1&amp;w=552&amp;s=b4ba9827e900802cc878acf0d99ee6b7</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>9ace384c9b333333</t>
+          <t>81683b7767116799</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6089,41 +6139,41 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LinusPro elektrolytter tabs</t>
+          <t>Coop fyldt pasta, gnocci eller pastasauce</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>LinusPro</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>20 stk</t>
+          <t>250-500 g</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1,00. kr/stk</t>
+          <t>72,00. kr/kg</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>1032271</t>
+          <t>1032295</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb4eb190b0ac0f3ceb7acbb03cf4bb5ee&amp;w=252&amp;s=21766ae8d6265d543dc9244c9d678bb0</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffd2885822175ab2e1cb4bf6b077d6634&amp;w=552&amp;s=dca688f0dcbe3d7b5f424b7687fdaf3e</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>bcda03e38383e38d</t>
+          <t>ca933999b3659992</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6133,7 +6183,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -6145,41 +6195,41 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Bodylab proteinpulver eller creatin kapsler</t>
+          <t>Eriks sauce</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bodylab</t>
+          <t>Eriks</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>400 g</t>
+          <t>230 ml</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>237,50. kr/kg</t>
+          <t>86,96. kr/l</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>1032273</t>
+          <t>1032298</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Faa0e5e6896c2ec0a7e5433edcdad54fe&amp;w=252&amp;s=80e1e4838899ee5cbe802758b7318214</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F988e68b0918858bbd1cb60af06ed50b6%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8c48223405c63dbd7b7dcffa03c67663%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F385eddfb6a96a3717db24d9527b9da14&amp;w=252&amp;s=c3937679391848c776a0cfdbb9bd4bd7</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>964933cd68696679</t>
+          <t>96b2694da4babab0</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6201,41 +6251,41 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Thise økologisk aktiv yoghurt</t>
+          <t>Peka flødekartofler</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Thise</t>
+          <t>Peka</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>750 g</t>
+          <t>1500 g</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>20,00. kr/kg</t>
+          <t>30,00. kr/kg</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>1032275</t>
+          <t>1032297</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7e93d2ca013495801149437c4f337db8&amp;w=252&amp;s=d7ee564021d2eab178c920b4c6ad8d18</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4f21d3a0410b2b4c20fd41a75cc36127&amp;w=252&amp;s=fdec354c32f610f74c4b2b30470f179f</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>c2c3e1e369593936</t>
+          <t>9664c76566669b19</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -6257,43 +6307,31 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Stay Strong pro skyr</t>
+          <t>Ølands-, græskar-solsikke eller spelt-chia surdejsbaguette*</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Stay</t>
+          <t>Ølands-,</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>500 g</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>30,00. kr/kg</t>
-        </is>
-      </c>
+          <t>. 1 stk</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1032277</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F80a0572d8976ff02703e64057e8d3aa1&amp;w=274&amp;s=d85bf00dcef16293e579c2df7f850832</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>d4f05fa3a54b1e0a</t>
-        </is>
-      </c>
+          <t>1032301</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -6313,43 +6351,31 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Arla eller Cheasy koldskål</t>
+          <t>Softkernerugbrød*</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Arla</t>
+          <t>Softkernerugbrød*</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>1 l</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>18,00. kr/l</t>
-        </is>
-      </c>
+          <t>30,00. 1 stk</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1032279</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F21d4dfcafd3ae43fad3470cc7d2ba34d&amp;w=552&amp;s=f4bad87656fd986cac8ef360ed05cd37</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>c4a10af40bf61bf6</t>
-        </is>
-      </c>
+          <t>1032303</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -6369,43 +6395,31 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Président Brie eller Saint Morgon rødkit</t>
+          <t>Dagmar- eller vandkringlestang*</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Président</t>
+          <t>Dagmar-</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>200 g</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>140,00. kr/kg</t>
-        </is>
-      </c>
+          <t>. 1 stk</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>1032281</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fde57cf6c9c3f11f6fcecc9a7afee6b3d&amp;w=260&amp;s=60e6444287b44a80e2a1a225299715ea</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>c4c44beb1f242f1b</t>
-        </is>
-      </c>
+          <t>1032305</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -6425,41 +6439,41 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Them Fætter Kras skæreost</t>
+          <t>Coop Asia cubes eller dumplings</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Them</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>. 450 g</t>
+          <t>320-350 g</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>122,22. kr/kg</t>
+          <t>62,50. kr/kg</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1032284</t>
+          <t>1032314</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd6b18bfb1c1fa6eccee9cb1390dad49d&amp;w=252&amp;s=688d6637048917189e692b27f3680009</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff581625e8a342f4ac897e14e2d6822a9&amp;w=552&amp;s=0a6c370c43ba917e7f8dbdc536f6152a</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>c0c3c73cd6989b33</t>
+          <t>ccbd736319602e99</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -6481,41 +6495,41 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Riberhus skiveost</t>
+          <t>Coop bagels, croissanter eller Irma pitabrød</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Riberhus</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>200-240 g</t>
+          <t>330-440 g</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>145,00. kr/kg</t>
+          <t>60,61. kr/kg</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
-          <t>1032286</t>
+          <t>1032308</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F31a840cb8a5bce2c381aa01154011e9d&amp;w=252&amp;s=77aa83c8826b4c671c2f187ad65e5459</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F85f3106d4c6c546aac725ec8960f86ec&amp;w=552&amp;s=6d1905fa930f03b64d1fd4c2a23305a9</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>c11b6af437353568</t>
+          <t>9a6d65cc318693ce</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6525,7 +6539,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6551,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Coop dansk piskefløde</t>
+          <t>Coop færdigret</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6547,12 +6561,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>500 ml</t>
+          <t>300-400 g</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>40,00. kr/l</t>
+          <t>66,67. kr/kg</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -6561,17 +6575,17 @@
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>1032391</t>
+          <t>1032311</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>https://d3qnoxvhi29qvt.cloudfront.net/feed-images/a625bbb17159f916dafa1b52a7584a9e</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9e1da16dd557c87d08156b291dfa382d&amp;w=252&amp;s=8d9197c25dbd7a8bf86f3e758552cace</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>abf1947b1a64c19c</t>
+          <t>93131ad08cc7cb6f</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6581,7 +6595,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -6593,41 +6607,41 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Hanegal økologisk postej</t>
+          <t>Coop Kylling</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hanegal</t>
+          <t>Coop</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>200 g</t>
+          <t>350-1500 g</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>80,00. kr/kg</t>
+          <t>111,43. kr/kg</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1032293</t>
+          <t>1032307</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa75e687ee442a326dbf38132cf8b1606%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fad8e47f99bb6be477e88b675707447b1&amp;w=552&amp;s=b4ba9827e900802cc878acf0d99ee6b7</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3ce72983cb84d346721b9561d732e5f8&amp;w=252&amp;s=29c8334e8f887c23dfee17616de96a7b</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>81683b7767116799</t>
+          <t>c16dcbc466b29369</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6649,41 +6663,41 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Coop fyldt pasta, gnocci eller pastasauce</t>
+          <t>De Cecco pasta</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>De</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>250-500 g</t>
+          <t>500 g</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>72,00. kr/kg</t>
+          <t>44,00. kr/kg</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
-          <t>1032295</t>
+          <t>1032319</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffd2885822175ab2e1cb4bf6b077d6634&amp;w=552&amp;s=dca688f0dcbe3d7b5f424b7687fdaf3e</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbccdd1a4a97bb1a6c93b9385fe1d5d00&amp;w=236&amp;s=f3ce185abbae5d9ad99e93222482db0f</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>ca933999b3659992</t>
+          <t>c4496e9b37b23067</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6705,41 +6719,41 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Eriks sauce</t>
+          <t>Beauvais ketchup eller Heinz mayonnaise</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Eriks</t>
+          <t>Beauvais</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>230 ml</t>
+          <t>395-500 g</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>86,96. kr/l</t>
+          <t>40,51. kr/kg</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
-          <t>1032298</t>
+          <t>1032327</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F988e68b0918858bbd1cb60af06ed50b6%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8c48223405c63dbd7b7dcffa03c67663%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F385eddfb6a96a3717db24d9527b9da14&amp;w=252&amp;s=c3937679391848c776a0cfdbb9bd4bd7</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbbd4f6c9994d41069470e32148174cd3&amp;w=352&amp;s=1530754d30c85651c64e531cc426c7ee</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>96b2694da4babab0</t>
+          <t>916a66dc6a993917</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -6761,41 +6775,41 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Peka flødekartofler</t>
+          <t>Havrefras, Pauluns eller Nesquik morgenmad</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Peka</t>
+          <t>Havrefras,</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>1500 g</t>
+          <t>300-375 g</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>30,00. kr/kg</t>
+          <t>96,67. kr/kg</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1032297</t>
+          <t>1032325</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4f21d3a0410b2b4c20fd41a75cc36127&amp;w=252&amp;s=fdec354c32f610f74c4b2b30470f179f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fcc75c5fbc9928c4d2033a12a0801ce69%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0282210ae3d81e1e4c3a5763a504602e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F90f71e29fd933dfcbbc2baacc7ce2c3d&amp;w=752&amp;s=b023ef318e2fcb0804683eb84fb568ab</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>9664c76566669b19</t>
+          <t>8495e966855a3f72</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -6805,7 +6819,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -6817,31 +6831,43 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ølands-, græskar-solsikke eller spelt-chia surdejsbaguette*</t>
+          <t>Snackpot eller Reeva nudler</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ølands-,</t>
+          <t>Snackpot</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>. 1 stk</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>58-75 g</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>172,41. kr/kg</t>
+        </is>
+      </c>
       <c r="F118" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>1032301</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
+          <t>1032321</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1f34a0c079c535b1835ee54eb42ce927%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F30950d44c9893bb166b2d22515f6ceb5&amp;w=352&amp;s=0a4291687e62533c40a303123c0584fa</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>95e82a424b17677b</t>
+        </is>
+      </c>
       <c r="K118" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -6861,31 +6887,43 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Onsdagssnegl*</t>
+          <t>Valsemøllen mel</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Onsdagssnegl*</t>
+          <t>Valsemøllen</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>. Stk</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+          <t>1700-2000 g</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>10,59. kr/kg</t>
+        </is>
+      </c>
       <c r="F119" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>1032300</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
+          <t>1032323</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F45245aa7cafc6008d35cd56b1f571c2e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F26c3bce03269f1b790b95f2e2dded4e6%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F94f8684603f324e946da60c1ac847f45&amp;w=352&amp;s=654e498e71ec907441d6023924ca2b77</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>90a147f277639e4a</t>
+        </is>
+      </c>
       <c r="K119" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -6893,7 +6931,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -6905,31 +6943,43 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Softkernerugbrød*</t>
+          <t>Haribo, Minecraft, Twister, Champagnebrus eller Filur is</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Softkernerugbrød*</t>
+          <t>Haribo,</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>30,00. 1 stk</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>300-400 ml</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>106,67. kr/l</t>
+        </is>
+      </c>
       <c r="F120" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>1032303</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
+          <t>1032317</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3bb0b1ce9b819ead9006103b4ac48978&amp;w=1152&amp;s=fdf095121d825afd1db7e2631cb2d027</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>cf9e69903c613669</t>
+        </is>
+      </c>
       <c r="K120" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -6937,7 +6987,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -6949,31 +6999,43 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Dagmar- eller vandkringlestang*</t>
+          <t>Ritter Sport</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Dagmar-</t>
+          <t>Ritter</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>. 1 stk</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>100 g</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>150,00. kr/kg</t>
+        </is>
+      </c>
       <c r="F121" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>1032305</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
+          <t>1032335</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5c3b985750b52b08ac05e348cc91caea&amp;w=552&amp;s=56cc71570c3259676e2ff734018f7bf9</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>924dc7276c6c3365</t>
+        </is>
+      </c>
       <c r="K121" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -6993,41 +7055,41 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Coop Asia cubes eller dumplings</t>
+          <t>Kims chips</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Kims</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>320-350 g</t>
+          <t>75-95 g</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>62,50. kr/kg</t>
+          <t>136,84. kr/kg</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>1032314</t>
+          <t>1032328</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff581625e8a342f4ac897e14e2d6822a9&amp;w=552&amp;s=0a6c370c43ba917e7f8dbdc536f6152a</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8dd6b48ae02256a81d443070b70eb83b%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F345f7631fc0ec8166fd84b331ae94a27%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0bed7d070350a742826c40e788c8c085%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa8423809ed43114a7b59626e9a14c79b&amp;w=552&amp;s=26826038cc1b9b889fd129754594c593</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>ccbd736319602e99</t>
+          <t>f96644be039d069d</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7037,7 +7099,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -7049,41 +7111,41 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Coop bagels, croissanter eller Irma pitabrød</t>
+          <t>Panda lakrids</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Panda</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>330-440 g</t>
+          <t>175-200 g</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>60,61. kr/kg</t>
+          <t>102,86. kr/kg</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>1032308</t>
+          <t>1032330</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F85f3106d4c6c546aac725ec8960f86ec&amp;w=552&amp;s=6d1905fa930f03b64d1fd4c2a23305a9</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3c7e49722268778ba70212d46acd4460%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff2b91423719bc682e8ec1bd2b78aa726&amp;w=252&amp;s=001af68e63c467d49d231e7a288b952a</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>9a6d65cc318693ce</t>
+          <t>91c47f7e449336b0</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7093,7 +7155,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -7105,41 +7167,41 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Coop færdigret</t>
+          <t>Toms karameller</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Toms</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>300-400 g</t>
+          <t>100-160 g</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>66,67. kr/kg</t>
+          <t>220,00. kr/kg</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>1032311</t>
+          <t>1032332</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9e1da16dd557c87d08156b291dfa382d&amp;w=252&amp;s=8d9197c25dbd7a8bf86f3e758552cace</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2330f293d45af72debd3395d66e69182%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4cd6647a4fc03779eb695b809d41b1e3%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Febf0755cbc7cf738b709f7295ef50344&amp;w=252&amp;s=78a99d14bd749e85971bdca2cab602d5</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>93131ad08cc7cb6f</t>
+          <t>96b34bda344d60ec</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7149,7 +7211,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -7161,41 +7223,41 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Coop Kylling</t>
+          <t>Lindt Excellence chokolade</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Coop</t>
+          <t>Lindt</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>350-1500 g</t>
+          <t>100 g</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>111,43. kr/kg</t>
+          <t>350,00. kr/kg</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
-          <t>1032307</t>
+          <t>1032334</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3ce72983cb84d346721b9561d732e5f8&amp;w=252&amp;s=29c8334e8f887c23dfee17616de96a7b</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffa17f1fab0cb98d42f55636724d59223%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe60a0a06130a95b493e510fe95c31bbe%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F08e017a61d039ece6dd4f14583ad64ed&amp;w=252&amp;s=7663ac3ec0486b108096255491bd72a7</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>c16dcbc466b29369</t>
+          <t>ace9711616e1ad8d</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7205,7 +7267,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 plade</t>
         </is>
       </c>
     </row>
@@ -7217,41 +7279,41 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>De Cecco pasta</t>
+          <t>M&amp;M's eller Maltesers</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>De</t>
+          <t>M&amp;M's</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>500 g</t>
+          <t>93-125 g</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>44,00. kr/kg</t>
+          <t>301,08. kr/kg</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>1032319</t>
+          <t>1032338</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbccdd1a4a97bb1a6c93b9385fe1d5d00&amp;w=236&amp;s=f3ce185abbae5d9ad99e93222482db0f</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd8fe0605bca67b79f79df39f4c798fc1%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F22691f7565912a8e280633d7cd61ef81%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb47cfcdca344d4f7d730e1779f8bf55d&amp;w=252&amp;s=d6d04e17983a0c02541f2471b47db75d</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>c4496e9b37b23067</t>
+          <t>b5b25a9d4d48694b</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7261,7 +7323,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 pose</t>
         </is>
       </c>
     </row>
@@ -7273,41 +7335,41 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Beauvais ketchup eller Heinz mayonnaise</t>
+          <t>Coca-Cola, Tuborg Squash eller Monster</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Beauvais</t>
+          <t>Coca-Cola,</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>395-500 g</t>
+          <t>. 24 x 33 cl</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>40,51. kr/kg</t>
+          <t>19,75 kr/l</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
-          <t>1032327</t>
+          <t>1032348</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbbd4f6c9994d41069470e32148174cd3&amp;w=352&amp;s=1530754d30c85651c64e531cc426c7ee</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9367eeb451f887222420fd3d05dbb8b1&amp;w=552&amp;s=8ef83f672ea1720f7bdf850713492225</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>916a66dc6a993917</t>
+          <t>c7336fc43e38086b</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7317,7 +7379,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -7329,41 +7391,41 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Havrefras, Pauluns eller Nesquik morgenmad</t>
+          <t>Smirnoff</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Havrefras,</t>
+          <t>Smirnoff</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>300-375 g</t>
+          <t>27,5 cl</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>96,67. kr/kg</t>
+          <t>47,27 kr/l</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1032325</t>
+          <t>1032342</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fcc75c5fbc9928c4d2033a12a0801ce69%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0282210ae3d81e1e4c3a5763a504602e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F90f71e29fd933dfcbbc2baacc7ce2c3d&amp;w=752&amp;s=b023ef318e2fcb0804683eb84fb568ab</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc204450127c987e0a2dc615139740e6c%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2f8f90c27c5f0fe41ccc197a03a3a00b%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff0d878e996b891f0252e0b633cefd2f0&amp;w=236&amp;s=7f55e5e728c765805f59271787ee02ad</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>8495e966855a3f72</t>
+          <t>ad4152fa03b75b07</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7373,7 +7435,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -7385,41 +7447,41 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Snackpot eller Reeva nudler</t>
+          <t>Blandet saft, Cocio eller 16 Serien</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Snackpot</t>
+          <t>Blandet</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>58-75 g</t>
+          <t>. 60-100 cl</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>172,41. kr/kg</t>
+          <t>26,67. kr/l</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>1032321</t>
+          <t>1032353</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1f34a0c079c535b1835ee54eb42ce927%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F30950d44c9893bb166b2d22515f6ceb5&amp;w=352&amp;s=0a4291687e62533c40a303123c0584fa</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1a75ea076163d6cddb0fc6868664ec47&amp;w=252&amp;s=4ceb6463c4579cee6afac5c1cb209bce</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>95e82a424b17677b</t>
+          <t>c4b272b6e392e2c9</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -7429,7 +7491,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 stk./flaske</t>
         </is>
       </c>
     </row>
@@ -7441,22 +7503,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Valsemøllen mel</t>
+          <t>Faxe Kondi eller Pepsi Max</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Valsemøllen</t>
+          <t>Faxe</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>1700-2000 g</t>
+          <t>150 cl</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>10,59. kr/kg</t>
+          <t>12,00 kr/l</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -7465,17 +7527,17 @@
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
-          <t>1032323</t>
+          <t>1032350</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F45245aa7cafc6008d35cd56b1f571c2e%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F26c3bce03269f1b790b95f2e2dded4e6%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F94f8684603f324e946da60c1ac847f45&amp;w=352&amp;s=654e498e71ec907441d6023924ca2b77</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd0bd1df678221fa74c9449b0c09216f0&amp;w=252&amp;s=43376f4b5feb82e39b2ac08c22a92204</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>90a147f277639e4a</t>
+          <t>f48701701d7f0e6e</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7485,7 +7547,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 flaske</t>
         </is>
       </c>
     </row>
@@ -7497,41 +7559,41 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Haribo, Minecraft, Twister, Champagnebrus eller Filur is</t>
+          <t>Kaiserdom, Oranjeboom eller Praga øl</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Haribo,</t>
+          <t>Kaiserdom,</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>300-400 ml</t>
+          <t>50 cl</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>106,67. kr/l</t>
+          <t>16,00 kr/l</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>1032317</t>
+          <t>1032340</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3bb0b1ce9b819ead9006103b4ac48978&amp;w=1152&amp;s=fdf095121d825afd1db7e2631cb2d027</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F14c38e90ab2e6791dad79baea5988e88&amp;w=252&amp;s=b60bcb51c8a34fcc5907b1f9ffbf6ac0</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>cf9e69903c613669</t>
+          <t>da87257964e4984f</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7541,7 +7603,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>1 pakke</t>
+          <t>1 dåse</t>
         </is>
       </c>
     </row>
@@ -7553,41 +7615,41 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ritter Sport</t>
+          <t>Corona, Leffe, Peroni eller Stella Artois øl</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ritter</t>
+          <t>Corona,</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>100 g</t>
+          <t>. 33 cl</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>150,00. kr/kg</t>
+          <t>36,36 kr/l</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>1032335</t>
+          <t>1032355</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5c3b985750b52b08ac05e348cc91caea&amp;w=552&amp;s=56cc71570c3259676e2ff734018f7bf9</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4d51277a0dfa650baaf4212c70bb82bf&amp;w=252&amp;s=ad9064b46952dd01c9dc2c9dbec2a342</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>924dc7276c6c3365</t>
+          <t>b1392dd6c6197a13</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7597,7 +7659,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>1 stk.</t>
+          <t>1 flaske/dåse</t>
         </is>
       </c>
     </row>
@@ -7609,41 +7671,41 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Kims chips</t>
+          <t>1664, Carlsberg eller Tuborg øl</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Kims</t>
+          <t>1664,</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>75-95 g</t>
+          <t>. 12-18 x 33 cl</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>136,84. kr/kg</t>
+          <t>22,47 kr/l</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>1032328</t>
+          <t>1032345</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8dd6b48ae02256a81d443070b70eb83b%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F345f7631fc0ec8166fd84b331ae94a27%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F0bed7d070350a742826c40e788c8c085%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa8423809ed43114a7b59626e9a14c79b&amp;w=552&amp;s=26826038cc1b9b889fd129754594c593</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5fb2cb78ae6e81779b3ba8e2ca16d9f5&amp;w=1152&amp;s=78420e93c7e6c3160e56ebfae0d2b811</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>f96644be039d069d</t>
+          <t>d04861643d373fd3</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -7653,7 +7715,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>1 pose</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -7665,41 +7727,41 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Panda lakrids</t>
+          <t>Whiskas menuboks eller tørkost</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Panda</t>
+          <t>Whiskas</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>175-200 g</t>
+          <t>800-1020 g</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>102,86. kr/kg</t>
+          <t>50,00. kr/kg</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>1032330</t>
+          <t>1032363</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3c7e49722268778ba70212d46acd4460%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff2b91423719bc682e8ec1bd2b78aa726&amp;w=252&amp;s=001af68e63c467d49d231e7a288b952a</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7507f919eec60e502b127d1071208b32&amp;w=252&amp;s=4068aa337b6e6f24c42198a79c109204</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>91c47f7e449336b0</t>
+          <t>90cc3c3acd6939a7</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -7709,7 +7771,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>1 pose</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -7721,41 +7783,41 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Toms karameller</t>
+          <t>Always eller Tampax</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Toms</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>100-160 g</t>
+          <t>16-60 stk</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>220,00. kr/kg</t>
+          <t>2,27. kr/stk</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>22</v>
+        <v>109</v>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
-          <t>1032332</t>
+          <t>1032375</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2330f293d45af72debd3395d66e69182%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4cd6647a4fc03779eb695b809d41b1e3%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Febf0755cbc7cf738b709f7295ef50344&amp;w=252&amp;s=78a99d14bd749e85971bdca2cab602d5</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7505403b8a4bcb3f2029de2717d4afc4&amp;w=252&amp;s=c0434f2f6e60412e5e7ecf2eef829ab0</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>96b34bda344d60ec</t>
+          <t>805842b23be73fb3</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -7765,7 +7827,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>1 pose</t>
+          <t>3 pakker</t>
         </is>
       </c>
     </row>
@@ -7777,41 +7839,37 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Lindt Excellence chokolade</t>
+          <t>Indpakning</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Lindt</t>
+          <t>Indpakning</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>100 g</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>350,00. kr/kg</t>
-        </is>
-      </c>
+          <t>, g</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
-          <t>1032334</t>
+          <t>1032360</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffa17f1fab0cb98d42f55636724d59223%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe60a0a06130a95b493e510fe95c31bbe%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F08e017a61d039ece6dd4f14583ad64ed&amp;w=252&amp;s=7663ac3ec0486b108096255491bd72a7</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbb6b21cf9c54434874e0ef4e7c05e630&amp;w=552&amp;s=84c494ed55b2e77185b78df42dfc367c</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>ace9711616e1ad8d</t>
+          <t>cecd3198663833ce</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -7821,7 +7879,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>1 plade</t>
+          <t>1 stk.</t>
         </is>
       </c>
     </row>
@@ -7833,53 +7891,35 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>M&amp;M's eller Maltesers</t>
+          <t>Ovnfaste fade</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>M&amp;M's</t>
+          <t>Ovnfaste</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>93-125 g</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>301,08. kr/kg</t>
-        </is>
-      </c>
-      <c r="F137" t="n">
-        <v>28</v>
-      </c>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>1032338</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd8fe0605bca67b79f79df39f4c798fc1%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F22691f7565912a8e280633d7cd61ef81%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb47cfcdca344d4f7d730e1779f8bf55d&amp;w=252&amp;s=d6d04e17983a0c02541f2471b47db75d</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>b5b25a9d4d48694b</t>
-        </is>
-      </c>
+          <t>1032386</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>1 pose</t>
-        </is>
-      </c>
+      <c r="L137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7889,41 +7929,35 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Coca-Cola, Tuborg Squash eller Monster</t>
+          <t>Udvalgte Gastromax køkkenredskaber</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Coca-Cola,</t>
+          <t>Udvalgte</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>. 24 x 33 cl</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>19,75 kr/l</t>
-        </is>
-      </c>
-      <c r="F138" t="n">
-        <v>79</v>
-      </c>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>1032348</t>
+          <t>1032388</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F9367eeb451f887222420fd3d05dbb8b1&amp;w=552&amp;s=8ef83f672ea1720f7bdf850713492225</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbe4176b465cbb9eaa7319ee66f781012&amp;w=1152&amp;s=ee17c69604190a18362583e4f1b806d5</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>c7336fc43e38086b</t>
+          <t>d99999622667791c</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -7931,11 +7965,7 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>1 pakke</t>
-        </is>
-      </c>
+      <c r="L138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7945,41 +7975,31 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Smirnoff</t>
+          <t>Bluey 3-pak hipster eller 2-pak boxershorts</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Smirnoff</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>27,5 cl</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>47,27 kr/l</t>
-        </is>
-      </c>
-      <c r="F139" t="n">
-        <v>13</v>
-      </c>
+          <t>Bluey</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>1032342</t>
+          <t>1032393</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc204450127c987e0a2dc615139740e6c%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2f8f90c27c5f0fe41ccc197a03a3a00b%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff0d878e996b891f0252e0b633cefd2f0&amp;w=236&amp;s=7f55e5e728c765805f59271787ee02ad</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa93b1e5f88fa258b3a20a6c52833dc94&amp;w=1152&amp;s=51db888b3785d099c61bd48d48ddcb6e</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>ad4152fa03b75b07</t>
+          <t>84e80b17797d1774</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -7989,7 +8009,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>1 pakke</t>
         </is>
       </c>
     </row>
@@ -8001,41 +8021,41 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Blandet saft, Cocio eller 16 Serien</t>
+          <t>Ribena</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Blandet</t>
+          <t>Ribena</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>. 60-100 cl</t>
+          <t>3 x 85 cl</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>26,67. kr/l</t>
+          <t>27,06. kr/l</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
-          <t>1032353</t>
+          <t>1032401</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F1a75ea076163d6cddb0fc6868664ec47&amp;w=252&amp;s=4ceb6463c4579cee6afac5c1cb209bce</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F75347ae354784e9008f1f3778a01c554%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5b09cde4195e593e11ee54e2bfc62b7d%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4d51d3cfba7d26613c50927fb72c7a68&amp;w=251&amp;s=34100420548d0e8143b723477d1a3bfc</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>c4b272b6e392e2c9</t>
+          <t>acc95236a97233ae</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -8045,7 +8065,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>1 stk./flaske</t>
+          <t>3 flasker</t>
         </is>
       </c>
     </row>
@@ -8057,41 +8077,41 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Faxe Kondi eller Pepsi Max</t>
+          <t>San Pellegrino</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Faxe</t>
+          <t>San</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>150 cl</t>
+          <t>6x100 cl</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>12,00 kr/l</t>
+          <t>10,00 kr/l</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>1032350</t>
+          <t>1032402</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd0bd1df678221fa74c9449b0c09216f0&amp;w=252&amp;s=43376f4b5feb82e39b2ac08c22a92204</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5b957ae768be1db716b35d6aa306e4e2&amp;w=552&amp;s=0aa6dac213b0e80a8304cbfe025b3036</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>f48701701d7f0e6e</t>
+          <t>c26a3fd03fc278c2</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8101,7 +8121,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>1 flaske</t>
+          <t>6 flasker</t>
         </is>
       </c>
     </row>
@@ -8113,41 +8133,41 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Kaiserdom, Oranjeboom eller Praga øl</t>
+          <t>Irma rejer</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Kaiserdom,</t>
+          <t>Irma</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>50 cl</t>
+          <t>4x150 g</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>16,00 kr/l</t>
+          <t>165,00. kr/kg</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>1032340</t>
+          <t>1032403</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F14c38e90ab2e6791dad79baea5988e88&amp;w=252&amp;s=b60bcb51c8a34fcc5907b1f9ffbf6ac0</t>
+          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=694&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3cff44ec878276625e94d33eddb83d25&amp;w=507&amp;s=6a349ad3605db5ca16ce34692d74e0ec</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>da87257964e4984f</t>
+          <t>d0650ee83f9ee189</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8156,1682 +8176,6 @@
         </is>
       </c>
       <c r="L142" t="inlineStr">
-        <is>
-          <t>1 dåse</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Corona, Leffe, Peroni eller Stella Artois øl</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Corona,</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>. 33 cl</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>36,36 kr/l</t>
-        </is>
-      </c>
-      <c r="F143" t="n">
-        <v>12</v>
-      </c>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>1032355</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=214&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4d51277a0dfa650baaf4212c70bb82bf&amp;w=252&amp;s=ad9064b46952dd01c9dc2c9dbec2a342</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>b1392dd6c6197a13</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>1 flaske/dåse</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>1664, Carlsberg eller Tuborg øl</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>1664,</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>. 12-18 x 33 cl</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>22,47 kr/l</t>
-        </is>
-      </c>
-      <c r="F144" t="n">
-        <v>89</v>
-      </c>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>1032345</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5fb2cb78ae6e81779b3ba8e2ca16d9f5&amp;w=1152&amp;s=78420e93c7e6c3160e56ebfae0d2b811</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>d04861643d373fd3</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>1 pakke</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Whiskas menuboks eller tørkost</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Whiskas</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>800-1020 g</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>50,00. kr/kg</t>
-        </is>
-      </c>
-      <c r="F145" t="n">
-        <v>40</v>
-      </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>1032363</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7507f919eec60e502b127d1071208b32&amp;w=252&amp;s=4068aa337b6e6f24c42198a79c109204</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>90cc3c3acd6939a7</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>1 stk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Änglamark eller Coop Color vaskekapsler</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Änglamark</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>1 stk</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="n">
-        <v>39</v>
-      </c>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>1032357</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fc49559a533a30044634e6adaca380d68%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ffc3deeb63bdd2b141c92cb39d649610c&amp;w=252&amp;s=bafb594a39f187d9ae7df6401d6346cb</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>d4d6142f6f3e4823</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>1 stk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>A+ flydende vaske-middel eller kapsler</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>675 ml</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="n">
-        <v>27</v>
-      </c>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>1032359</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F568fabf752b06f7c1ccd8856fd0ee654&amp;w=343&amp;s=f996b38a30b2cf3f8646608aabf5b681</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>80e115e9f9167c9e</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>1 stk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Urban Spa håndæbe</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Urban</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>300-500 ml</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>96,67. kr/l</t>
-        </is>
-      </c>
-      <c r="F148" t="n">
-        <v>29</v>
-      </c>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>1032369</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fb4080f12a54dc31fdea134cf1ab20fca%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6096fa6d0a3ae1c7dbf0716031833320&amp;w=552&amp;s=8318b8e99c46ad642a236fe694def561</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>c45633633be8dcc8</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>1 stk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Änglamark håndopvask</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Änglamark</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>500 ml</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>18,00. kr/l</t>
-        </is>
-      </c>
-      <c r="F149" t="n">
-        <v>9</v>
-      </c>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>1032372</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3a3d575b4fbb667babf4046399bd2ddc&amp;w=129&amp;s=3e86d775810e3981b4c94a02e33fb3e2</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>c44f2e2f24bc74b4</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>1 stk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Domestos, Harpic toiletrengøring eller Bref blokke</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Domestos,</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>750 ml</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>400,00. kr/kg</t>
-        </is>
-      </c>
-      <c r="F150" t="n">
-        <v>15</v>
-      </c>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>1032374</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F311f7de2060d8d8e924aff6d27e7d7ae&amp;w=252&amp;s=96ff70458b992e6b1c537d4183ae3be4</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>e44f37a01d793133</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>1 stk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Always eller Tampax</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>16-60 stk</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>2,27. kr/stk</t>
-        </is>
-      </c>
-      <c r="F151" t="n">
-        <v>109</v>
-      </c>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>1032375</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7505403b8a4bcb3f2029de2717d4afc4&amp;w=252&amp;s=c0434f2f6e60412e5e7ecf2eef829ab0</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>805842b23be73fb3</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>3 pakker</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Livol eller Gerimax vitaminer</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Livol</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>80-150 stk</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>1,11. kr/stk</t>
-        </is>
-      </c>
-      <c r="F152" t="n">
-        <v>89</v>
-      </c>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>1032382</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8a8d2864ae1a9ccc4251e7986c92a9cd&amp;w=552&amp;s=316bf63c38fae7a44df0866d450a5445</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>ef65319a1a518e2d</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>1 stk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Kleenex</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Kleenex</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>56-72 stk</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>0,19. kr/stk</t>
-        </is>
-      </c>
-      <c r="F153" t="n">
-        <v>14</v>
-      </c>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>1032378</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa9abe7e675e43d817d027c2d24a91552%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F764e729fb48391b3ed7c6ee09818fcee%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F6aa55d5b7210d408e56cb3aba16d1a27&amp;w=552&amp;s=b26b1a1280952b2601390fd4ae9f4b3b</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>d6e5291aac46c2f5</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>1 pakke</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Essence kurv str M</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Essence</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>2 stk</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="n">
-        <v>30</v>
-      </c>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>1032362</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=619&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4599ca8db1f52a1e8b955e9cb4f16ebc%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fe0c11f636ecb4899113d8fdaa0c789fa&amp;w=552&amp;s=771c6a04d212c62c0c63e020845b32e0</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>817a7d853a47698e</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>2 stk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Indpakning</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Indpakning</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>, g</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="n">
-        <v>5</v>
-      </c>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>1032360</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=248&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbb6b21cf9c54434874e0ef4e7c05e630&amp;w=552&amp;s=84c494ed55b2e77185b78df42dfc367c</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>cecd3198663833ce</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>1 stk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Nakke- og skuldermassage</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Nakke-</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="n">
-        <v>399</v>
-      </c>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>1032364</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>1 stk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>OBH Nordica støvsuger</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>OBH</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>. L</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="n">
-        <v>699</v>
-      </c>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>1032370</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4c36185453b387c77e988dab9a0500fa&amp;w=214&amp;s=2c3275ee3b962afd11544bbc3a0854e8</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>cb1e30c92d714bcd</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>1 stk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Sjö strygerobot</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Sjö</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>-1 l</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="n">
-        <v>499</v>
-      </c>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>1032368</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=231&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8519bef5a4c780b2f8a5977ef21cd5ca&amp;w=552&amp;s=a275946ef5b89e41e8234c9a903400dd</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>9966319966799966</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Sjö husholdningsprodukter</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Sjö</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>1 stk</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="n">
-        <v>99</v>
-      </c>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>1032373</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F30b40da706c72239dee649a83dd6a91c&amp;w=1152&amp;s=8016c39982f18ff213417d282201a037</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>91696a366966d6b4</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>1 stk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Leki Orange mobiltilbehør</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Leki</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>3 stk</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="n">
-        <v>100</v>
-      </c>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>1032377</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fdfbdf3d6ca169f60df8d03228bbed721%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7f150f7f7e31e1004519c360620c4135%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F98f97e4844fcc74429b160cfa50929b3&amp;w=552&amp;s=6cd24750c0a36550ef0e65b816eb9ed3</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>94199936694ee1f9</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>3 stk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>25% rabat på alle print</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>1032376</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Ovnfaste fade</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Ovnfaste</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>1032386</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Udvalgte opbevaringsglas</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Udvalgte</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>200-1500 ml</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>1032385</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F7b9d245863e5d29f1987e6edcc5a658e&amp;w=1152&amp;s=1e2d3677b53fd58d874ebb78ca00c8d8</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>c9993c9467c139bc</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Udvalgte Gastromax køkkenredskaber</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Udvalgte</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>1032388</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fbe4176b465cbb9eaa7319ee66f781012&amp;w=1152&amp;s=ee17c69604190a18362583e4f1b806d5</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>d99999622667791c</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Opbevaringssæt 6-pak</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Opbevaringssæt</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2 x 500 ml</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="n">
-        <v>79</v>
-      </c>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>1032383</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F880557680fc5f735654372578a01a6d4&amp;w=343&amp;s=4db085654b5d0e55a15d6c522771a5cc</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>c81f7072798d34f1</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>1 sæt</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Klar til sommer</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Klar</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>128.  G</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="n">
-        <v>80</v>
-      </c>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>1032392</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=602&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Ff2411675331b4577005f65368bd434e2&amp;w=552&amp;s=0724f2a457bbc41a915a37a7328744c4</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>d12e2ed1eee3900e</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Bluey kjole</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Bluey</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>1 stk</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>1032389</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F2cf274507a758766463f2bd7e00a54d5&amp;w=131&amp;s=ce9a826cc83b39784246999a7c98cd86</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>955a2e582ee125e7</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>1 stk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Bluey 3-pak hipster eller 2-pak boxershorts</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Bluey</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>1032393</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa93b1e5f88fa258b3a20a6c52833dc94&amp;w=1152&amp;s=51db888b3785d099c61bd48d48ddcb6e</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>84e80b17797d1774</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>1 pakke</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Sloggi Pure Comfort</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Sloggi</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>1032397</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fd1aa829f25f4f7331f43856b2df9c1bd&amp;w=1152&amp;s=2767e8553062196bd4abf51342a83f45</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>9bcc74cc65316633</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Dameundertøj</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Dameundertøj</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>3 stk</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="n">
-        <v>149</v>
-      </c>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>1032396</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>3 stk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>EVA dameslippers</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>EVA</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>1032394</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=636&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F8882fac3a7634bbfb1203ca9a3dfc590&amp;w=552&amp;s=45b35642568078c332252384efbf18a3</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>9d9b624572d69c0b</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>1 par</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Dreams, Gosh eller Kaos deospray</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Dreams,</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>150 ml</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>566,67. kr/l</t>
-        </is>
-      </c>
-      <c r="F172" t="n">
-        <v>85</v>
-      </c>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>1032398</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2Fa420994c6b75e356fe6da0294d108a9f%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F18eff764342e595150406c8c226bf353%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F571efe16a7c29009bb4dda55b1f74fe7&amp;w=552&amp;s=59b981a1d26f0711f8bf8da28238671f</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>cf38383892c7c3c7</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>1 stk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Ribena</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Ribena</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>3 x 85 cl</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>27,06. kr/l</t>
-        </is>
-      </c>
-      <c r="F173" t="n">
-        <v>69</v>
-      </c>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>1032401</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2.6&amp;h=323&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F75347ae354784e9008f1f3778a01c554%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5b09cde4195e593e11ee54e2bfc62b7d%2Cs3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F4d51d3cfba7d26613c50927fb72c7a68&amp;w=251&amp;s=34100420548d0e8143b723477d1a3bfc</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>acc95236a97233ae</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>3 flasker</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>San Pellegrino</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>San</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>6x100 cl</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>10,00 kr/l</t>
-        </is>
-      </c>
-      <c r="F174" t="n">
-        <v>60</v>
-      </c>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>1032402</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=265&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F5b957ae768be1db716b35d6aa306e4e2&amp;w=552&amp;s=0aa6dac213b0e80a8304cbfe025b3036</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>c26a3fd03fc278c2</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>6 flasker</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Avis</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Irma rejer</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Irma</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>4x150 g</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>165,00. kr/kg</t>
-        </is>
-      </c>
-      <c r="F175" t="n">
-        <v>99</v>
-      </c>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>1032403</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>https://image-transformer-api.tjek.com/?_id=v2&amp;h=694&amp;u=s3%3A%2F%2Fsgn-prd-bumblebee%2Ffeed-images%2F3cff44ec878276625e94d33eddb83d25&amp;w=507&amp;s=6a349ad3605db5ca16ce34692d74e0ec</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>d0650ee83f9ee189</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr">
         <is>
           <t>4 poser</t>
         </is>
